--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -1411,10 +1411,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117730596</v>
+        <v>117730652</v>
       </c>
       <c r="B8" t="n">
-        <v>90517</v>
+        <v>97740</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1423,25 +1423,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>220093</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1451,10 +1451,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448073</v>
+        <v>447857</v>
       </c>
       <c r="R8" t="n">
-        <v>7032151</v>
+        <v>7031920</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,17 +1516,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117730620</v>
+        <v>117730596</v>
       </c>
       <c r="B9" t="n">
-        <v>77417</v>
+        <v>90517</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1539,21 +1539,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1563,10 +1563,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447975</v>
+        <v>448073</v>
       </c>
       <c r="R9" t="n">
-        <v>7032018</v>
+        <v>7032151</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,10 +1635,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117730652</v>
+        <v>117730620</v>
       </c>
       <c r="B10" t="n">
-        <v>97740</v>
+        <v>77417</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1647,25 +1647,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220093</v>
+        <v>228579</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447857</v>
+        <v>447975</v>
       </c>
       <c r="R10" t="n">
-        <v>7031920</v>
+        <v>7032018</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1710,7 +1710,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1859,10 +1859,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117730584</v>
+        <v>117730635</v>
       </c>
       <c r="B12" t="n">
-        <v>97740</v>
+        <v>90499</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,38 +1871,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220093</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Småbodflon Ö, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448038</v>
+        <v>447984</v>
       </c>
       <c r="R12" t="n">
-        <v>7032237</v>
+        <v>7031919</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117730635</v>
+        <v>117730626</v>
       </c>
       <c r="B13" t="n">
-        <v>90499</v>
+        <v>78564</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1987,21 +1987,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447984</v>
+        <v>447933</v>
       </c>
       <c r="R13" t="n">
-        <v>7031919</v>
+        <v>7031939</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2083,10 +2083,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117730626</v>
+        <v>117730628</v>
       </c>
       <c r="B14" t="n">
-        <v>78564</v>
+        <v>79590</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,25 +2095,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>283</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447933</v>
+        <v>447950</v>
       </c>
       <c r="R14" t="n">
-        <v>7031939</v>
+        <v>7031927</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2195,10 +2195,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117730628</v>
+        <v>117730597</v>
       </c>
       <c r="B15" t="n">
-        <v>79590</v>
+        <v>74590</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2207,25 +2207,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6462</v>
+        <v>6486</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2235,10 +2235,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447950</v>
+        <v>448080</v>
       </c>
       <c r="R15" t="n">
-        <v>7031927</v>
+        <v>7032150</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2300,17 +2300,17 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117730597</v>
+        <v>117730584</v>
       </c>
       <c r="B16" t="n">
-        <v>74590</v>
+        <v>97740</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2319,38 +2319,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6486</v>
+        <v>220093</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Småbodflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448080</v>
+        <v>448038</v>
       </c>
       <c r="R16" t="n">
-        <v>7032150</v>
+        <v>7032237</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2412,17 +2412,17 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117730660</v>
+        <v>117730632</v>
       </c>
       <c r="B17" t="n">
-        <v>74592</v>
+        <v>74583</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,25 +2431,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6440</v>
+        <v>492</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2459,10 +2459,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447981</v>
+        <v>447955</v>
       </c>
       <c r="R17" t="n">
-        <v>7032123</v>
+        <v>7031923</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,10 +2531,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117730632</v>
+        <v>117730660</v>
       </c>
       <c r="B18" t="n">
-        <v>74583</v>
+        <v>74592</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2543,25 +2543,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>492</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2571,10 +2571,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447955</v>
+        <v>447981</v>
       </c>
       <c r="R18" t="n">
-        <v>7031923</v>
+        <v>7032123</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2755,10 +2755,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117720886</v>
+        <v>117730591</v>
       </c>
       <c r="B20" t="n">
-        <v>74592</v>
+        <v>97735</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2767,41 +2767,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>219795</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stångmyren (Stångmyren), Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448111</v>
+        <v>448061</v>
       </c>
       <c r="R20" t="n">
-        <v>7032224</v>
+        <v>7032169</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2851,51 +2851,26 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117730585</v>
+        <v>117720886</v>
       </c>
       <c r="B21" t="n">
-        <v>97857</v>
+        <v>74592</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2904,41 +2879,41 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Småbodflon Ö, Jmt</t>
+          <t>Stångmyren (Stångmyren), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448008</v>
+        <v>448111</v>
       </c>
       <c r="R21" t="n">
-        <v>7032180</v>
+        <v>7032224</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2967,7 +2942,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2977,7 +2952,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2988,26 +2963,51 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117730591</v>
+        <v>117730585</v>
       </c>
       <c r="B22" t="n">
-        <v>97735</v>
+        <v>97857</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3020,34 +3020,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>219795</v>
+        <v>221952</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Småbodflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448061</v>
+        <v>448008</v>
       </c>
       <c r="R22" t="n">
-        <v>7032169</v>
+        <v>7032180</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3079,7 +3079,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3089,7 +3089,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3109,7 +3109,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3564,10 +3564,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117730587</v>
+        <v>117730670</v>
       </c>
       <c r="B27" t="n">
-        <v>79561</v>
+        <v>78480</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3580,21 +3580,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3604,10 +3604,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448044</v>
+        <v>447963</v>
       </c>
       <c r="R27" t="n">
-        <v>7032175</v>
+        <v>7032212</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3639,7 +3639,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3649,7 +3649,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,17 +3669,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117730670</v>
+        <v>117730587</v>
       </c>
       <c r="B28" t="n">
-        <v>78480</v>
+        <v>79561</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3692,21 +3692,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3716,10 +3716,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447963</v>
+        <v>448044</v>
       </c>
       <c r="R28" t="n">
-        <v>7032212</v>
+        <v>7032175</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117730594</v>
+        <v>117730623</v>
       </c>
       <c r="B29" t="n">
-        <v>78480</v>
+        <v>90782</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3804,21 +3804,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>448073</v>
+        <v>447964</v>
       </c>
       <c r="R29" t="n">
-        <v>7032151</v>
+        <v>7032011</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3863,7 +3863,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3873,7 +3873,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3900,10 +3900,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117730623</v>
+        <v>117730594</v>
       </c>
       <c r="B30" t="n">
-        <v>90782</v>
+        <v>78480</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3916,21 +3916,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3940,10 +3940,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447964</v>
+        <v>448073</v>
       </c>
       <c r="R30" t="n">
-        <v>7032011</v>
+        <v>7032151</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY54"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117721029</v>
+        <v>117730646</v>
       </c>
       <c r="B4" t="n">
-        <v>78480</v>
+        <v>90499</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,46 +920,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stångmyren (Stångmyren), Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>448050</v>
+        <v>447885</v>
       </c>
       <c r="R4" t="n">
-        <v>7032167</v>
+        <v>7031873</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,51 +1000,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117730604</v>
+        <v>117730628</v>
       </c>
       <c r="B5" t="n">
-        <v>79562</v>
+        <v>79590</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1062,25 +1028,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1090,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>448069</v>
+        <v>447950</v>
       </c>
       <c r="R5" t="n">
-        <v>7032132</v>
+        <v>7031927</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1125,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1135,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1155,17 +1121,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117730664</v>
+        <v>117730654</v>
       </c>
       <c r="B6" t="n">
-        <v>79562</v>
+        <v>74592</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1178,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1202,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447989</v>
+        <v>447902</v>
       </c>
       <c r="R6" t="n">
-        <v>7032173</v>
+        <v>7032039</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1237,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1247,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117721068</v>
+        <v>117730602</v>
       </c>
       <c r="B7" t="n">
-        <v>77417</v>
+        <v>79521</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1286,41 +1252,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>229497</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stångmyren (Stångmyren), Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448050</v>
+        <v>448069</v>
       </c>
       <c r="R7" t="n">
-        <v>7032167</v>
+        <v>7032132</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1359,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,51 +1336,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117730652</v>
+        <v>117720883</v>
       </c>
       <c r="B8" t="n">
-        <v>97740</v>
+        <v>78480</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1423,41 +1364,50 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Châtel.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Stångmyren (Stångmyren), Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447857</v>
+        <v>448111</v>
       </c>
       <c r="R8" t="n">
-        <v>7031920</v>
+        <v>7032224</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,7 +1436,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1446,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,23 +1457,48 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117730596</v>
+        <v>117730633</v>
       </c>
       <c r="B9" t="n">
         <v>90517</v>
@@ -1563,10 +1538,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>448073</v>
+        <v>447960</v>
       </c>
       <c r="R9" t="n">
-        <v>7032151</v>
+        <v>7031925</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1598,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1608,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,17 +1603,17 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117730620</v>
+        <v>117730665</v>
       </c>
       <c r="B10" t="n">
-        <v>77417</v>
+        <v>79561</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1651,21 +1626,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1675,10 +1650,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447975</v>
+        <v>447986</v>
       </c>
       <c r="R10" t="n">
-        <v>7032018</v>
+        <v>7032183</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1710,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1720,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1740,17 +1715,17 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117730654</v>
+        <v>117720990</v>
       </c>
       <c r="B11" t="n">
-        <v>74592</v>
+        <v>79561</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,37 +1738,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Stångmyren (Stångmyren), Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447902</v>
+        <v>448054</v>
       </c>
       <c r="R11" t="n">
-        <v>7032039</v>
+        <v>7032149</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1822,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1832,7 +1807,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,26 +1818,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117730635</v>
+        <v>117730606</v>
       </c>
       <c r="B12" t="n">
-        <v>90499</v>
+        <v>79561</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,21 +1875,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447984</v>
+        <v>448072</v>
       </c>
       <c r="R12" t="n">
-        <v>7031919</v>
+        <v>7032136</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1934,7 +1934,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,17 +1964,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117730626</v>
+        <v>117730592</v>
       </c>
       <c r="B13" t="n">
-        <v>78564</v>
+        <v>104914</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,25 +1983,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>283</v>
+        <v>221725</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2011,10 +2011,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447933</v>
+        <v>448069</v>
       </c>
       <c r="R13" t="n">
-        <v>7031939</v>
+        <v>7032155</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2046,7 +2046,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,17 +2076,17 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117730628</v>
+        <v>117720886</v>
       </c>
       <c r="B14" t="n">
-        <v>79590</v>
+        <v>74592</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,41 +2095,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Stångmyren (Stångmyren), Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447950</v>
+        <v>448111</v>
       </c>
       <c r="R14" t="n">
-        <v>7031927</v>
+        <v>7032224</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,26 +2179,51 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117730597</v>
+        <v>117721029</v>
       </c>
       <c r="B15" t="n">
-        <v>74590</v>
+        <v>78480</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2207,41 +2232,50 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Stångmyren (Stångmyren), Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448080</v>
+        <v>448050</v>
       </c>
       <c r="R15" t="n">
-        <v>7032150</v>
+        <v>7032167</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2270,7 +2304,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2280,7 +2314,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,26 +2325,51 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117730584</v>
+        <v>117721129</v>
       </c>
       <c r="B16" t="n">
-        <v>97740</v>
+        <v>74592</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2319,41 +2378,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220093</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Småbodflon Ö, Jmt</t>
+          <t>Stångmyren (Stångmyren), Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448038</v>
+        <v>448050</v>
       </c>
       <c r="R16" t="n">
-        <v>7032237</v>
+        <v>7032167</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2382,7 +2441,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2392,7 +2451,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,26 +2462,51 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117730632</v>
+        <v>117730667</v>
       </c>
       <c r="B17" t="n">
-        <v>74583</v>
+        <v>77417</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,25 +2515,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>492</v>
+        <v>228579</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2459,10 +2543,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447955</v>
+        <v>447983</v>
       </c>
       <c r="R17" t="n">
-        <v>7031923</v>
+        <v>7032208</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2494,7 +2578,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2504,7 +2588,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,10 +2615,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117730660</v>
+        <v>117730662</v>
       </c>
       <c r="B18" t="n">
-        <v>74592</v>
+        <v>97857</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2543,25 +2627,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6440</v>
+        <v>221952</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2571,10 +2655,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447981</v>
+        <v>447993</v>
       </c>
       <c r="R18" t="n">
-        <v>7032123</v>
+        <v>7032161</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2606,7 +2690,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2616,7 +2700,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2643,10 +2727,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117730667</v>
+        <v>117730596</v>
       </c>
       <c r="B19" t="n">
-        <v>77417</v>
+        <v>90517</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2659,21 +2743,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2683,10 +2767,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447983</v>
+        <v>448073</v>
       </c>
       <c r="R19" t="n">
-        <v>7032208</v>
+        <v>7032151</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2718,7 +2802,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2728,7 +2812,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2748,17 +2832,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117730591</v>
+        <v>117730670</v>
       </c>
       <c r="B20" t="n">
-        <v>97735</v>
+        <v>78480</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2767,25 +2851,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>219795</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2795,10 +2879,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>448061</v>
+        <v>447963</v>
       </c>
       <c r="R20" t="n">
-        <v>7032169</v>
+        <v>7032212</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2830,7 +2914,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2840,7 +2924,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2860,17 +2944,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117720886</v>
+        <v>117730621</v>
       </c>
       <c r="B21" t="n">
-        <v>74592</v>
+        <v>78480</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2883,37 +2967,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stångmyren (Stångmyren), Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>448111</v>
+        <v>447974</v>
       </c>
       <c r="R21" t="n">
-        <v>7032224</v>
+        <v>7032018</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2942,7 +3026,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2952,7 +3036,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2963,51 +3047,26 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117730585</v>
+        <v>117730660</v>
       </c>
       <c r="B22" t="n">
-        <v>97857</v>
+        <v>74592</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3016,38 +3075,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221952</v>
+        <v>6440</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Småbodflon Ö, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>448008</v>
+        <v>447981</v>
       </c>
       <c r="R22" t="n">
-        <v>7032180</v>
+        <v>7032123</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3079,7 +3138,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3089,7 +3148,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3109,17 +3168,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117730592</v>
+        <v>117720942</v>
       </c>
       <c r="B23" t="n">
-        <v>104914</v>
+        <v>79562</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3128,41 +3187,41 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221725</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Stångmyren (Stångmyren), Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448069</v>
+        <v>448054</v>
       </c>
       <c r="R23" t="n">
-        <v>7032155</v>
+        <v>7032149</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3191,7 +3250,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3201,7 +3260,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3212,26 +3271,51 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117730618</v>
+        <v>117730666</v>
       </c>
       <c r="B24" t="n">
-        <v>97740</v>
+        <v>90517</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3240,25 +3324,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220093</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3268,10 +3352,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>448064</v>
+        <v>447986</v>
       </c>
       <c r="R24" t="n">
-        <v>7032071</v>
+        <v>7032193</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3303,7 +3387,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3313,7 +3397,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3333,17 +3417,17 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117730602</v>
+        <v>117730656</v>
       </c>
       <c r="B25" t="n">
-        <v>79521</v>
+        <v>78480</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3352,25 +3436,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3380,10 +3464,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448069</v>
+        <v>448021</v>
       </c>
       <c r="R25" t="n">
-        <v>7032132</v>
+        <v>7032121</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3415,7 +3499,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3425,7 +3509,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3445,17 +3529,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117730659</v>
+        <v>117730597</v>
       </c>
       <c r="B26" t="n">
-        <v>77417</v>
+        <v>74590</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3464,25 +3548,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228579</v>
+        <v>6486</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3492,10 +3576,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447981</v>
+        <v>448080</v>
       </c>
       <c r="R26" t="n">
-        <v>7032123</v>
+        <v>7032150</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3527,7 +3611,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3537,7 +3621,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3557,17 +3641,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117730670</v>
+        <v>117730586</v>
       </c>
       <c r="B27" t="n">
-        <v>78480</v>
+        <v>97740</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3576,38 +3660,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220093</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Småbodflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447963</v>
+        <v>448008</v>
       </c>
       <c r="R27" t="n">
-        <v>7032212</v>
+        <v>7032180</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3639,7 +3723,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3649,7 +3733,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,17 +3753,17 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117730587</v>
+        <v>117730668</v>
       </c>
       <c r="B28" t="n">
-        <v>79561</v>
+        <v>74592</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3692,21 +3776,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3716,10 +3800,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>448044</v>
+        <v>447983</v>
       </c>
       <c r="R28" t="n">
-        <v>7032175</v>
+        <v>7032208</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3751,7 +3835,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3761,7 +3845,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3781,17 +3865,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117730623</v>
+        <v>117730664</v>
       </c>
       <c r="B29" t="n">
-        <v>90782</v>
+        <v>79562</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3804,21 +3888,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3828,10 +3912,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447964</v>
+        <v>447989</v>
       </c>
       <c r="R29" t="n">
-        <v>7032011</v>
+        <v>7032173</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3863,7 +3947,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3873,7 +3957,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3893,17 +3977,17 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117730594</v>
+        <v>117730635</v>
       </c>
       <c r="B30" t="n">
-        <v>78480</v>
+        <v>90499</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3916,21 +4000,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3940,10 +4024,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>448073</v>
+        <v>447984</v>
       </c>
       <c r="R30" t="n">
-        <v>7032151</v>
+        <v>7031919</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -3975,7 +4059,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3985,7 +4069,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4005,17 +4089,17 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117730653</v>
+        <v>117730632</v>
       </c>
       <c r="B31" t="n">
-        <v>77417</v>
+        <v>74583</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4024,25 +4108,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228579</v>
+        <v>492</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4052,10 +4136,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447872</v>
+        <v>447955</v>
       </c>
       <c r="R31" t="n">
-        <v>7031959</v>
+        <v>7031923</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4087,7 +4171,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4097,7 +4181,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4124,10 +4208,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117730668</v>
+        <v>117730587</v>
       </c>
       <c r="B32" t="n">
-        <v>74592</v>
+        <v>79561</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4140,21 +4224,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4164,10 +4248,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447983</v>
+        <v>448044</v>
       </c>
       <c r="R32" t="n">
-        <v>7032208</v>
+        <v>7032175</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -4199,7 +4283,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4209,7 +4293,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4229,17 +4313,17 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117730621</v>
+        <v>117730645</v>
       </c>
       <c r="B33" t="n">
-        <v>78480</v>
+        <v>90513</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4252,21 +4336,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4276,10 +4360,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447974</v>
+        <v>447905</v>
       </c>
       <c r="R33" t="n">
-        <v>7032018</v>
+        <v>7031857</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4311,7 +4395,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4321,7 +4405,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4341,17 +4425,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117730669</v>
+        <v>117730601</v>
       </c>
       <c r="B34" t="n">
-        <v>97857</v>
+        <v>74404</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4364,21 +4448,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221952</v>
+        <v>6428</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4388,10 +4472,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447978</v>
+        <v>448071</v>
       </c>
       <c r="R34" t="n">
-        <v>7032207</v>
+        <v>7032132</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4423,7 +4507,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4433,7 +4517,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>07:23</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4453,17 +4537,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117730662</v>
+        <v>117730584</v>
       </c>
       <c r="B35" t="n">
-        <v>97857</v>
+        <v>97740</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4476,34 +4560,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Småbodflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447993</v>
+        <v>448038</v>
       </c>
       <c r="R35" t="n">
-        <v>7032161</v>
+        <v>7032237</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4535,7 +4619,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4545,7 +4629,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4565,17 +4649,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117730656</v>
+        <v>117730585</v>
       </c>
       <c r="B36" t="n">
-        <v>78480</v>
+        <v>97857</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4584,38 +4668,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Småbodflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>448021</v>
+        <v>448008</v>
       </c>
       <c r="R36" t="n">
-        <v>7032121</v>
+        <v>7032180</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4647,7 +4731,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4657,7 +4741,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4677,17 +4761,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117730625</v>
+        <v>117730604</v>
       </c>
       <c r="B37" t="n">
-        <v>78480</v>
+        <v>79562</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4700,21 +4784,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4724,10 +4808,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447931</v>
+        <v>448069</v>
       </c>
       <c r="R37" t="n">
-        <v>7031941</v>
+        <v>7032132</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4759,7 +4843,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4769,7 +4853,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4796,10 +4880,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117730645</v>
+        <v>117730630</v>
       </c>
       <c r="B38" t="n">
-        <v>90513</v>
+        <v>74584</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4812,21 +4896,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4836,10 +4920,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447905</v>
+        <v>447948</v>
       </c>
       <c r="R38" t="n">
-        <v>7031857</v>
+        <v>7031925</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -4871,7 +4955,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4881,7 +4965,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4908,10 +4992,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117730665</v>
+        <v>117730623</v>
       </c>
       <c r="B39" t="n">
-        <v>79561</v>
+        <v>90782</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4924,21 +5008,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4948,10 +5032,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447986</v>
+        <v>447964</v>
       </c>
       <c r="R39" t="n">
-        <v>7032183</v>
+        <v>7032011</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -4983,7 +5067,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4993,7 +5077,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5013,17 +5097,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117730666</v>
+        <v>117730591</v>
       </c>
       <c r="B40" t="n">
-        <v>90517</v>
+        <v>97735</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5032,25 +5116,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>219795</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5060,10 +5144,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>447986</v>
+        <v>448061</v>
       </c>
       <c r="R40" t="n">
-        <v>7032193</v>
+        <v>7032169</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5095,7 +5179,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5105,7 +5189,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5125,17 +5209,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117721129</v>
+        <v>117730618</v>
       </c>
       <c r="B41" t="n">
-        <v>74592</v>
+        <v>97740</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5144,41 +5228,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6440</v>
+        <v>220093</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stångmyren (Stångmyren), Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448050</v>
+        <v>448064</v>
       </c>
       <c r="R41" t="n">
-        <v>7032167</v>
+        <v>7032071</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5207,7 +5291,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5217,7 +5301,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5228,51 +5312,26 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117730650</v>
+        <v>117730655</v>
       </c>
       <c r="B42" t="n">
-        <v>97740</v>
+        <v>97857</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5285,21 +5344,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5309,10 +5368,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447843</v>
+        <v>447931</v>
       </c>
       <c r="R42" t="n">
-        <v>7031899</v>
+        <v>7032019</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5344,7 +5403,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5354,7 +5413,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5381,10 +5440,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117730606</v>
+        <v>117730653</v>
       </c>
       <c r="B43" t="n">
-        <v>79561</v>
+        <v>77417</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5397,21 +5456,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5421,10 +5480,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>448072</v>
+        <v>447872</v>
       </c>
       <c r="R43" t="n">
-        <v>7032136</v>
+        <v>7031959</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5456,7 +5515,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5466,7 +5525,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5486,17 +5545,17 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117730646</v>
+        <v>117730594</v>
       </c>
       <c r="B44" t="n">
-        <v>90499</v>
+        <v>78480</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5509,21 +5568,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5533,10 +5592,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447885</v>
+        <v>448073</v>
       </c>
       <c r="R44" t="n">
-        <v>7031873</v>
+        <v>7032151</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5568,7 +5627,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5578,7 +5637,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5598,17 +5657,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117720942</v>
+        <v>117730652</v>
       </c>
       <c r="B45" t="n">
-        <v>79562</v>
+        <v>97740</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5617,41 +5676,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>220093</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stångmyren (Stångmyren), Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>448054</v>
+        <v>447857</v>
       </c>
       <c r="R45" t="n">
-        <v>7032149</v>
+        <v>7031920</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5680,7 +5739,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5690,7 +5749,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5701,51 +5760,26 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117720990</v>
+        <v>117730650</v>
       </c>
       <c r="B46" t="n">
-        <v>79561</v>
+        <v>97740</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5754,41 +5788,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>220093</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stångmyren (Stångmyren), Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>448054</v>
+        <v>447843</v>
       </c>
       <c r="R46" t="n">
-        <v>7032149</v>
+        <v>7031899</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5817,7 +5851,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5827,7 +5861,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5838,51 +5872,26 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117730630</v>
+        <v>117730620</v>
       </c>
       <c r="B47" t="n">
-        <v>74584</v>
+        <v>77417</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5895,21 +5904,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>308</v>
+        <v>228579</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5919,10 +5928,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447948</v>
+        <v>447975</v>
       </c>
       <c r="R47" t="n">
-        <v>7031925</v>
+        <v>7032018</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5954,7 +5963,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5964,7 +5973,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5984,17 +5993,17 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>117730633</v>
+        <v>117730669</v>
       </c>
       <c r="B48" t="n">
-        <v>90517</v>
+        <v>97857</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6003,25 +6012,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>221952</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -6031,10 +6040,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447960</v>
+        <v>447978</v>
       </c>
       <c r="R48" t="n">
-        <v>7031925</v>
+        <v>7032207</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6066,7 +6075,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6076,7 +6085,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6103,10 +6112,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117730586</v>
+        <v>117730663</v>
       </c>
       <c r="B49" t="n">
-        <v>97740</v>
+        <v>57287</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6115,38 +6124,46 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220093</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Småbodflon Ö, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>448008</v>
+        <v>447983</v>
       </c>
       <c r="R49" t="n">
-        <v>7032180</v>
+        <v>7032169</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6178,7 +6195,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6188,7 +6205,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6208,17 +6225,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117730648</v>
+        <v>117730659</v>
       </c>
       <c r="B50" t="n">
-        <v>104914</v>
+        <v>77417</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6227,25 +6244,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221725</v>
+        <v>228579</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6255,10 +6272,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447847</v>
+        <v>447981</v>
       </c>
       <c r="R50" t="n">
-        <v>7031902</v>
+        <v>7032123</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6290,7 +6307,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6300,7 +6317,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6327,10 +6344,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117730663</v>
+        <v>117730626</v>
       </c>
       <c r="B51" t="n">
-        <v>57287</v>
+        <v>78564</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6343,42 +6360,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>283</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447983</v>
+        <v>447933</v>
       </c>
       <c r="R51" t="n">
-        <v>7032169</v>
+        <v>7031939</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6410,7 +6419,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6420,7 +6429,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6447,10 +6456,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117730655</v>
+        <v>117730625</v>
       </c>
       <c r="B52" t="n">
-        <v>97857</v>
+        <v>78480</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6459,25 +6468,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6490,7 +6499,7 @@
         <v>447931</v>
       </c>
       <c r="R52" t="n">
-        <v>7032019</v>
+        <v>7031941</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6522,7 +6531,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6532,7 +6541,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6552,17 +6561,17 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117730601</v>
+        <v>117721068</v>
       </c>
       <c r="B53" t="n">
-        <v>74404</v>
+        <v>77417</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6571,41 +6580,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6428</v>
+        <v>228579</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Stångmyren (Stångmyren), Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>448071</v>
+        <v>448050</v>
       </c>
       <c r="R53" t="n">
-        <v>7032132</v>
+        <v>7032167</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6634,7 +6643,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6644,7 +6653,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6655,26 +6664,51 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117720883</v>
+        <v>117730648</v>
       </c>
       <c r="B54" t="n">
-        <v>78480</v>
+        <v>104914</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6683,50 +6717,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Stångmyren (Stångmyren), Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>448111</v>
+        <v>447847</v>
       </c>
       <c r="R54" t="n">
-        <v>7032224</v>
+        <v>7031902</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6755,7 +6780,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6765,7 +6790,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6776,44 +6801,281 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Matilda Pettersson</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>118093428</v>
+      </c>
+      <c r="B55" t="n">
+        <v>101374</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>22</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Skarptandad daggkåpa</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Alchemilla oxyodonta</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>447988</v>
+      </c>
+      <c r="R55" t="n">
+        <v>7032159</v>
+      </c>
+      <c r="S55" t="n">
+        <v>5</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
           <t>Fredrik Jonsson</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
+      <c r="AX55" t="inlineStr">
         <is>
           <t>Fredrik Jonsson</t>
         </is>
       </c>
-      <c r="AY54" t="inlineStr"/>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>117730599</v>
+      </c>
+      <c r="B56" t="n">
+        <v>74589</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>310</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Nordlig nållav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Chaenotheca laevigata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>448071</v>
+      </c>
+      <c r="R56" t="n">
+        <v>7032132</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-06-12</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117730646</v>
+        <v>117730662</v>
       </c>
       <c r="B4" t="n">
-        <v>90499</v>
+        <v>97859</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447885</v>
+        <v>447993</v>
       </c>
       <c r="R4" t="n">
-        <v>7031873</v>
+        <v>7032161</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117730628</v>
+        <v>117730666</v>
       </c>
       <c r="B5" t="n">
-        <v>79590</v>
+        <v>90519</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1028,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447950</v>
+        <v>447986</v>
       </c>
       <c r="R5" t="n">
-        <v>7031927</v>
+        <v>7032193</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:43</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117730654</v>
+        <v>117730584</v>
       </c>
       <c r="B6" t="n">
-        <v>74592</v>
+        <v>97742</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>220093</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Småbodflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447902</v>
+        <v>448038</v>
       </c>
       <c r="R6" t="n">
-        <v>7032039</v>
+        <v>7032237</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,17 +1233,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117730602</v>
+        <v>117730618</v>
       </c>
       <c r="B7" t="n">
-        <v>79521</v>
+        <v>97742</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>229497</v>
+        <v>220093</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448069</v>
+        <v>448064</v>
       </c>
       <c r="R7" t="n">
-        <v>7032132</v>
+        <v>7032071</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>117720883</v>
+        <v>117730594</v>
       </c>
       <c r="B8" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1385,29 +1385,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stångmyren (Stångmyren), Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>448111</v>
+        <v>448073</v>
       </c>
       <c r="R8" t="n">
-        <v>7032224</v>
+        <v>7032151</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1436,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1446,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,51 +1448,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>117730633</v>
+        <v>117730632</v>
       </c>
       <c r="B9" t="n">
-        <v>90517</v>
+        <v>74585</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,25 +1476,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>492</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Smalskaftslav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracilenta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1538,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447960</v>
+        <v>447955</v>
       </c>
       <c r="R9" t="n">
-        <v>7031925</v>
+        <v>7031923</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1573,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117730665</v>
+        <v>117730628</v>
       </c>
       <c r="B10" t="n">
-        <v>79561</v>
+        <v>79592</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,25 +1588,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1650,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447986</v>
+        <v>447950</v>
       </c>
       <c r="R10" t="n">
-        <v>7032183</v>
+        <v>7031927</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1685,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117720990</v>
+        <v>117730623</v>
       </c>
       <c r="B11" t="n">
-        <v>79561</v>
+        <v>90784</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,37 +1704,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stångmyren (Stångmyren), Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>448054</v>
+        <v>447964</v>
       </c>
       <c r="R11" t="n">
-        <v>7032149</v>
+        <v>7032011</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1797,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,51 +1784,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>117730606</v>
+        <v>117730645</v>
       </c>
       <c r="B12" t="n">
-        <v>79561</v>
+        <v>90515</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,21 +1816,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1899,10 +1840,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>448072</v>
+        <v>447905</v>
       </c>
       <c r="R12" t="n">
-        <v>7032136</v>
+        <v>7031857</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1934,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1944,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1964,17 +1905,17 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>117730592</v>
+        <v>117721129</v>
       </c>
       <c r="B13" t="n">
-        <v>104914</v>
+        <v>74594</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1983,41 +1924,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Stångmyren (Stångmyren), Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>448069</v>
+        <v>448050</v>
       </c>
       <c r="R13" t="n">
-        <v>7032155</v>
+        <v>7032167</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2046,7 +1987,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2056,7 +1997,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,26 +2008,51 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>117720886</v>
+        <v>117730656</v>
       </c>
       <c r="B14" t="n">
-        <v>74592</v>
+        <v>78482</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,37 +2065,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stångmyren (Stångmyren), Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>448111</v>
+        <v>448021</v>
       </c>
       <c r="R14" t="n">
-        <v>7032224</v>
+        <v>7032121</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2158,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2168,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>08:08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,51 +2145,26 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>117721029</v>
+        <v>117730591</v>
       </c>
       <c r="B15" t="n">
-        <v>78480</v>
+        <v>97737</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2232,50 +2173,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>219795</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hartm.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stångmyren (Stångmyren), Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>448050</v>
+        <v>448061</v>
       </c>
       <c r="R15" t="n">
-        <v>7032167</v>
+        <v>7032169</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2304,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2314,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2325,51 +2257,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>117721129</v>
+        <v>117730664</v>
       </c>
       <c r="B16" t="n">
-        <v>74592</v>
+        <v>79564</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2382,37 +2289,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stångmyren (Stångmyren), Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>448050</v>
+        <v>447989</v>
       </c>
       <c r="R16" t="n">
-        <v>7032167</v>
+        <v>7032173</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2441,7 +2348,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2451,7 +2358,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2462,51 +2369,26 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117730667</v>
+        <v>117730659</v>
       </c>
       <c r="B17" t="n">
-        <v>77417</v>
+        <v>77419</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2543,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447983</v>
+        <v>447981</v>
       </c>
       <c r="R17" t="n">
-        <v>7032208</v>
+        <v>7032123</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2578,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2588,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>07:26</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2615,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>117730662</v>
+        <v>117720883</v>
       </c>
       <c r="B18" t="n">
-        <v>97857</v>
+        <v>78482</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2627,41 +2509,50 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Stångmyren (Stångmyren), Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447993</v>
+        <v>448111</v>
       </c>
       <c r="R18" t="n">
-        <v>7032161</v>
+        <v>7032224</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2690,7 +2581,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2700,7 +2591,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2711,26 +2602,51 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>117730596</v>
+        <v>117730663</v>
       </c>
       <c r="B19" t="n">
-        <v>90517</v>
+        <v>57288</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2743,34 +2659,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>448073</v>
+        <v>447983</v>
       </c>
       <c r="R19" t="n">
-        <v>7032151</v>
+        <v>7032169</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2802,7 +2726,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2812,7 +2736,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2832,17 +2756,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>117730670</v>
+        <v>117730654</v>
       </c>
       <c r="B20" t="n">
-        <v>78480</v>
+        <v>74594</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2855,21 +2779,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2879,10 +2803,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447963</v>
+        <v>447902</v>
       </c>
       <c r="R20" t="n">
-        <v>7032212</v>
+        <v>7032039</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2914,7 +2838,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2924,7 +2848,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2951,10 +2875,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>117730621</v>
+        <v>117721029</v>
       </c>
       <c r="B21" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2984,20 +2908,29 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Stångmyren (Stångmyren), Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447974</v>
+        <v>448050</v>
       </c>
       <c r="R21" t="n">
-        <v>7032018</v>
+        <v>7032167</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3026,7 +2959,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3036,7 +2969,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3047,26 +2980,51 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117730660</v>
+        <v>117730596</v>
       </c>
       <c r="B22" t="n">
-        <v>74592</v>
+        <v>90519</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3079,21 +3037,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3103,10 +3061,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447981</v>
+        <v>448073</v>
       </c>
       <c r="R22" t="n">
-        <v>7032123</v>
+        <v>7032151</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3138,7 +3096,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3148,7 +3106,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3168,17 +3126,17 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>117720942</v>
+        <v>117721068</v>
       </c>
       <c r="B23" t="n">
-        <v>79562</v>
+        <v>77419</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3191,21 +3149,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>228579</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3215,10 +3173,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>448054</v>
+        <v>448050</v>
       </c>
       <c r="R23" t="n">
-        <v>7032149</v>
+        <v>7032167</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3250,7 +3208,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3260,7 +3218,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3274,17 +3232,17 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>Lågörtgranskog</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
@@ -3294,7 +3252,7 @@
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3312,10 +3270,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117730666</v>
+        <v>117730670</v>
       </c>
       <c r="B24" t="n">
-        <v>90517</v>
+        <v>78482</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3328,21 +3286,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3352,10 +3310,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447986</v>
+        <v>447963</v>
       </c>
       <c r="R24" t="n">
-        <v>7032193</v>
+        <v>7032212</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3387,7 +3345,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3397,7 +3355,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3424,10 +3382,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>117730656</v>
+        <v>117730667</v>
       </c>
       <c r="B25" t="n">
-        <v>78480</v>
+        <v>77419</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3440,21 +3398,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3464,10 +3422,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>448021</v>
+        <v>447983</v>
       </c>
       <c r="R25" t="n">
-        <v>7032121</v>
+        <v>7032208</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3499,7 +3457,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3509,7 +3467,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:08</t>
+          <t>07:26</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3536,10 +3494,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>117730597</v>
+        <v>117730665</v>
       </c>
       <c r="B26" t="n">
-        <v>74590</v>
+        <v>79563</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3548,25 +3506,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6486</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3576,10 +3534,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>448080</v>
+        <v>447986</v>
       </c>
       <c r="R26" t="n">
-        <v>7032150</v>
+        <v>7032183</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3611,7 +3569,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3621,7 +3579,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3641,17 +3599,17 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>117730586</v>
+        <v>117720942</v>
       </c>
       <c r="B27" t="n">
-        <v>97740</v>
+        <v>79564</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3660,41 +3618,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220093</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Småbodflon Ö, Jmt</t>
+          <t>Stångmyren (Stångmyren), Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>448008</v>
+        <v>448054</v>
       </c>
       <c r="R27" t="n">
-        <v>7032180</v>
+        <v>7032149</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3723,7 +3681,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3733,7 +3691,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3744,26 +3702,51 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>117730668</v>
+        <v>117730653</v>
       </c>
       <c r="B28" t="n">
-        <v>74592</v>
+        <v>77419</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3776,21 +3759,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3800,10 +3783,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447983</v>
+        <v>447872</v>
       </c>
       <c r="R28" t="n">
-        <v>7032208</v>
+        <v>7031959</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3835,7 +3818,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3845,7 +3828,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>07:25</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3872,10 +3855,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>117730664</v>
+        <v>117730630</v>
       </c>
       <c r="B29" t="n">
-        <v>79562</v>
+        <v>74586</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3888,21 +3871,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3912,10 +3895,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447989</v>
+        <v>447948</v>
       </c>
       <c r="R29" t="n">
-        <v>7032173</v>
+        <v>7031925</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3947,7 +3930,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3957,7 +3940,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3984,10 +3967,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>117730635</v>
+        <v>117730650</v>
       </c>
       <c r="B30" t="n">
-        <v>90499</v>
+        <v>97742</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3996,25 +3979,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>220093</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4024,10 +4007,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447984</v>
+        <v>447843</v>
       </c>
       <c r="R30" t="n">
-        <v>7031919</v>
+        <v>7031899</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4059,7 +4042,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4069,7 +4052,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4096,10 +4079,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>117730632</v>
+        <v>117730648</v>
       </c>
       <c r="B31" t="n">
-        <v>74583</v>
+        <v>104916</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4108,25 +4091,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>492</v>
+        <v>221725</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Smalskaftslav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chaenotheca gracilenta</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4136,10 +4119,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447955</v>
+        <v>447847</v>
       </c>
       <c r="R31" t="n">
-        <v>7031923</v>
+        <v>7031902</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4171,7 +4154,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4181,7 +4164,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4208,10 +4191,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>117730587</v>
+        <v>117720886</v>
       </c>
       <c r="B32" t="n">
-        <v>79561</v>
+        <v>74594</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4224,37 +4207,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Stångmyren (Stångmyren), Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>448044</v>
+        <v>448111</v>
       </c>
       <c r="R32" t="n">
-        <v>7032175</v>
+        <v>7032224</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4283,7 +4266,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4293,7 +4276,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4304,26 +4287,51 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>117730645</v>
+        <v>117730660</v>
       </c>
       <c r="B33" t="n">
-        <v>90513</v>
+        <v>74594</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4336,21 +4344,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>6440</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4360,10 +4368,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447905</v>
+        <v>447981</v>
       </c>
       <c r="R33" t="n">
-        <v>7031857</v>
+        <v>7032123</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4395,7 +4403,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4405,7 +4413,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4432,10 +4440,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>117730601</v>
+        <v>117730626</v>
       </c>
       <c r="B34" t="n">
-        <v>74404</v>
+        <v>78566</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4444,25 +4452,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6428</v>
+        <v>283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4472,10 +4480,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>448071</v>
+        <v>447933</v>
       </c>
       <c r="R34" t="n">
-        <v>7032132</v>
+        <v>7031939</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4507,7 +4515,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4517,7 +4525,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4537,17 +4545,17 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>117730584</v>
+        <v>117730625</v>
       </c>
       <c r="B35" t="n">
-        <v>97740</v>
+        <v>78482</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4556,38 +4564,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220093</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Småbodflon Ö, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>448038</v>
+        <v>447931</v>
       </c>
       <c r="R35" t="n">
-        <v>7032237</v>
+        <v>7031941</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4619,7 +4627,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4629,7 +4637,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4649,17 +4657,17 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>117730585</v>
+        <v>117730633</v>
       </c>
       <c r="B36" t="n">
-        <v>97857</v>
+        <v>90519</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4668,38 +4676,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221952</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Småbodflon Ö, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>448008</v>
+        <v>447960</v>
       </c>
       <c r="R36" t="n">
-        <v>7032180</v>
+        <v>7031925</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4731,7 +4739,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4741,7 +4749,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4761,17 +4769,17 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>117730604</v>
+        <v>117730668</v>
       </c>
       <c r="B37" t="n">
-        <v>79562</v>
+        <v>74594</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4784,21 +4792,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4808,10 +4816,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>448069</v>
+        <v>447983</v>
       </c>
       <c r="R37" t="n">
-        <v>7032132</v>
+        <v>7032208</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4843,7 +4851,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4853,7 +4861,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>07:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4873,17 +4881,17 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>117730630</v>
+        <v>117720990</v>
       </c>
       <c r="B38" t="n">
-        <v>74584</v>
+        <v>79563</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4896,37 +4904,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Stångmyren (Stångmyren), Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447948</v>
+        <v>448054</v>
       </c>
       <c r="R38" t="n">
-        <v>7031925</v>
+        <v>7032149</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4955,7 +4963,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4965,7 +4973,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4976,26 +4984,51 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Lågörtgranskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>117730623</v>
+        <v>117730646</v>
       </c>
       <c r="B39" t="n">
-        <v>90782</v>
+        <v>90501</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5008,21 +5041,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5032,10 +5065,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447964</v>
+        <v>447885</v>
       </c>
       <c r="R39" t="n">
-        <v>7032011</v>
+        <v>7031873</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5067,7 +5100,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5077,7 +5110,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5097,17 +5130,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>117730591</v>
+        <v>117730621</v>
       </c>
       <c r="B40" t="n">
-        <v>97735</v>
+        <v>78482</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5116,25 +5149,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>219795</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5144,10 +5177,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>448061</v>
+        <v>447974</v>
       </c>
       <c r="R40" t="n">
-        <v>7032169</v>
+        <v>7032018</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5179,7 +5212,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5189,7 +5222,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5216,10 +5249,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>117730618</v>
+        <v>117730597</v>
       </c>
       <c r="B41" t="n">
-        <v>97740</v>
+        <v>74592</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5228,25 +5261,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220093</v>
+        <v>6486</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5256,10 +5289,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>448064</v>
+        <v>448080</v>
       </c>
       <c r="R41" t="n">
-        <v>7032071</v>
+        <v>7032150</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -5291,7 +5324,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5301,7 +5334,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5328,10 +5361,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>117730655</v>
+        <v>117730587</v>
       </c>
       <c r="B42" t="n">
-        <v>97857</v>
+        <v>79563</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5340,25 +5373,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221952</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5368,10 +5401,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447931</v>
+        <v>448044</v>
       </c>
       <c r="R42" t="n">
-        <v>7032019</v>
+        <v>7032175</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5403,7 +5436,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5413,7 +5446,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5433,17 +5466,17 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>117730653</v>
+        <v>117730652</v>
       </c>
       <c r="B43" t="n">
-        <v>77417</v>
+        <v>97742</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5452,25 +5485,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228579</v>
+        <v>220093</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5480,10 +5513,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447872</v>
+        <v>447857</v>
       </c>
       <c r="R43" t="n">
-        <v>7031959</v>
+        <v>7031920</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5515,7 +5548,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5525,7 +5558,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>08:59</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5552,10 +5585,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>117730594</v>
+        <v>117730635</v>
       </c>
       <c r="B44" t="n">
-        <v>78480</v>
+        <v>90501</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5568,21 +5601,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5592,10 +5625,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>448073</v>
+        <v>447984</v>
       </c>
       <c r="R44" t="n">
-        <v>7032151</v>
+        <v>7031919</v>
       </c>
       <c r="S44" t="n">
         <v>25</v>
@@ -5627,7 +5660,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5637,7 +5670,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5657,17 +5690,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117730652</v>
+        <v>117730592</v>
       </c>
       <c r="B45" t="n">
-        <v>97740</v>
+        <v>104916</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5680,21 +5713,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220093</v>
+        <v>221725</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5704,10 +5737,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447857</v>
+        <v>448069</v>
       </c>
       <c r="R45" t="n">
-        <v>7031920</v>
+        <v>7032155</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5739,7 +5772,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5749,7 +5782,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5769,17 +5802,17 @@
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>117730650</v>
+        <v>117730585</v>
       </c>
       <c r="B46" t="n">
-        <v>97740</v>
+        <v>97859</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5792,34 +5825,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Småbodflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447843</v>
+        <v>448008</v>
       </c>
       <c r="R46" t="n">
-        <v>7031899</v>
+        <v>7032180</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5851,7 +5884,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5861,7 +5894,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5881,17 +5914,17 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>117730620</v>
+        <v>117730655</v>
       </c>
       <c r="B47" t="n">
-        <v>77417</v>
+        <v>97859</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5900,25 +5933,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228579</v>
+        <v>221952</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5928,10 +5961,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447975</v>
+        <v>447931</v>
       </c>
       <c r="R47" t="n">
-        <v>7032018</v>
+        <v>7032019</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5963,7 +5996,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5973,7 +6006,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5993,7 +6026,7 @@
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6003,7 +6036,7 @@
         <v>117730669</v>
       </c>
       <c r="B48" t="n">
-        <v>97857</v>
+        <v>97859</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6112,10 +6145,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>117730663</v>
+        <v>117730602</v>
       </c>
       <c r="B49" t="n">
-        <v>57287</v>
+        <v>79523</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6124,46 +6157,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447983</v>
+        <v>448069</v>
       </c>
       <c r="R49" t="n">
-        <v>7032169</v>
+        <v>7032132</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6195,7 +6220,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6205,7 +6230,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>07:45</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6225,17 +6250,17 @@
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>117730659</v>
+        <v>117730620</v>
       </c>
       <c r="B50" t="n">
-        <v>77417</v>
+        <v>77419</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6272,10 +6297,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447981</v>
+        <v>447975</v>
       </c>
       <c r="R50" t="n">
-        <v>7032123</v>
+        <v>7032018</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6307,7 +6332,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6317,7 +6342,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>08:02</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6337,17 +6362,17 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117730626</v>
+        <v>117730606</v>
       </c>
       <c r="B51" t="n">
-        <v>78564</v>
+        <v>79563</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6360,21 +6385,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>283</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6384,10 +6409,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447933</v>
+        <v>448072</v>
       </c>
       <c r="R51" t="n">
-        <v>7031939</v>
+        <v>7032136</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6419,7 +6444,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6429,7 +6454,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6449,17 +6474,17 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117730625</v>
+        <v>117730604</v>
       </c>
       <c r="B52" t="n">
-        <v>78480</v>
+        <v>79564</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6472,21 +6497,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6496,10 +6521,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447931</v>
+        <v>448069</v>
       </c>
       <c r="R52" t="n">
-        <v>7031941</v>
+        <v>7032132</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6531,7 +6556,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6541,7 +6566,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6568,10 +6593,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>117721068</v>
+        <v>117730586</v>
       </c>
       <c r="B53" t="n">
-        <v>77417</v>
+        <v>97742</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6580,41 +6605,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228579</v>
+        <v>220093</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Stångmyren (Stångmyren), Jmt</t>
+          <t>Småbodflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>448050</v>
+        <v>448008</v>
       </c>
       <c r="R53" t="n">
-        <v>7032167</v>
+        <v>7032180</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6643,7 +6668,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6653,7 +6678,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6664,51 +6689,26 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>117730648</v>
+        <v>117730601</v>
       </c>
       <c r="B54" t="n">
-        <v>104914</v>
+        <v>74406</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6721,21 +6721,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221725</v>
+        <v>6428</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6745,10 +6745,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447847</v>
+        <v>448071</v>
       </c>
       <c r="R54" t="n">
-        <v>7031902</v>
+        <v>7032132</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6790,7 +6790,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6810,17 +6810,17 @@
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118093428</v>
+        <v>117730599</v>
       </c>
       <c r="B55" t="n">
-        <v>101374</v>
+        <v>74589</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6829,41 +6829,44 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>22</v>
+        <v>310</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447988</v>
+        <v>448071</v>
       </c>
       <c r="R55" t="n">
-        <v>7032159</v>
+        <v>7032132</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6892,7 +6895,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6902,7 +6905,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6911,33 +6914,58 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>117730599</v>
+        <v>118093428</v>
       </c>
       <c r="B56" t="n">
-        <v>74589</v>
+        <v>101374</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6946,44 +6974,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>310</v>
+        <v>22</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Buser) C. G. Westerl.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>448071</v>
+        <v>447988</v>
       </c>
       <c r="R56" t="n">
-        <v>7032132</v>
+        <v>7032159</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7012,7 +7037,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7022,7 +7047,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7031,48 +7056,23 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
-      </c>
-      <c r="AS56" t="inlineStr">
-        <is>
-          <t>Fredrik Jonsson</t>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>

--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117730662</v>
+        <v>117730584</v>
       </c>
       <c r="B4" t="n">
-        <v>97859</v>
+        <v>97742</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>220093</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>Småbodflon Ö, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447993</v>
+        <v>448038</v>
       </c>
       <c r="R4" t="n">
-        <v>7032161</v>
+        <v>7032237</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117730666</v>
+        <v>117730618</v>
       </c>
       <c r="B5" t="n">
-        <v>90519</v>
+        <v>97742</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1028,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>220093</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447986</v>
+        <v>448064</v>
       </c>
       <c r="R5" t="n">
-        <v>7032193</v>
+        <v>7032071</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1121,17 +1121,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson</t>
+          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117730584</v>
+        <v>117730666</v>
       </c>
       <c r="B6" t="n">
-        <v>97742</v>
+        <v>90519</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,38 +1140,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220093</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Småbodflon Ö, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>448038</v>
+        <v>447986</v>
       </c>
       <c r="R6" t="n">
-        <v>7032237</v>
+        <v>7032193</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>07:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,17 +1233,17 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>117730618</v>
+        <v>117730662</v>
       </c>
       <c r="B7" t="n">
-        <v>97742</v>
+        <v>97859</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220093</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>448064</v>
+        <v>447993</v>
       </c>
       <c r="R7" t="n">
-        <v>7032071</v>
+        <v>7032161</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Johan Råghall, Matilda Pettersson, Fredrik Jonsson</t>
+          <t>Johan Råghall, Matilda Pettersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -6369,10 +6369,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>117730606</v>
+        <v>117730604</v>
       </c>
       <c r="B51" t="n">
-        <v>79563</v>
+        <v>79564</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6385,21 +6385,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6409,10 +6409,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>448072</v>
+        <v>448069</v>
       </c>
       <c r="R51" t="n">
-        <v>7032136</v>
+        <v>7032132</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6444,7 +6444,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6481,10 +6481,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>117730604</v>
+        <v>117730606</v>
       </c>
       <c r="B52" t="n">
-        <v>79564</v>
+        <v>79563</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6497,21 +6497,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>448069</v>
+        <v>448072</v>
       </c>
       <c r="R52" t="n">
-        <v>7032132</v>
+        <v>7032136</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6556,7 +6556,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD52" t="b">

--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7758,6 +7758,8503 @@
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>120398173</v>
+      </c>
+      <c r="B63" t="n">
+        <v>78626</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>283</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>447933</v>
+      </c>
+      <c r="R63" t="n">
+        <v>7031977</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>120398200</v>
+      </c>
+      <c r="B64" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>448113</v>
+      </c>
+      <c r="R64" t="n">
+        <v>7032192</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>120398176</v>
+      </c>
+      <c r="B65" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>447950</v>
+      </c>
+      <c r="R65" t="n">
+        <v>7031971</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>120398177</v>
+      </c>
+      <c r="B66" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>447950</v>
+      </c>
+      <c r="R66" t="n">
+        <v>7031971</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>på bark på stam av gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>120407779</v>
+      </c>
+      <c r="B67" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>448080</v>
+      </c>
+      <c r="R67" t="n">
+        <v>7032230</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>120407757</v>
+      </c>
+      <c r="B68" t="n">
+        <v>77479</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>447945</v>
+      </c>
+      <c r="R68" t="n">
+        <v>7031891</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>120410105</v>
+      </c>
+      <c r="B69" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>447912</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7031942</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Britta Sterner, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>120407780</v>
+      </c>
+      <c r="B70" t="n">
+        <v>101469</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>22</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Skarptandad daggkåpa</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Alchemilla oxyodonta</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>448079</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7032239</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>120398192</v>
+      </c>
+      <c r="B71" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>448084</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7032156</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>120410098</v>
+      </c>
+      <c r="B72" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>447938</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7031999</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Britta Sterner, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>120407776</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91512</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>448121</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7032208</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>120407763</v>
+      </c>
+      <c r="B74" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>447956</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7031963</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>120398202</v>
+      </c>
+      <c r="B75" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>448121</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7032229</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>120410100</v>
+      </c>
+      <c r="B76" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>447936</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7032074</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Britta Sterner, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>120407749</v>
+      </c>
+      <c r="B77" t="n">
+        <v>77479</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>447916</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7032098</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>120407766</v>
+      </c>
+      <c r="B78" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>448082</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7032097</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>120407751</v>
+      </c>
+      <c r="B79" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>447900</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7032092</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>120407768</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78626</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>283</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>448083</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7032095</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>120407772</v>
+      </c>
+      <c r="B81" t="n">
+        <v>78626</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>283</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>448093</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7032124</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>120407764</v>
+      </c>
+      <c r="B82" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>447980</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7031975</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>120398179</v>
+      </c>
+      <c r="B83" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>447981</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7031976</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>120398203</v>
+      </c>
+      <c r="B84" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>448121</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7032229</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>120398189</v>
+      </c>
+      <c r="B85" t="n">
+        <v>78626</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>283</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>448087</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7032124</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>På grenar på gammal undertryckt gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>120398171</v>
+      </c>
+      <c r="B86" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>447838</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7031933</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>på granlåga # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>120410104</v>
+      </c>
+      <c r="B87" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>447915</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7032086</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Britta Sterner, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>120410103</v>
+      </c>
+      <c r="B88" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>447924</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7032085</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Britta Sterner, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>120410101</v>
+      </c>
+      <c r="B89" t="n">
+        <v>94334</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>447936</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7032054</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Britta Sterner, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>120407774</v>
+      </c>
+      <c r="B90" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>448102</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7032163</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>120398178</v>
+      </c>
+      <c r="B91" t="n">
+        <v>77479</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>447950</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7031971</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>på bark på stam av gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>120407775</v>
+      </c>
+      <c r="B92" t="n">
+        <v>91512</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>448101</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7032166</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>120410090</v>
+      </c>
+      <c r="B93" t="n">
+        <v>105017</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>448077</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7032240</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Britta Sterner, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>120407747</v>
+      </c>
+      <c r="B94" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>447884</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7032094</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>120407781</v>
+      </c>
+      <c r="B95" t="n">
+        <v>77479</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>448064</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7032247</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>10:33</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>120398195</v>
+      </c>
+      <c r="B96" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>448076</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7032148</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>På död gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>120398196</v>
+      </c>
+      <c r="B97" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>448076</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7032148</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>På död gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>120398198</v>
+      </c>
+      <c r="B98" t="n">
+        <v>78626</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>283</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>448094</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7032145</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>120407741</v>
+      </c>
+      <c r="B99" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>447935</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7032200</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>120407746</v>
+      </c>
+      <c r="B100" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>447902</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7032164</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>120410099</v>
+      </c>
+      <c r="B101" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>447940</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7032074</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Britta Sterner, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>120410089</v>
+      </c>
+      <c r="B102" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>448084</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7032224</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Britta Sterner, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>120410102</v>
+      </c>
+      <c r="B103" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>447931</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7031818</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Britta Sterner, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>120398188</v>
+      </c>
+      <c r="B104" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>448087</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7032124</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>120407783</v>
+      </c>
+      <c r="B105" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>448072</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7032251</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>10:29</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>120407745</v>
+      </c>
+      <c r="B106" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>447909</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7032166</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>120398172</v>
+      </c>
+      <c r="B107" t="n">
+        <v>74652</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6486</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Skuggnål</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Chaenotheca sphaerocephala</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>447921</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7031952</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>Djup hålighet vid granbas # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>120398204</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79624</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>448111</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7032232</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>På död rönn # Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>120398194</v>
+      </c>
+      <c r="B109" t="n">
+        <v>77479</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>448084</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7032156</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>120398191</v>
+      </c>
+      <c r="B110" t="n">
+        <v>78626</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>283</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>448091</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7032130</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>På klen undertryckt gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>120407778</v>
+      </c>
+      <c r="B111" t="n">
+        <v>74638</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>6439</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Gulnål</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Chaenotheca brachypoda</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>448118</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7032220</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>120407748</v>
+      </c>
+      <c r="B112" t="n">
+        <v>82321</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>447916</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7032098</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>120407756</v>
+      </c>
+      <c r="B113" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>447945</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7031891</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>120407743</v>
+      </c>
+      <c r="B114" t="n">
+        <v>77479</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>447906</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7032176</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>120407777</v>
+      </c>
+      <c r="B115" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>448119</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7032212</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>120398180</v>
+      </c>
+      <c r="B116" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>447981</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7031976</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>120398201</v>
+      </c>
+      <c r="B117" t="n">
+        <v>105017</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>448113</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7032192</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>På marken</t>
+        </is>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>120398174</v>
+      </c>
+      <c r="B118" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>447933</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7031977</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>120407744</v>
+      </c>
+      <c r="B119" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>447906</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7032176</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>120407740</v>
+      </c>
+      <c r="B120" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>448010</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7032227</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120407762</v>
+      </c>
+      <c r="B121" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>447905</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7031937</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>120407750</v>
+      </c>
+      <c r="B122" t="n">
+        <v>74654</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>447916</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7032098</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>120398205</v>
+      </c>
+      <c r="B123" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>448111</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7032232</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>På död rönn # Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>120407753</v>
+      </c>
+      <c r="B124" t="n">
+        <v>74640</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>306</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Kornig nållav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Chaenotheca chlorella</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>447913</v>
+      </c>
+      <c r="R124" t="n">
+        <v>7031958</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>120410088</v>
+      </c>
+      <c r="B125" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>448098</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7032176</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Britta Sterner, Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>120407758</v>
+      </c>
+      <c r="B126" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>447946</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7031890</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>120407754</v>
+      </c>
+      <c r="B127" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>447910</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7031953</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>120407759</v>
+      </c>
+      <c r="B128" t="n">
+        <v>91512</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>447940</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7031893</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>120407752</v>
+      </c>
+      <c r="B129" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>447908</v>
+      </c>
+      <c r="R129" t="n">
+        <v>7032002</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>120398199</v>
+      </c>
+      <c r="B130" t="n">
+        <v>78626</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>283</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Kavernularia</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Hypogymnia hultenii</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>448099</v>
+      </c>
+      <c r="R130" t="n">
+        <v>7032188</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>120398190</v>
+      </c>
+      <c r="B131" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>448091</v>
+      </c>
+      <c r="R131" t="n">
+        <v>7032130</v>
+      </c>
+      <c r="S131" t="n">
+        <v>10</v>
+      </c>
+      <c r="T131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U131" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
+      <c r="AD131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG131" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT131" t="inlineStr"/>
+      <c r="AW131" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX131" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>120398193</v>
+      </c>
+      <c r="B132" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>448084</v>
+      </c>
+      <c r="R132" t="n">
+        <v>7032156</v>
+      </c>
+      <c r="S132" t="n">
+        <v>10</v>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U132" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG132" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT132" t="inlineStr"/>
+      <c r="AW132" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX132" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>120398181</v>
+      </c>
+      <c r="B133" t="n">
+        <v>77479</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>447981</v>
+      </c>
+      <c r="R133" t="n">
+        <v>7031976</v>
+      </c>
+      <c r="S133" t="n">
+        <v>10</v>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U133" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG133" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT133" t="inlineStr"/>
+      <c r="AW133" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson</t>
+        </is>
+      </c>
+      <c r="AX133" t="inlineStr">
+        <is>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>120407773</v>
+      </c>
+      <c r="B134" t="n">
+        <v>77479</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>448090</v>
+      </c>
+      <c r="R134" t="n">
+        <v>7032160</v>
+      </c>
+      <c r="S134" t="n">
+        <v>10</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>120407755</v>
+      </c>
+      <c r="B135" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Stångmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>447922</v>
+      </c>
+      <c r="R135" t="n">
+        <v>7031922</v>
+      </c>
+      <c r="S135" t="n">
+        <v>10</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Alsen</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Johan Råghall, Britta Sterner</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -10577,10 +10577,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120410104</v>
+        <v>120407774</v>
       </c>
       <c r="B87" t="n">
-        <v>74654</v>
+        <v>90580</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10593,21 +10593,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10617,10 +10617,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447915</v>
+        <v>448102</v>
       </c>
       <c r="R87" t="n">
-        <v>7032086</v>
+        <v>7032163</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10650,9 +10650,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10667,19 +10677,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120410103</v>
+        <v>120410104</v>
       </c>
       <c r="B88" t="n">
         <v>74654</v>
@@ -10719,10 +10729,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447924</v>
+        <v>447915</v>
       </c>
       <c r="R88" t="n">
-        <v>7032085</v>
+        <v>7032086</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10781,10 +10791,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120410101</v>
+        <v>120410103</v>
       </c>
       <c r="B89" t="n">
-        <v>94334</v>
+        <v>74654</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10793,25 +10803,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10821,10 +10831,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447936</v>
+        <v>447924</v>
       </c>
       <c r="R89" t="n">
-        <v>7032054</v>
+        <v>7032085</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10883,10 +10893,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120407774</v>
+        <v>120410101</v>
       </c>
       <c r="B90" t="n">
-        <v>90580</v>
+        <v>94334</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10895,25 +10905,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>2809</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10923,10 +10933,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>448102</v>
+        <v>447936</v>
       </c>
       <c r="R90" t="n">
-        <v>7032163</v>
+        <v>7032054</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10956,19 +10966,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>10:58</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10983,12 +10983,12 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -14718,10 +14718,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120398205</v>
+        <v>120410088</v>
       </c>
       <c r="B123" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14734,34 +14734,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>448111</v>
+        <v>448098</v>
       </c>
       <c r="R123" t="n">
-        <v>7032232</v>
+        <v>7032176</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14791,21 +14791,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD123" t="b">
         <v>0</v>
       </c>
@@ -14814,31 +14804,16 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>På död rönn # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
@@ -14957,10 +14932,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120410088</v>
+        <v>120398205</v>
       </c>
       <c r="B125" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14973,34 +14948,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>448098</v>
+        <v>448111</v>
       </c>
       <c r="R125" t="n">
-        <v>7032176</v>
+        <v>7032232</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15030,11 +15005,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA125" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD125" t="b">
         <v>0</v>
       </c>
@@ -15043,16 +15028,31 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>På död rönn # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>

--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -7760,10 +7760,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120398173</v>
+        <v>120410105</v>
       </c>
       <c r="B63" t="n">
-        <v>78626</v>
+        <v>90580</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7776,34 +7776,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447933</v>
+        <v>447912</v>
       </c>
       <c r="R63" t="n">
-        <v>7031977</v>
+        <v>7031942</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7833,21 +7833,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7856,38 +7846,23 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120398200</v>
+        <v>120398196</v>
       </c>
       <c r="B64" t="n">
         <v>78542</v>
@@ -7927,10 +7902,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>448113</v>
+        <v>448076</v>
       </c>
       <c r="R64" t="n">
-        <v>7032192</v>
+        <v>7032148</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7962,7 +7937,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7972,7 +7947,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7996,7 +7971,7 @@
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På död gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8014,7 +7989,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120398176</v>
+        <v>120398174</v>
       </c>
       <c r="B65" t="n">
         <v>78542</v>
@@ -8054,10 +8029,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>447950</v>
+        <v>447933</v>
       </c>
       <c r="R65" t="n">
-        <v>7031971</v>
+        <v>7031977</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8089,7 +8064,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8099,7 +8074,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8141,10 +8116,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120398177</v>
+        <v>120410089</v>
       </c>
       <c r="B66" t="n">
-        <v>74654</v>
+        <v>90580</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8157,34 +8132,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447950</v>
+        <v>448084</v>
       </c>
       <c r="R66" t="n">
-        <v>7031971</v>
+        <v>7032224</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8214,21 +8189,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>11:53</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8237,38 +8202,23 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120407779</v>
+        <v>120407740</v>
       </c>
       <c r="B67" t="n">
         <v>78542</v>
@@ -8308,10 +8258,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>448080</v>
+        <v>448010</v>
       </c>
       <c r="R67" t="n">
-        <v>7032230</v>
+        <v>7032227</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8343,7 +8293,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8353,7 +8303,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8373,17 +8323,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120407757</v>
+        <v>120407775</v>
       </c>
       <c r="B68" t="n">
-        <v>77479</v>
+        <v>91512</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8392,25 +8342,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228579</v>
+        <v>4769</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8420,10 +8370,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447945</v>
+        <v>448101</v>
       </c>
       <c r="R68" t="n">
-        <v>7031891</v>
+        <v>7032166</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8455,7 +8405,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8465,7 +8415,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8485,17 +8435,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120410105</v>
+        <v>120407743</v>
       </c>
       <c r="B69" t="n">
-        <v>90580</v>
+        <v>77479</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8508,21 +8458,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8532,10 +8482,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447912</v>
+        <v>447906</v>
       </c>
       <c r="R69" t="n">
-        <v>7031942</v>
+        <v>7032176</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8565,9 +8515,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8582,22 +8542,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120407780</v>
+        <v>120407773</v>
       </c>
       <c r="B70" t="n">
-        <v>101469</v>
+        <v>77479</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8606,25 +8566,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>22</v>
+        <v>228579</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8634,10 +8594,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>448079</v>
+        <v>448090</v>
       </c>
       <c r="R70" t="n">
-        <v>7032239</v>
+        <v>7032160</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8669,7 +8629,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8679,7 +8639,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8706,10 +8666,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120398192</v>
+        <v>120410090</v>
       </c>
       <c r="B71" t="n">
-        <v>74654</v>
+        <v>105017</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8718,38 +8678,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>448084</v>
+        <v>448077</v>
       </c>
       <c r="R71" t="n">
-        <v>7032156</v>
+        <v>7032240</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8779,21 +8739,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8802,41 +8752,26 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120410098</v>
+        <v>120398189</v>
       </c>
       <c r="B72" t="n">
-        <v>90580</v>
+        <v>78626</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8849,34 +8784,43 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>283</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447938</v>
+        <v>448087</v>
       </c>
       <c r="R72" t="n">
-        <v>7031999</v>
+        <v>7032124</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8906,11 +8850,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8919,26 +8873,41 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>På grenar på gammal undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120407776</v>
+        <v>120398191</v>
       </c>
       <c r="B73" t="n">
-        <v>91512</v>
+        <v>78626</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8947,38 +8916,47 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4769</v>
+        <v>283</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>448121</v>
+        <v>448091</v>
       </c>
       <c r="R73" t="n">
-        <v>7032208</v>
+        <v>7032130</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9010,7 +8988,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9020,7 +8998,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9031,23 +9009,38 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>På klen undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120407763</v>
+        <v>120398176</v>
       </c>
       <c r="B74" t="n">
         <v>78542</v>
@@ -9083,14 +9076,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>447956</v>
+        <v>447950</v>
       </c>
       <c r="R74" t="n">
-        <v>7031963</v>
+        <v>7031971</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9122,7 +9115,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9132,7 +9125,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9143,23 +9136,38 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120398202</v>
+        <v>120407779</v>
       </c>
       <c r="B75" t="n">
         <v>78542</v>
@@ -9195,14 +9203,14 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>448121</v>
+        <v>448080</v>
       </c>
       <c r="R75" t="n">
-        <v>7032229</v>
+        <v>7032230</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9234,7 +9242,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9244,7 +9252,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9255,38 +9263,23 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120410100</v>
+        <v>120407741</v>
       </c>
       <c r="B76" t="n">
         <v>90598</v>
@@ -9326,10 +9319,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447936</v>
+        <v>447935</v>
       </c>
       <c r="R76" t="n">
-        <v>7032074</v>
+        <v>7032200</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9359,9 +9352,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9376,22 +9379,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120407749</v>
+        <v>120407744</v>
       </c>
       <c r="B77" t="n">
-        <v>77479</v>
+        <v>74654</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9404,21 +9407,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9428,10 +9431,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447916</v>
+        <v>447906</v>
       </c>
       <c r="R77" t="n">
-        <v>7032098</v>
+        <v>7032176</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9463,7 +9466,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9473,7 +9476,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9500,10 +9503,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120407766</v>
+        <v>120398178</v>
       </c>
       <c r="B78" t="n">
-        <v>78542</v>
+        <v>77479</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9516,34 +9519,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>448082</v>
+        <v>447950</v>
       </c>
       <c r="R78" t="n">
-        <v>7032097</v>
+        <v>7031971</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9575,7 +9578,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9585,7 +9588,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9596,23 +9599,38 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>på bark på stam av gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120407751</v>
+        <v>120407755</v>
       </c>
       <c r="B79" t="n">
         <v>78542</v>
@@ -9652,10 +9670,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447900</v>
+        <v>447922</v>
       </c>
       <c r="R79" t="n">
-        <v>7032092</v>
+        <v>7031922</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9687,7 +9705,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9697,7 +9715,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9724,10 +9742,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120407768</v>
+        <v>120407748</v>
       </c>
       <c r="B80" t="n">
-        <v>78626</v>
+        <v>82321</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9740,21 +9758,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>283</v>
+        <v>1312</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9764,10 +9782,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>448083</v>
+        <v>447916</v>
       </c>
       <c r="R80" t="n">
-        <v>7032095</v>
+        <v>7032098</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9799,7 +9817,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9809,7 +9827,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9829,17 +9847,17 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120407772</v>
+        <v>120398192</v>
       </c>
       <c r="B81" t="n">
-        <v>78626</v>
+        <v>74654</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9852,34 +9870,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>448093</v>
+        <v>448084</v>
       </c>
       <c r="R81" t="n">
-        <v>7032124</v>
+        <v>7032156</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9911,7 +9929,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9921,7 +9939,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9932,26 +9950,41 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120407764</v>
+        <v>120398194</v>
       </c>
       <c r="B82" t="n">
-        <v>78542</v>
+        <v>77479</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9964,34 +9997,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>447980</v>
+        <v>448084</v>
       </c>
       <c r="R82" t="n">
-        <v>7031975</v>
+        <v>7032156</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10023,7 +10056,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10033,7 +10066,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10044,26 +10077,41 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120398179</v>
+        <v>120410101</v>
       </c>
       <c r="B83" t="n">
-        <v>74654</v>
+        <v>94334</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10072,38 +10120,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>2809</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447981</v>
+        <v>447936</v>
       </c>
       <c r="R83" t="n">
-        <v>7031976</v>
+        <v>7032054</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10133,21 +10181,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z83" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB83" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10156,38 +10194,23 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120398203</v>
+        <v>120410103</v>
       </c>
       <c r="B84" t="n">
         <v>74654</v>
@@ -10223,14 +10246,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>448121</v>
+        <v>447924</v>
       </c>
       <c r="R84" t="n">
-        <v>7032229</v>
+        <v>7032085</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10260,21 +10283,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10283,41 +10296,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120398189</v>
+        <v>120398195</v>
       </c>
       <c r="B85" t="n">
-        <v>78626</v>
+        <v>90598</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10330,43 +10328,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>283</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>448087</v>
+        <v>448076</v>
       </c>
       <c r="R85" t="n">
-        <v>7032124</v>
+        <v>7032148</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10398,7 +10387,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10408,7 +10397,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10432,7 +10421,7 @@
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>På grenar på gammal undertryckt gran # Picea abies</t>
+          <t>På död gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10450,10 +10439,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120398171</v>
+        <v>120398190</v>
       </c>
       <c r="B86" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10466,34 +10455,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447838</v>
+        <v>448091</v>
       </c>
       <c r="R86" t="n">
-        <v>7031933</v>
+        <v>7032130</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10525,7 +10514,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10535,7 +10524,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10559,7 +10548,7 @@
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>på granlåga # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10577,10 +10566,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120407774</v>
+        <v>120407783</v>
       </c>
       <c r="B87" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10593,21 +10582,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10617,10 +10606,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>448102</v>
+        <v>448072</v>
       </c>
       <c r="R87" t="n">
-        <v>7032163</v>
+        <v>7032251</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10652,7 +10641,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10662,7 +10651,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10689,10 +10678,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120410104</v>
+        <v>120407763</v>
       </c>
       <c r="B88" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10705,21 +10694,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10729,10 +10718,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447915</v>
+        <v>447956</v>
       </c>
       <c r="R88" t="n">
-        <v>7032086</v>
+        <v>7031963</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10762,9 +10751,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10779,22 +10778,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120410103</v>
+        <v>120407752</v>
       </c>
       <c r="B89" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10807,21 +10806,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10831,10 +10830,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447924</v>
+        <v>447908</v>
       </c>
       <c r="R89" t="n">
-        <v>7032085</v>
+        <v>7032002</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10864,9 +10863,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10881,22 +10890,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120410101</v>
+        <v>120398205</v>
       </c>
       <c r="B90" t="n">
-        <v>94334</v>
+        <v>79623</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10905,38 +10914,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2809</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447936</v>
+        <v>448111</v>
       </c>
       <c r="R90" t="n">
-        <v>7032054</v>
+        <v>7032232</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10966,11 +10975,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -10979,26 +10998,41 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>På död rönn # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120398178</v>
+        <v>120410088</v>
       </c>
       <c r="B91" t="n">
-        <v>77479</v>
+        <v>90580</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11011,34 +11045,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447950</v>
+        <v>448098</v>
       </c>
       <c r="R91" t="n">
-        <v>7031971</v>
+        <v>7032176</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11068,21 +11102,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -11091,41 +11115,26 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120407775</v>
+        <v>120398173</v>
       </c>
       <c r="B92" t="n">
-        <v>91512</v>
+        <v>78626</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11134,38 +11143,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4769</v>
+        <v>283</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>448101</v>
+        <v>447933</v>
       </c>
       <c r="R92" t="n">
-        <v>7032166</v>
+        <v>7031977</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11197,7 +11206,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11207,7 +11216,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11218,26 +11227,41 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120410090</v>
+        <v>120398172</v>
       </c>
       <c r="B93" t="n">
-        <v>105017</v>
+        <v>74652</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11246,38 +11270,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221725</v>
+        <v>6486</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>448077</v>
+        <v>447921</v>
       </c>
       <c r="R93" t="n">
-        <v>7032240</v>
+        <v>7031952</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11307,11 +11331,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -11320,26 +11354,41 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>Djup hålighet vid granbas # Picea abies</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120407747</v>
+        <v>120410100</v>
       </c>
       <c r="B94" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11352,21 +11401,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11376,10 +11425,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447884</v>
+        <v>447936</v>
       </c>
       <c r="R94" t="n">
-        <v>7032094</v>
+        <v>7032074</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11409,19 +11458,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11436,22 +11475,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120407781</v>
+        <v>120407758</v>
       </c>
       <c r="B95" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11464,21 +11503,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -11488,10 +11527,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>448064</v>
+        <v>447946</v>
       </c>
       <c r="R95" t="n">
-        <v>7032247</v>
+        <v>7031890</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11523,7 +11562,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11533,7 +11572,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11553,17 +11592,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120398195</v>
+        <v>120407749</v>
       </c>
       <c r="B96" t="n">
-        <v>90598</v>
+        <v>77479</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11576,34 +11615,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>448076</v>
+        <v>447916</v>
       </c>
       <c r="R96" t="n">
-        <v>7032148</v>
+        <v>7032098</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11635,7 +11674,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11645,7 +11684,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11656,41 +11695,26 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>På död gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120398196</v>
+        <v>120407774</v>
       </c>
       <c r="B97" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11703,34 +11727,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>448076</v>
+        <v>448102</v>
       </c>
       <c r="R97" t="n">
-        <v>7032148</v>
+        <v>7032163</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11762,7 +11786,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11772,7 +11796,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11783,41 +11807,26 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>På död gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120398198</v>
+        <v>120398177</v>
       </c>
       <c r="B98" t="n">
-        <v>78626</v>
+        <v>74654</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11830,34 +11839,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>448094</v>
+        <v>447950</v>
       </c>
       <c r="R98" t="n">
-        <v>7032145</v>
+        <v>7031971</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11889,7 +11898,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11899,7 +11908,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11923,7 +11932,7 @@
       </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11941,10 +11950,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120407741</v>
+        <v>120398171</v>
       </c>
       <c r="B99" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11957,34 +11966,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447935</v>
+        <v>447838</v>
       </c>
       <c r="R99" t="n">
-        <v>7032200</v>
+        <v>7031933</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12016,7 +12025,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12026,7 +12035,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12037,23 +12046,38 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>på granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120407746</v>
+        <v>120398200</v>
       </c>
       <c r="B100" t="n">
         <v>78542</v>
@@ -12089,14 +12113,14 @@
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447902</v>
+        <v>448113</v>
       </c>
       <c r="R100" t="n">
-        <v>7032164</v>
+        <v>7032192</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12128,7 +12152,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12138,7 +12162,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12149,26 +12173,41 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120410099</v>
+        <v>120407753</v>
       </c>
       <c r="B101" t="n">
-        <v>90598</v>
+        <v>74640</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12177,25 +12216,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12205,10 +12244,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447940</v>
+        <v>447913</v>
       </c>
       <c r="R101" t="n">
-        <v>7032074</v>
+        <v>7031958</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12238,9 +12277,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12255,22 +12304,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120410089</v>
+        <v>120407776</v>
       </c>
       <c r="B102" t="n">
-        <v>90580</v>
+        <v>91512</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12279,25 +12328,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12307,10 +12356,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>448084</v>
+        <v>448121</v>
       </c>
       <c r="R102" t="n">
-        <v>7032224</v>
+        <v>7032208</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12340,9 +12389,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12357,19 +12416,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120410102</v>
+        <v>120407745</v>
       </c>
       <c r="B103" t="n">
         <v>90598</v>
@@ -12409,10 +12468,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447931</v>
+        <v>447909</v>
       </c>
       <c r="R103" t="n">
-        <v>7031818</v>
+        <v>7032166</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12442,9 +12501,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12459,22 +12528,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120398188</v>
+        <v>120407781</v>
       </c>
       <c r="B104" t="n">
-        <v>78542</v>
+        <v>77479</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12487,34 +12556,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>448087</v>
+        <v>448064</v>
       </c>
       <c r="R104" t="n">
-        <v>7032124</v>
+        <v>7032247</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12546,7 +12615,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12556,7 +12625,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12567,38 +12636,23 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120407783</v>
+        <v>120407746</v>
       </c>
       <c r="B105" t="n">
         <v>78542</v>
@@ -12638,10 +12692,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>448072</v>
+        <v>447902</v>
       </c>
       <c r="R105" t="n">
-        <v>7032251</v>
+        <v>7032164</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12673,7 +12727,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12683,7 +12737,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12703,17 +12757,17 @@
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120407745</v>
+        <v>120398202</v>
       </c>
       <c r="B106" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12726,34 +12780,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>447909</v>
+        <v>448121</v>
       </c>
       <c r="R106" t="n">
-        <v>7032166</v>
+        <v>7032229</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12785,7 +12839,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12795,7 +12849,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12806,26 +12860,41 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120398172</v>
+        <v>120398193</v>
       </c>
       <c r="B107" t="n">
-        <v>74652</v>
+        <v>78542</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12834,38 +12903,38 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447921</v>
+        <v>448084</v>
       </c>
       <c r="R107" t="n">
-        <v>7031952</v>
+        <v>7032156</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12897,7 +12966,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12907,7 +12976,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12931,7 +13000,7 @@
       </c>
       <c r="AO107" t="inlineStr">
         <is>
-          <t>Djup hålighet vid granbas # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12949,10 +13018,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120398204</v>
+        <v>120398180</v>
       </c>
       <c r="B108" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12965,34 +13034,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>448111</v>
+        <v>447981</v>
       </c>
       <c r="R108" t="n">
-        <v>7032232</v>
+        <v>7031976</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13024,7 +13093,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13034,7 +13103,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13048,17 +13117,17 @@
       </c>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO108" t="inlineStr">
         <is>
-          <t>På död rönn # Sorbus aucuparia</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -13076,10 +13145,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120398194</v>
+        <v>120410098</v>
       </c>
       <c r="B109" t="n">
-        <v>77479</v>
+        <v>90580</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13092,34 +13161,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>448084</v>
+        <v>447938</v>
       </c>
       <c r="R109" t="n">
-        <v>7032156</v>
+        <v>7031999</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13149,21 +13218,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -13172,41 +13231,26 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120398191</v>
+        <v>120410104</v>
       </c>
       <c r="B110" t="n">
-        <v>78626</v>
+        <v>74654</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13219,43 +13263,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>448091</v>
+        <v>447915</v>
       </c>
       <c r="R110" t="n">
-        <v>7032130</v>
+        <v>7032086</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13285,21 +13320,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -13308,41 +13333,26 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>På klen undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120407778</v>
+        <v>120410102</v>
       </c>
       <c r="B111" t="n">
-        <v>74638</v>
+        <v>90598</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13351,25 +13361,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6439</v>
+        <v>5432</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -13379,10 +13389,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>448118</v>
+        <v>447931</v>
       </c>
       <c r="R111" t="n">
-        <v>7032220</v>
+        <v>7031818</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13412,19 +13422,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>10:45</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13439,22 +13439,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120407748</v>
+        <v>120407750</v>
       </c>
       <c r="B112" t="n">
-        <v>82321</v>
+        <v>74654</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13467,21 +13467,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13563,10 +13563,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120407756</v>
+        <v>120407754</v>
       </c>
       <c r="B113" t="n">
-        <v>74654</v>
+        <v>57320</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13579,34 +13579,43 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447945</v>
+        <v>447910</v>
       </c>
       <c r="R113" t="n">
-        <v>7031891</v>
+        <v>7031953</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13638,7 +13647,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13648,7 +13657,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13675,10 +13684,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120407743</v>
+        <v>120407756</v>
       </c>
       <c r="B114" t="n">
-        <v>77479</v>
+        <v>74654</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13691,21 +13700,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13715,10 +13724,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447906</v>
+        <v>447945</v>
       </c>
       <c r="R114" t="n">
-        <v>7032176</v>
+        <v>7031891</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13750,7 +13759,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13760,7 +13769,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13787,10 +13796,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120407777</v>
+        <v>120407772</v>
       </c>
       <c r="B115" t="n">
-        <v>78542</v>
+        <v>78626</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13803,21 +13812,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -13827,10 +13836,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>448119</v>
+        <v>448093</v>
       </c>
       <c r="R115" t="n">
-        <v>7032212</v>
+        <v>7032124</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13862,7 +13871,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13872,7 +13881,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13899,10 +13908,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120398180</v>
+        <v>120398181</v>
       </c>
       <c r="B116" t="n">
-        <v>78542</v>
+        <v>77479</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13915,21 +13924,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -14026,10 +14035,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120398201</v>
+        <v>120398188</v>
       </c>
       <c r="B117" t="n">
-        <v>105017</v>
+        <v>78542</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14038,25 +14047,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14066,10 +14075,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>448113</v>
+        <v>448087</v>
       </c>
       <c r="R117" t="n">
-        <v>7032192</v>
+        <v>7032124</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14101,7 +14110,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14111,7 +14120,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14123,9 +14132,19 @@
       <c r="AG117" t="b">
         <v>0</v>
       </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT117" t="inlineStr"/>
@@ -14143,7 +14162,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120398174</v>
+        <v>120407777</v>
       </c>
       <c r="B118" t="n">
         <v>78542</v>
@@ -14179,14 +14198,14 @@
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447933</v>
+        <v>448119</v>
       </c>
       <c r="R118" t="n">
-        <v>7031977</v>
+        <v>7032212</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14218,7 +14237,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -14228,7 +14247,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14239,41 +14258,26 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120407744</v>
+        <v>120407751</v>
       </c>
       <c r="B119" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14286,21 +14290,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -14310,10 +14314,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>447906</v>
+        <v>447900</v>
       </c>
       <c r="R119" t="n">
-        <v>7032176</v>
+        <v>7032092</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14345,7 +14349,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14355,7 +14359,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14382,10 +14386,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120407740</v>
+        <v>120398199</v>
       </c>
       <c r="B120" t="n">
-        <v>78542</v>
+        <v>78626</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14398,34 +14402,43 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>448010</v>
+        <v>448099</v>
       </c>
       <c r="R120" t="n">
-        <v>7032227</v>
+        <v>7032188</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14457,7 +14470,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14467,7 +14480,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14478,26 +14491,41 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120407762</v>
+        <v>120398204</v>
       </c>
       <c r="B121" t="n">
-        <v>90580</v>
+        <v>79624</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14510,34 +14538,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447905</v>
+        <v>448111</v>
       </c>
       <c r="R121" t="n">
-        <v>7031937</v>
+        <v>7032232</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14569,7 +14597,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14579,7 +14607,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14590,23 +14618,38 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>På död rönn # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120407750</v>
+        <v>120398203</v>
       </c>
       <c r="B122" t="n">
         <v>74654</v>
@@ -14642,14 +14685,14 @@
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447916</v>
+        <v>448121</v>
       </c>
       <c r="R122" t="n">
-        <v>7032098</v>
+        <v>7032229</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14681,7 +14724,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14691,7 +14734,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14702,26 +14745,41 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120410088</v>
+        <v>120407759</v>
       </c>
       <c r="B123" t="n">
-        <v>90580</v>
+        <v>91512</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14730,25 +14788,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14758,10 +14816,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>448098</v>
+        <v>447940</v>
       </c>
       <c r="R123" t="n">
-        <v>7032176</v>
+        <v>7031893</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14791,9 +14849,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14808,22 +14876,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120407753</v>
+        <v>120407762</v>
       </c>
       <c r="B124" t="n">
-        <v>74640</v>
+        <v>90580</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14832,25 +14900,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>306</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14860,10 +14928,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>447913</v>
+        <v>447905</v>
       </c>
       <c r="R124" t="n">
-        <v>7031958</v>
+        <v>7031937</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14895,7 +14963,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14905,7 +14973,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14925,17 +14993,17 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120398205</v>
+        <v>120398198</v>
       </c>
       <c r="B125" t="n">
-        <v>79623</v>
+        <v>78626</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14948,21 +15016,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6458</v>
+        <v>283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14972,10 +15040,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>448111</v>
+        <v>448094</v>
       </c>
       <c r="R125" t="n">
-        <v>7032232</v>
+        <v>7032145</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15007,7 +15075,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15017,7 +15085,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15031,17 +15099,17 @@
       </c>
       <c r="AJ125" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK125" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO125" t="inlineStr">
         <is>
-          <t>På död rönn # Sorbus aucuparia</t>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -15059,7 +15127,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120407758</v>
+        <v>120407766</v>
       </c>
       <c r="B126" t="n">
         <v>78542</v>
@@ -15099,10 +15167,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447946</v>
+        <v>448082</v>
       </c>
       <c r="R126" t="n">
-        <v>7031890</v>
+        <v>7032097</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15134,7 +15202,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15144,7 +15212,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15164,17 +15232,17 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120407754</v>
+        <v>120407780</v>
       </c>
       <c r="B127" t="n">
-        <v>57320</v>
+        <v>101469</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15183,47 +15251,38 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100109</v>
+        <v>22</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Buser) C. G. Westerl.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
           <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>447910</v>
+        <v>448079</v>
       </c>
       <c r="R127" t="n">
-        <v>7031953</v>
+        <v>7032239</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15255,7 +15314,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15265,7 +15324,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15285,17 +15344,17 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120407759</v>
+        <v>120407757</v>
       </c>
       <c r="B128" t="n">
-        <v>91512</v>
+        <v>77479</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15304,25 +15363,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4769</v>
+        <v>228579</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15332,10 +15391,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>447940</v>
+        <v>447945</v>
       </c>
       <c r="R128" t="n">
-        <v>7031893</v>
+        <v>7031891</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15367,7 +15426,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15377,7 +15436,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15404,10 +15463,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120407752</v>
+        <v>120407764</v>
       </c>
       <c r="B129" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15420,21 +15479,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15444,10 +15503,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>447908</v>
+        <v>447980</v>
       </c>
       <c r="R129" t="n">
-        <v>7032002</v>
+        <v>7031975</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15479,7 +15538,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15489,7 +15548,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15509,17 +15568,17 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120398199</v>
+        <v>120407778</v>
       </c>
       <c r="B130" t="n">
-        <v>78626</v>
+        <v>74638</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15528,47 +15587,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>283</v>
+        <v>6439</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>448099</v>
+        <v>448118</v>
       </c>
       <c r="R130" t="n">
-        <v>7032188</v>
+        <v>7032220</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15600,7 +15650,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15610,7 +15660,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15621,41 +15671,26 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120398190</v>
+        <v>120410099</v>
       </c>
       <c r="B131" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15668,34 +15703,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>448091</v>
+        <v>447940</v>
       </c>
       <c r="R131" t="n">
-        <v>7032130</v>
+        <v>7032074</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15725,21 +15760,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -15748,41 +15773,26 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120398193</v>
+        <v>120407768</v>
       </c>
       <c r="B132" t="n">
-        <v>78542</v>
+        <v>78626</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15795,34 +15805,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>448084</v>
+        <v>448083</v>
       </c>
       <c r="R132" t="n">
-        <v>7032156</v>
+        <v>7032095</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15854,7 +15864,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15864,7 +15874,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15875,41 +15885,26 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120398181</v>
+        <v>120407747</v>
       </c>
       <c r="B133" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15922,34 +15917,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>447981</v>
+        <v>447884</v>
       </c>
       <c r="R133" t="n">
-        <v>7031976</v>
+        <v>7032094</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15981,7 +15976,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15991,7 +15986,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16002,41 +15997,26 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120407773</v>
+        <v>120398179</v>
       </c>
       <c r="B134" t="n">
-        <v>77479</v>
+        <v>74654</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16049,34 +16029,34 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>448090</v>
+        <v>447981</v>
       </c>
       <c r="R134" t="n">
-        <v>7032160</v>
+        <v>7031976</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16108,7 +16088,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16118,7 +16098,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16129,26 +16109,41 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO134" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120407755</v>
+        <v>120398201</v>
       </c>
       <c r="B135" t="n">
-        <v>78542</v>
+        <v>105017</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16157,38 +16152,38 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>447922</v>
+        <v>448113</v>
       </c>
       <c r="R135" t="n">
-        <v>7031922</v>
+        <v>7032192</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16220,7 +16215,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16230,7 +16225,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16241,16 +16236,21 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
+      </c>
+      <c r="AO135" t="inlineStr">
+        <is>
+          <t>På marken</t>
+        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>

--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -14386,10 +14386,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120398199</v>
+        <v>120407759</v>
       </c>
       <c r="B120" t="n">
-        <v>78626</v>
+        <v>91512</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14398,47 +14398,38 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>448099</v>
+        <v>447940</v>
       </c>
       <c r="R120" t="n">
-        <v>7032188</v>
+        <v>7031893</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14470,7 +14461,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14480,7 +14471,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14491,41 +14482,26 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ120" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK120" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120398204</v>
+        <v>120407762</v>
       </c>
       <c r="B121" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14538,34 +14514,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>448111</v>
+        <v>447905</v>
       </c>
       <c r="R121" t="n">
-        <v>7032232</v>
+        <v>7031937</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14597,7 +14573,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14607,7 +14583,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14618,41 +14594,26 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>På död rönn # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120398203</v>
+        <v>120398199</v>
       </c>
       <c r="B122" t="n">
-        <v>74654</v>
+        <v>78626</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14665,34 +14626,43 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>448121</v>
+        <v>448099</v>
       </c>
       <c r="R122" t="n">
-        <v>7032229</v>
+        <v>7032188</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14724,7 +14694,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14734,7 +14704,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14758,7 +14728,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14776,10 +14746,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120407759</v>
+        <v>120398204</v>
       </c>
       <c r="B123" t="n">
-        <v>91512</v>
+        <v>79624</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14788,38 +14758,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4769</v>
+        <v>2081</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447940</v>
+        <v>448111</v>
       </c>
       <c r="R123" t="n">
-        <v>7031893</v>
+        <v>7032232</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14851,7 +14821,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14861,7 +14831,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14872,26 +14842,41 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO123" t="inlineStr">
+        <is>
+          <t>På död rönn # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120407762</v>
+        <v>120398203</v>
       </c>
       <c r="B124" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14904,34 +14889,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>447905</v>
+        <v>448121</v>
       </c>
       <c r="R124" t="n">
-        <v>7031937</v>
+        <v>7032229</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14963,7 +14948,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14973,7 +14958,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14984,16 +14969,31 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -7760,10 +7760,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120410105</v>
+        <v>120398192</v>
       </c>
       <c r="B63" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7776,34 +7776,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447912</v>
+        <v>448084</v>
       </c>
       <c r="R63" t="n">
-        <v>7031942</v>
+        <v>7032156</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7833,11 +7833,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7846,26 +7856,41 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120398196</v>
+        <v>120410090</v>
       </c>
       <c r="B64" t="n">
-        <v>78542</v>
+        <v>105017</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7874,38 +7899,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>448076</v>
+        <v>448077</v>
       </c>
       <c r="R64" t="n">
-        <v>7032148</v>
+        <v>7032240</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7935,21 +7960,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7958,41 +7973,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>På död gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120398174</v>
+        <v>120407781</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
+        <v>77479</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8005,34 +8005,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>447933</v>
+        <v>448064</v>
       </c>
       <c r="R65" t="n">
-        <v>7031977</v>
+        <v>7032247</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8064,7 +8064,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8085,41 +8085,26 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120410089</v>
+        <v>120398178</v>
       </c>
       <c r="B66" t="n">
-        <v>90580</v>
+        <v>77479</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8132,34 +8117,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>448084</v>
+        <v>447950</v>
       </c>
       <c r="R66" t="n">
-        <v>7032224</v>
+        <v>7031971</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8189,11 +8174,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8202,23 +8197,38 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>på bark på stam av gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120407740</v>
+        <v>120407758</v>
       </c>
       <c r="B67" t="n">
         <v>78542</v>
@@ -8258,10 +8268,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>448010</v>
+        <v>447946</v>
       </c>
       <c r="R67" t="n">
-        <v>7032227</v>
+        <v>7031890</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8293,7 +8303,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8303,7 +8313,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8330,10 +8340,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120407775</v>
+        <v>120407764</v>
       </c>
       <c r="B68" t="n">
-        <v>91512</v>
+        <v>78542</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8342,25 +8352,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8370,10 +8380,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>448101</v>
+        <v>447980</v>
       </c>
       <c r="R68" t="n">
-        <v>7032166</v>
+        <v>7031975</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8405,7 +8415,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8415,7 +8425,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8442,10 +8452,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120407743</v>
+        <v>120398180</v>
       </c>
       <c r="B69" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8458,34 +8468,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447906</v>
+        <v>447981</v>
       </c>
       <c r="R69" t="n">
-        <v>7032176</v>
+        <v>7031976</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8517,7 +8527,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8527,7 +8537,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8538,26 +8548,41 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120407773</v>
+        <v>120410088</v>
       </c>
       <c r="B70" t="n">
-        <v>77479</v>
+        <v>90580</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8570,21 +8595,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8594,10 +8619,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>448090</v>
+        <v>448098</v>
       </c>
       <c r="R70" t="n">
-        <v>7032160</v>
+        <v>7032176</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8627,19 +8652,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>11:11</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>11:11</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8654,22 +8669,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120410090</v>
+        <v>120410101</v>
       </c>
       <c r="B71" t="n">
-        <v>105017</v>
+        <v>94334</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8682,21 +8697,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8706,10 +8721,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>448077</v>
+        <v>447936</v>
       </c>
       <c r="R71" t="n">
-        <v>7032240</v>
+        <v>7032054</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8768,10 +8783,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120398189</v>
+        <v>120398204</v>
       </c>
       <c r="B72" t="n">
-        <v>78626</v>
+        <v>79624</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8784,43 +8799,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>283</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>448087</v>
+        <v>448111</v>
       </c>
       <c r="R72" t="n">
-        <v>7032124</v>
+        <v>7032232</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8852,7 +8858,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8862,7 +8868,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8876,17 +8882,17 @@
       </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>På grenar på gammal undertryckt gran # Picea abies</t>
+          <t>På död rönn # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8897,17 +8903,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120398191</v>
+        <v>120407756</v>
       </c>
       <c r="B73" t="n">
-        <v>78626</v>
+        <v>74654</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8920,43 +8926,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>448091</v>
+        <v>447945</v>
       </c>
       <c r="R73" t="n">
-        <v>7032130</v>
+        <v>7031891</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8988,7 +8985,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8998,7 +8995,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9009,38 +9006,23 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>På klen undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120398176</v>
+        <v>120398193</v>
       </c>
       <c r="B74" t="n">
         <v>78542</v>
@@ -9076,14 +9058,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>447950</v>
+        <v>448084</v>
       </c>
       <c r="R74" t="n">
-        <v>7031971</v>
+        <v>7032156</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9115,7 +9097,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9125,7 +9107,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9160,14 +9142,14 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120407779</v>
+        <v>120407740</v>
       </c>
       <c r="B75" t="n">
         <v>78542</v>
@@ -9207,10 +9189,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>448080</v>
+        <v>448010</v>
       </c>
       <c r="R75" t="n">
-        <v>7032230</v>
+        <v>7032227</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9242,7 +9224,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9252,7 +9234,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9272,17 +9254,17 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120407741</v>
+        <v>120407783</v>
       </c>
       <c r="B76" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9295,21 +9277,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9319,10 +9301,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447935</v>
+        <v>448072</v>
       </c>
       <c r="R76" t="n">
-        <v>7032200</v>
+        <v>7032251</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9354,7 +9336,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9364,7 +9346,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9384,17 +9366,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120407744</v>
+        <v>120410102</v>
       </c>
       <c r="B77" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9407,21 +9389,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9431,10 +9413,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447906</v>
+        <v>447931</v>
       </c>
       <c r="R77" t="n">
-        <v>7032176</v>
+        <v>7031818</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9464,19 +9446,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>14:26</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9491,22 +9463,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120398178</v>
+        <v>120407772</v>
       </c>
       <c r="B78" t="n">
-        <v>77479</v>
+        <v>78626</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9519,34 +9491,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228579</v>
+        <v>283</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447950</v>
+        <v>448093</v>
       </c>
       <c r="R78" t="n">
-        <v>7031971</v>
+        <v>7032124</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9578,7 +9550,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9588,7 +9560,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9599,38 +9571,23 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120407755</v>
+        <v>120398200</v>
       </c>
       <c r="B79" t="n">
         <v>78542</v>
@@ -9666,14 +9623,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447922</v>
+        <v>448113</v>
       </c>
       <c r="R79" t="n">
-        <v>7031922</v>
+        <v>7032192</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9705,7 +9662,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9715,7 +9672,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9726,26 +9683,41 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120407748</v>
+        <v>120398175</v>
       </c>
       <c r="B80" t="n">
-        <v>82321</v>
+        <v>78626</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9758,34 +9730,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1312</v>
+        <v>283</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447916</v>
+        <v>447933</v>
       </c>
       <c r="R80" t="n">
-        <v>7032098</v>
+        <v>7031977</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9817,7 +9789,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9827,7 +9799,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9838,26 +9810,41 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120398192</v>
+        <v>120407751</v>
       </c>
       <c r="B81" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9870,34 +9857,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>448084</v>
+        <v>447900</v>
       </c>
       <c r="R81" t="n">
-        <v>7032156</v>
+        <v>7032092</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9929,7 +9916,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9939,7 +9926,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9950,41 +9937,26 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120398194</v>
+        <v>120398174</v>
       </c>
       <c r="B82" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9997,34 +9969,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>448084</v>
+        <v>447933</v>
       </c>
       <c r="R82" t="n">
-        <v>7032156</v>
+        <v>7031977</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10056,7 +10028,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10066,7 +10038,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10108,10 +10080,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120410101</v>
+        <v>120398177</v>
       </c>
       <c r="B83" t="n">
-        <v>94334</v>
+        <v>74654</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10120,38 +10092,38 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447936</v>
+        <v>447950</v>
       </c>
       <c r="R83" t="n">
-        <v>7032054</v>
+        <v>7031971</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10181,11 +10153,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10194,26 +10176,41 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>på bark på stam av gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120410103</v>
+        <v>120398202</v>
       </c>
       <c r="B84" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10226,34 +10223,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447924</v>
+        <v>448121</v>
       </c>
       <c r="R84" t="n">
-        <v>7032085</v>
+        <v>7032229</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10283,11 +10280,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10296,26 +10303,41 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120398195</v>
+        <v>120398198</v>
       </c>
       <c r="B85" t="n">
-        <v>90598</v>
+        <v>78626</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10328,21 +10350,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10352,10 +10374,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>448076</v>
+        <v>448094</v>
       </c>
       <c r="R85" t="n">
-        <v>7032148</v>
+        <v>7032145</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10387,7 +10409,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10397,7 +10419,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10421,7 +10443,7 @@
       </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>På död gammal gran # Picea abies</t>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -10432,17 +10454,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120398190</v>
+        <v>120398205</v>
       </c>
       <c r="B86" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10455,21 +10477,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10479,10 +10501,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>448091</v>
+        <v>448111</v>
       </c>
       <c r="R86" t="n">
-        <v>7032130</v>
+        <v>7032232</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10514,7 +10536,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10524,7 +10546,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10538,17 +10560,17 @@
       </c>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK86" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>På död rönn # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -10559,17 +10581,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120407783</v>
+        <v>120410100</v>
       </c>
       <c r="B87" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10582,21 +10604,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10606,10 +10628,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>448072</v>
+        <v>447936</v>
       </c>
       <c r="R87" t="n">
-        <v>7032251</v>
+        <v>7032074</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10639,19 +10661,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>10:29</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10666,22 +10678,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120407763</v>
+        <v>120407754</v>
       </c>
       <c r="B88" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10694,34 +10706,43 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447956</v>
+        <v>447910</v>
       </c>
       <c r="R88" t="n">
-        <v>7031963</v>
+        <v>7031953</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10753,7 +10774,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10763,7 +10784,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10783,17 +10804,17 @@
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120407752</v>
+        <v>120407750</v>
       </c>
       <c r="B89" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10806,21 +10827,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10830,10 +10851,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447908</v>
+        <v>447916</v>
       </c>
       <c r="R89" t="n">
-        <v>7032002</v>
+        <v>7032098</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10865,7 +10886,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10875,7 +10896,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10902,10 +10923,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120398205</v>
+        <v>120407747</v>
       </c>
       <c r="B90" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10918,34 +10939,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>448111</v>
+        <v>447884</v>
       </c>
       <c r="R90" t="n">
-        <v>7032232</v>
+        <v>7032094</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10977,7 +10998,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10987,7 +11008,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10998,41 +11019,26 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>På död rönn # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120410088</v>
+        <v>120398196</v>
       </c>
       <c r="B91" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11045,34 +11051,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>448098</v>
+        <v>448076</v>
       </c>
       <c r="R91" t="n">
-        <v>7032176</v>
+        <v>7032148</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11102,11 +11108,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -11115,26 +11131,41 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>På död gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120398173</v>
+        <v>120398195</v>
       </c>
       <c r="B92" t="n">
-        <v>78626</v>
+        <v>90598</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11147,34 +11178,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>283</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447933</v>
+        <v>448076</v>
       </c>
       <c r="R92" t="n">
-        <v>7031977</v>
+        <v>7032148</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11206,7 +11237,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11216,7 +11247,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11240,7 +11271,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+          <t>På död gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11251,17 +11282,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120398172</v>
+        <v>120407775</v>
       </c>
       <c r="B93" t="n">
-        <v>74652</v>
+        <v>91512</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11270,38 +11301,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6486</v>
+        <v>4769</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447921</v>
+        <v>448101</v>
       </c>
       <c r="R93" t="n">
-        <v>7031952</v>
+        <v>7032166</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11333,7 +11364,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11343,7 +11374,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11354,41 +11385,26 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Djup hålighet vid granbas # Picea abies</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120410100</v>
+        <v>120407768</v>
       </c>
       <c r="B94" t="n">
-        <v>90598</v>
+        <v>78626</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11401,21 +11417,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -11425,10 +11441,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447936</v>
+        <v>448083</v>
       </c>
       <c r="R94" t="n">
-        <v>7032074</v>
+        <v>7032095</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11458,9 +11474,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11475,19 +11501,19 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120407758</v>
+        <v>120407763</v>
       </c>
       <c r="B95" t="n">
         <v>78542</v>
@@ -11527,10 +11553,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447946</v>
+        <v>447956</v>
       </c>
       <c r="R95" t="n">
-        <v>7031890</v>
+        <v>7031963</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11562,7 +11588,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11572,7 +11598,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11592,17 +11618,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120407749</v>
+        <v>120407752</v>
       </c>
       <c r="B96" t="n">
-        <v>77479</v>
+        <v>90598</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11615,21 +11641,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228579</v>
+        <v>5432</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11639,10 +11665,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447916</v>
+        <v>447908</v>
       </c>
       <c r="R96" t="n">
-        <v>7032098</v>
+        <v>7032002</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11674,7 +11700,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11684,7 +11710,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11823,7 +11849,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120398177</v>
+        <v>120407744</v>
       </c>
       <c r="B98" t="n">
         <v>74654</v>
@@ -11859,14 +11885,14 @@
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447950</v>
+        <v>447906</v>
       </c>
       <c r="R98" t="n">
-        <v>7031971</v>
+        <v>7032176</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11898,7 +11924,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11908,7 +11934,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11919,41 +11945,26 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120398171</v>
+        <v>120407749</v>
       </c>
       <c r="B99" t="n">
-        <v>90580</v>
+        <v>77479</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11966,34 +11977,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447838</v>
+        <v>447916</v>
       </c>
       <c r="R99" t="n">
-        <v>7031933</v>
+        <v>7032098</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12025,7 +12036,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12035,7 +12046,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12046,41 +12057,26 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>på granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120398200</v>
+        <v>120398194</v>
       </c>
       <c r="B100" t="n">
-        <v>78542</v>
+        <v>77479</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12093,21 +12089,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12117,10 +12113,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>448113</v>
+        <v>448084</v>
       </c>
       <c r="R100" t="n">
-        <v>7032192</v>
+        <v>7032156</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12152,7 +12148,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12162,7 +12158,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12186,7 +12182,7 @@
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -12197,17 +12193,17 @@
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120407753</v>
+        <v>120398188</v>
       </c>
       <c r="B101" t="n">
-        <v>74640</v>
+        <v>78542</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12216,38 +12212,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447913</v>
+        <v>448087</v>
       </c>
       <c r="R101" t="n">
-        <v>7031958</v>
+        <v>7032124</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12279,7 +12275,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12289,7 +12285,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12300,26 +12296,41 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120407776</v>
+        <v>120410103</v>
       </c>
       <c r="B102" t="n">
-        <v>91512</v>
+        <v>74654</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12328,25 +12339,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12356,10 +12367,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>448121</v>
+        <v>447924</v>
       </c>
       <c r="R102" t="n">
-        <v>7032208</v>
+        <v>7032085</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12389,19 +12400,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>10:49</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12416,22 +12417,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120407745</v>
+        <v>120398171</v>
       </c>
       <c r="B103" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12444,34 +12445,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447909</v>
+        <v>447838</v>
       </c>
       <c r="R103" t="n">
-        <v>7032166</v>
+        <v>7031933</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12503,7 +12504,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12513,7 +12514,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12524,26 +12525,41 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>på granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120407781</v>
+        <v>120407779</v>
       </c>
       <c r="B104" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12556,21 +12572,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12580,10 +12596,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>448064</v>
+        <v>448080</v>
       </c>
       <c r="R104" t="n">
-        <v>7032247</v>
+        <v>7032230</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12615,7 +12631,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12625,7 +12641,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12652,10 +12668,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120407746</v>
+        <v>120410105</v>
       </c>
       <c r="B105" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12668,21 +12684,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12692,10 +12708,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447902</v>
+        <v>447912</v>
       </c>
       <c r="R105" t="n">
-        <v>7032164</v>
+        <v>7031942</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12725,19 +12741,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>14:22</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12752,22 +12758,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120398202</v>
+        <v>120410089</v>
       </c>
       <c r="B106" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12780,34 +12786,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>448121</v>
+        <v>448084</v>
       </c>
       <c r="R106" t="n">
-        <v>7032229</v>
+        <v>7032224</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12837,21 +12843,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -12860,41 +12856,26 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120398193</v>
+        <v>120410098</v>
       </c>
       <c r="B107" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12907,34 +12888,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>448084</v>
+        <v>447938</v>
       </c>
       <c r="R107" t="n">
-        <v>7032156</v>
+        <v>7031999</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12964,21 +12945,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12987,41 +12958,26 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120398180</v>
+        <v>120407778</v>
       </c>
       <c r="B108" t="n">
-        <v>78542</v>
+        <v>74638</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -13030,38 +12986,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447981</v>
+        <v>448118</v>
       </c>
       <c r="R108" t="n">
-        <v>7031976</v>
+        <v>7032220</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13093,7 +13049,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13103,7 +13059,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13114,41 +13070,26 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ108" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK108" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120410098</v>
+        <v>120398203</v>
       </c>
       <c r="B109" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13161,34 +13102,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>447938</v>
+        <v>448121</v>
       </c>
       <c r="R109" t="n">
-        <v>7031999</v>
+        <v>7032229</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13218,11 +13159,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -13231,26 +13182,41 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120410104</v>
+        <v>120407741</v>
       </c>
       <c r="B110" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13263,21 +13229,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13287,10 +13253,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447915</v>
+        <v>447935</v>
       </c>
       <c r="R110" t="n">
-        <v>7032086</v>
+        <v>7032200</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13320,9 +13286,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13337,22 +13313,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120410102</v>
+        <v>120398176</v>
       </c>
       <c r="B111" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13365,34 +13341,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447931</v>
+        <v>447950</v>
       </c>
       <c r="R111" t="n">
-        <v>7031818</v>
+        <v>7031971</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13422,11 +13398,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
@@ -13435,26 +13421,41 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120407750</v>
+        <v>120407759</v>
       </c>
       <c r="B112" t="n">
-        <v>74654</v>
+        <v>91512</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13463,25 +13464,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13491,10 +13492,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447916</v>
+        <v>447940</v>
       </c>
       <c r="R112" t="n">
-        <v>7032098</v>
+        <v>7031893</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13526,7 +13527,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13536,7 +13537,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13563,10 +13564,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120407754</v>
+        <v>120407755</v>
       </c>
       <c r="B113" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13579,43 +13580,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447910</v>
+        <v>447922</v>
       </c>
       <c r="R113" t="n">
-        <v>7031953</v>
+        <v>7031922</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13647,7 +13639,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13657,7 +13649,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13684,10 +13676,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120407756</v>
+        <v>120407746</v>
       </c>
       <c r="B114" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13700,21 +13692,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -13724,10 +13716,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447945</v>
+        <v>447902</v>
       </c>
       <c r="R114" t="n">
-        <v>7031891</v>
+        <v>7032164</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13759,7 +13751,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13769,7 +13761,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13796,10 +13788,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120407772</v>
+        <v>120398201</v>
       </c>
       <c r="B115" t="n">
-        <v>78626</v>
+        <v>105017</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13808,38 +13800,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>283</v>
+        <v>221725</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>448093</v>
+        <v>448113</v>
       </c>
       <c r="R115" t="n">
-        <v>7032124</v>
+        <v>7032192</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13871,7 +13863,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13881,7 +13873,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13892,16 +13884,21 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
+      </c>
+      <c r="AO115" t="inlineStr">
+        <is>
+          <t>På marken</t>
+        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
@@ -14028,17 +14025,17 @@
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Jana Novak, Fredrik Jonsson, Ulrika Nordin, Britta Sterner</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120398188</v>
+        <v>120407753</v>
       </c>
       <c r="B117" t="n">
-        <v>78542</v>
+        <v>74640</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14047,38 +14044,38 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>448087</v>
+        <v>447913</v>
       </c>
       <c r="R117" t="n">
-        <v>7032124</v>
+        <v>7031958</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14110,7 +14107,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14120,7 +14117,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14131,41 +14128,26 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120407777</v>
+        <v>120410099</v>
       </c>
       <c r="B118" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14178,21 +14160,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14202,10 +14184,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>448119</v>
+        <v>447940</v>
       </c>
       <c r="R118" t="n">
-        <v>7032212</v>
+        <v>7032074</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14235,19 +14217,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>10:48</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14262,22 +14234,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120407751</v>
+        <v>120398172</v>
       </c>
       <c r="B119" t="n">
-        <v>78542</v>
+        <v>74652</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14286,38 +14258,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>447900</v>
+        <v>447921</v>
       </c>
       <c r="R119" t="n">
-        <v>7032092</v>
+        <v>7031952</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14349,7 +14321,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14359,7 +14331,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14370,26 +14342,41 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO119" t="inlineStr">
+        <is>
+          <t>Djup hålighet vid granbas # Picea abies</t>
+        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120407759</v>
+        <v>120407748</v>
       </c>
       <c r="B120" t="n">
-        <v>91512</v>
+        <v>82321</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14398,25 +14385,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4769</v>
+        <v>1312</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -14426,10 +14413,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447940</v>
+        <v>447916</v>
       </c>
       <c r="R120" t="n">
-        <v>7031893</v>
+        <v>7032098</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14461,7 +14448,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14471,7 +14458,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14498,10 +14485,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120407762</v>
+        <v>120407766</v>
       </c>
       <c r="B121" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14514,21 +14501,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -14538,10 +14525,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447905</v>
+        <v>448082</v>
       </c>
       <c r="R121" t="n">
-        <v>7031937</v>
+        <v>7032097</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14573,7 +14560,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14583,7 +14570,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14610,7 +14597,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120398199</v>
+        <v>120398191</v>
       </c>
       <c r="B122" t="n">
         <v>78626</v>
@@ -14645,7 +14632,7 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -14659,10 +14646,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>448099</v>
+        <v>448091</v>
       </c>
       <c r="R122" t="n">
-        <v>7032188</v>
+        <v>7032130</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14694,7 +14681,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14704,7 +14691,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14728,7 +14715,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+          <t>På klen undertryckt gran # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14739,17 +14726,17 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120398204</v>
+        <v>120407780</v>
       </c>
       <c r="B123" t="n">
-        <v>79624</v>
+        <v>101469</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14758,38 +14745,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2081</v>
+        <v>22</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Buser) C. G. Westerl.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>448111</v>
+        <v>448079</v>
       </c>
       <c r="R123" t="n">
-        <v>7032232</v>
+        <v>7032239</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14821,7 +14808,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14831,7 +14818,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14842,41 +14829,26 @@
       </c>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ123" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK123" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>På död rönn # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120398203</v>
+        <v>120407762</v>
       </c>
       <c r="B124" t="n">
-        <v>74654</v>
+        <v>90580</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14889,34 +14861,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>448121</v>
+        <v>447905</v>
       </c>
       <c r="R124" t="n">
-        <v>7032229</v>
+        <v>7031937</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14948,7 +14920,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14958,7 +14930,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14969,38 +14941,23 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120398198</v>
+        <v>120398199</v>
       </c>
       <c r="B125" t="n">
         <v>78626</v>
@@ -15033,17 +14990,26 @@
           <t>(Degel.) Krog</t>
         </is>
       </c>
-      <c r="I125" t="inlineStr"/>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
           <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>448094</v>
+        <v>448099</v>
       </c>
       <c r="R125" t="n">
-        <v>7032145</v>
+        <v>7032188</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15075,7 +15041,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15085,7 +15051,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15120,17 +15086,17 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120407766</v>
+        <v>120398189</v>
       </c>
       <c r="B126" t="n">
-        <v>78542</v>
+        <v>78626</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15143,34 +15109,43 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>448082</v>
+        <v>448087</v>
       </c>
       <c r="R126" t="n">
-        <v>7032097</v>
+        <v>7032124</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15202,7 +15177,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15212,7 +15187,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15223,26 +15198,41 @@
       </c>
       <c r="AG126" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>På grenar på gammal undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120407780</v>
+        <v>120398179</v>
       </c>
       <c r="B127" t="n">
-        <v>101469</v>
+        <v>74654</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15251,38 +15241,38 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>22</v>
+        <v>6440</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>448079</v>
+        <v>447981</v>
       </c>
       <c r="R127" t="n">
-        <v>7032239</v>
+        <v>7031976</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15314,7 +15304,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15324,7 +15314,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15335,23 +15325,38 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120407757</v>
+        <v>120407743</v>
       </c>
       <c r="B128" t="n">
         <v>77479</v>
@@ -15391,10 +15396,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>447945</v>
+        <v>447906</v>
       </c>
       <c r="R128" t="n">
-        <v>7031891</v>
+        <v>7032176</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15426,7 +15431,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15436,7 +15441,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15463,10 +15468,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120407764</v>
+        <v>120410104</v>
       </c>
       <c r="B129" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15479,21 +15484,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15503,10 +15508,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>447980</v>
+        <v>447915</v>
       </c>
       <c r="R129" t="n">
-        <v>7031975</v>
+        <v>7032086</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15536,19 +15541,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z129" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB129" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15563,22 +15558,22 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120407778</v>
+        <v>120407777</v>
       </c>
       <c r="B130" t="n">
-        <v>74638</v>
+        <v>78542</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15587,25 +15582,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15615,10 +15610,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>448118</v>
+        <v>448119</v>
       </c>
       <c r="R130" t="n">
-        <v>7032220</v>
+        <v>7032212</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15650,7 +15645,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15660,7 +15655,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15687,10 +15682,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120410099</v>
+        <v>120407757</v>
       </c>
       <c r="B131" t="n">
-        <v>90598</v>
+        <v>77479</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15703,21 +15698,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15727,10 +15722,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>447940</v>
+        <v>447945</v>
       </c>
       <c r="R131" t="n">
-        <v>7032074</v>
+        <v>7031891</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15760,9 +15755,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15777,22 +15782,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120407768</v>
+        <v>120407773</v>
       </c>
       <c r="B132" t="n">
-        <v>78626</v>
+        <v>77479</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15805,21 +15810,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15829,10 +15834,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>448083</v>
+        <v>448090</v>
       </c>
       <c r="R132" t="n">
-        <v>7032095</v>
+        <v>7032160</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15864,7 +15869,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15874,7 +15879,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15901,10 +15906,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120407747</v>
+        <v>120407745</v>
       </c>
       <c r="B133" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15917,21 +15922,21 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15941,10 +15946,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>447884</v>
+        <v>447909</v>
       </c>
       <c r="R133" t="n">
-        <v>7032094</v>
+        <v>7032166</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15976,7 +15981,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -15986,7 +15991,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16013,10 +16018,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120398179</v>
+        <v>120407776</v>
       </c>
       <c r="B134" t="n">
-        <v>74654</v>
+        <v>91512</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16025,38 +16030,38 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>447981</v>
+        <v>448121</v>
       </c>
       <c r="R134" t="n">
-        <v>7031976</v>
+        <v>7032208</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16088,7 +16093,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16098,7 +16103,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16109,41 +16114,26 @@
       </c>
       <c r="AG134" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ134" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK134" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120398201</v>
+        <v>120398190</v>
       </c>
       <c r="B135" t="n">
-        <v>105017</v>
+        <v>78542</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16152,25 +16142,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -16180,10 +16170,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>448113</v>
+        <v>448091</v>
       </c>
       <c r="R135" t="n">
-        <v>7032192</v>
+        <v>7032130</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16215,7 +16205,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16225,7 +16215,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16237,9 +16227,19 @@
       <c r="AG135" t="b">
         <v>0</v>
       </c>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT135" t="inlineStr"/>
@@ -16250,7 +16250,7 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>

--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -7760,10 +7760,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120398192</v>
+        <v>120398195</v>
       </c>
       <c r="B63" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7776,21 +7776,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7800,10 +7800,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>448084</v>
+        <v>448076</v>
       </c>
       <c r="R63" t="n">
-        <v>7032156</v>
+        <v>7032148</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På död gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7880,17 +7880,17 @@
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120410090</v>
+        <v>120398191</v>
       </c>
       <c r="B64" t="n">
-        <v>105017</v>
+        <v>78626</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7899,38 +7899,47 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>221725</v>
+        <v>283</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>448077</v>
+        <v>448091</v>
       </c>
       <c r="R64" t="n">
-        <v>7032240</v>
+        <v>7032130</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7960,11 +7969,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7973,26 +7992,41 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>På klen undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120407781</v>
+        <v>120407746</v>
       </c>
       <c r="B65" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8005,21 +8039,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8029,10 +8063,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>448064</v>
+        <v>447902</v>
       </c>
       <c r="R65" t="n">
-        <v>7032247</v>
+        <v>7032164</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8064,7 +8098,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8074,7 +8108,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8094,17 +8128,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120398178</v>
+        <v>120407776</v>
       </c>
       <c r="B66" t="n">
-        <v>77479</v>
+        <v>91512</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8113,38 +8147,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228579</v>
+        <v>4769</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447950</v>
+        <v>448121</v>
       </c>
       <c r="R66" t="n">
-        <v>7031971</v>
+        <v>7032208</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8176,7 +8210,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8186,7 +8220,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8197,41 +8231,26 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120407758</v>
+        <v>120407772</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
+        <v>78626</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8244,21 +8263,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8268,10 +8287,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447946</v>
+        <v>448093</v>
       </c>
       <c r="R67" t="n">
-        <v>7031890</v>
+        <v>7032124</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8303,7 +8322,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8313,7 +8332,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8333,14 +8352,14 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120407764</v>
+        <v>120398176</v>
       </c>
       <c r="B68" t="n">
         <v>78542</v>
@@ -8376,14 +8395,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447980</v>
+        <v>447950</v>
       </c>
       <c r="R68" t="n">
-        <v>7031975</v>
+        <v>7031971</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8415,7 +8434,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8425,7 +8444,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8436,23 +8455,38 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120398180</v>
+        <v>120407763</v>
       </c>
       <c r="B69" t="n">
         <v>78542</v>
@@ -8488,14 +8522,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447981</v>
+        <v>447956</v>
       </c>
       <c r="R69" t="n">
-        <v>7031976</v>
+        <v>7031963</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8527,7 +8561,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8537,7 +8571,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8548,41 +8582,26 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120410088</v>
+        <v>120407768</v>
       </c>
       <c r="B70" t="n">
-        <v>90580</v>
+        <v>78626</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8595,21 +8614,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>283</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8619,10 +8638,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>448098</v>
+        <v>448083</v>
       </c>
       <c r="R70" t="n">
-        <v>7032176</v>
+        <v>7032095</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8652,9 +8671,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8669,22 +8698,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120410101</v>
+        <v>120407762</v>
       </c>
       <c r="B71" t="n">
-        <v>94334</v>
+        <v>90580</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8693,25 +8722,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2809</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8721,10 +8750,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447936</v>
+        <v>447905</v>
       </c>
       <c r="R71" t="n">
-        <v>7032054</v>
+        <v>7031937</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8754,9 +8783,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8771,22 +8810,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120398204</v>
+        <v>120410098</v>
       </c>
       <c r="B72" t="n">
-        <v>79624</v>
+        <v>90580</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8799,34 +8838,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>448111</v>
+        <v>447938</v>
       </c>
       <c r="R72" t="n">
-        <v>7032232</v>
+        <v>7031999</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8856,21 +8895,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8879,41 +8908,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>På död rönn # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120407756</v>
+        <v>120407757</v>
       </c>
       <c r="B73" t="n">
-        <v>74654</v>
+        <v>77479</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8926,21 +8940,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9022,7 +9036,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120398193</v>
+        <v>120398202</v>
       </c>
       <c r="B74" t="n">
         <v>78542</v>
@@ -9062,10 +9076,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>448084</v>
+        <v>448121</v>
       </c>
       <c r="R74" t="n">
-        <v>7032156</v>
+        <v>7032229</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9097,7 +9111,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9107,7 +9121,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9131,7 +9145,7 @@
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9142,17 +9156,17 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120407740</v>
+        <v>120398177</v>
       </c>
       <c r="B75" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9165,34 +9179,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>448010</v>
+        <v>447950</v>
       </c>
       <c r="R75" t="n">
-        <v>7032227</v>
+        <v>7031971</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9224,7 +9238,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9234,7 +9248,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9245,23 +9259,38 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>på bark på stam av gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120407783</v>
+        <v>120407751</v>
       </c>
       <c r="B76" t="n">
         <v>78542</v>
@@ -9301,10 +9330,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>448072</v>
+        <v>447900</v>
       </c>
       <c r="R76" t="n">
-        <v>7032251</v>
+        <v>7032092</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9336,7 +9365,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9346,7 +9375,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9366,17 +9395,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120410102</v>
+        <v>120407774</v>
       </c>
       <c r="B77" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9389,21 +9418,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -9413,10 +9442,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447931</v>
+        <v>448102</v>
       </c>
       <c r="R77" t="n">
-        <v>7031818</v>
+        <v>7032163</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9446,9 +9475,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9463,22 +9502,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120407772</v>
+        <v>120410105</v>
       </c>
       <c r="B78" t="n">
-        <v>78626</v>
+        <v>90580</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9491,21 +9530,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9515,10 +9554,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>448093</v>
+        <v>447912</v>
       </c>
       <c r="R78" t="n">
-        <v>7032124</v>
+        <v>7031942</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9548,19 +9587,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>11:18</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>11:18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9575,22 +9604,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120398200</v>
+        <v>120407781</v>
       </c>
       <c r="B79" t="n">
-        <v>78542</v>
+        <v>77479</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9603,34 +9632,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>448113</v>
+        <v>448064</v>
       </c>
       <c r="R79" t="n">
-        <v>7032192</v>
+        <v>7032247</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9662,7 +9691,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9672,7 +9701,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9683,41 +9712,26 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120398175</v>
+        <v>120407743</v>
       </c>
       <c r="B80" t="n">
-        <v>78626</v>
+        <v>77479</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9730,34 +9744,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447933</v>
+        <v>447906</v>
       </c>
       <c r="R80" t="n">
-        <v>7031977</v>
+        <v>7032176</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9789,7 +9803,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9799,7 +9813,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9810,41 +9824,26 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120407751</v>
+        <v>120410099</v>
       </c>
       <c r="B81" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9857,21 +9856,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9881,10 +9880,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447900</v>
+        <v>447940</v>
       </c>
       <c r="R81" t="n">
-        <v>7032092</v>
+        <v>7032074</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9914,19 +9913,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>14:08</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>14:08</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9941,22 +9930,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120398174</v>
+        <v>120407752</v>
       </c>
       <c r="B82" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9969,34 +9958,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>447933</v>
+        <v>447908</v>
       </c>
       <c r="R82" t="n">
-        <v>7031977</v>
+        <v>7032002</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10028,7 +10017,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10038,7 +10027,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10049,41 +10038,26 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120398177</v>
+        <v>120398196</v>
       </c>
       <c r="B83" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10096,34 +10070,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447950</v>
+        <v>448076</v>
       </c>
       <c r="R83" t="n">
-        <v>7031971</v>
+        <v>7032148</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10155,7 +10129,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10165,7 +10139,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10189,7 +10163,7 @@
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>På död gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10207,7 +10181,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120398202</v>
+        <v>120407747</v>
       </c>
       <c r="B84" t="n">
         <v>78542</v>
@@ -10243,14 +10217,14 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>448121</v>
+        <v>447884</v>
       </c>
       <c r="R84" t="n">
-        <v>7032229</v>
+        <v>7032094</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10282,7 +10256,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10292,7 +10266,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10303,41 +10277,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120398198</v>
+        <v>120407775</v>
       </c>
       <c r="B85" t="n">
-        <v>78626</v>
+        <v>91512</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10346,38 +10305,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>283</v>
+        <v>4769</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>448094</v>
+        <v>448101</v>
       </c>
       <c r="R85" t="n">
-        <v>7032145</v>
+        <v>7032166</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10409,7 +10368,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10419,7 +10378,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10430,41 +10389,26 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120398205</v>
+        <v>120407745</v>
       </c>
       <c r="B86" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10477,34 +10421,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>448111</v>
+        <v>447909</v>
       </c>
       <c r="R86" t="n">
-        <v>7032232</v>
+        <v>7032166</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10536,7 +10480,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10546,7 +10490,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10557,41 +10501,26 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>På död rönn # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120410100</v>
+        <v>120398180</v>
       </c>
       <c r="B87" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10604,34 +10533,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447936</v>
+        <v>447981</v>
       </c>
       <c r="R87" t="n">
-        <v>7032074</v>
+        <v>7031976</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10661,11 +10590,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10674,26 +10613,41 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120407754</v>
+        <v>120407750</v>
       </c>
       <c r="B88" t="n">
-        <v>57320</v>
+        <v>74654</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10706,43 +10660,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447910</v>
+        <v>447916</v>
       </c>
       <c r="R88" t="n">
-        <v>7031953</v>
+        <v>7032098</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10774,7 +10719,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10784,7 +10729,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10811,10 +10756,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120407750</v>
+        <v>120407740</v>
       </c>
       <c r="B89" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10827,21 +10772,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10851,10 +10796,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447916</v>
+        <v>448010</v>
       </c>
       <c r="R89" t="n">
-        <v>7032098</v>
+        <v>7032227</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10886,7 +10831,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10896,7 +10841,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10923,10 +10868,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120407747</v>
+        <v>120407749</v>
       </c>
       <c r="B90" t="n">
-        <v>78542</v>
+        <v>77479</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10939,21 +10884,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10963,10 +10908,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447884</v>
+        <v>447916</v>
       </c>
       <c r="R90" t="n">
-        <v>7032094</v>
+        <v>7032098</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10998,7 +10943,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11008,7 +10953,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11035,10 +10980,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120398196</v>
+        <v>120398172</v>
       </c>
       <c r="B91" t="n">
-        <v>78542</v>
+        <v>74652</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11047,38 +10992,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6486</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>448076</v>
+        <v>447921</v>
       </c>
       <c r="R91" t="n">
-        <v>7032148</v>
+        <v>7031952</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11110,7 +11055,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11120,7 +11065,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11144,7 +11089,7 @@
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>På död gammal gran # Picea abies</t>
+          <t>Djup hålighet vid granbas # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11155,17 +11100,17 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120398195</v>
+        <v>120398179</v>
       </c>
       <c r="B92" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11178,34 +11123,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>448076</v>
+        <v>447981</v>
       </c>
       <c r="R92" t="n">
-        <v>7032148</v>
+        <v>7031976</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11237,7 +11182,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11247,7 +11192,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11271,7 +11216,7 @@
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>På död gammal gran # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -11282,17 +11227,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120407775</v>
+        <v>120398181</v>
       </c>
       <c r="B93" t="n">
-        <v>91512</v>
+        <v>77479</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11301,38 +11246,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4769</v>
+        <v>228579</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>448101</v>
+        <v>447981</v>
       </c>
       <c r="R93" t="n">
-        <v>7032166</v>
+        <v>7031976</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11364,7 +11309,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11374,7 +11319,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11385,26 +11330,41 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120407768</v>
+        <v>120398178</v>
       </c>
       <c r="B94" t="n">
-        <v>78626</v>
+        <v>77479</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11417,34 +11377,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>448083</v>
+        <v>447950</v>
       </c>
       <c r="R94" t="n">
-        <v>7032095</v>
+        <v>7031971</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11476,7 +11436,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11486,7 +11446,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11497,23 +11457,38 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>på bark på stam av gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120407763</v>
+        <v>120407766</v>
       </c>
       <c r="B95" t="n">
         <v>78542</v>
@@ -11553,10 +11528,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447956</v>
+        <v>448082</v>
       </c>
       <c r="R95" t="n">
-        <v>7031963</v>
+        <v>7032097</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11588,7 +11563,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11598,7 +11573,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11625,10 +11600,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120407752</v>
+        <v>120407764</v>
       </c>
       <c r="B96" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11641,21 +11616,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11665,10 +11640,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447908</v>
+        <v>447980</v>
       </c>
       <c r="R96" t="n">
-        <v>7032002</v>
+        <v>7031975</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11700,7 +11675,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11710,7 +11685,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11730,17 +11705,17 @@
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120407774</v>
+        <v>120407753</v>
       </c>
       <c r="B97" t="n">
-        <v>90580</v>
+        <v>74640</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11749,25 +11724,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11777,10 +11752,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>448102</v>
+        <v>447913</v>
       </c>
       <c r="R97" t="n">
-        <v>7032163</v>
+        <v>7031958</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11812,7 +11787,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11822,7 +11797,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11842,17 +11817,17 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120407744</v>
+        <v>120398174</v>
       </c>
       <c r="B98" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11865,34 +11840,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447906</v>
+        <v>447933</v>
       </c>
       <c r="R98" t="n">
-        <v>7032176</v>
+        <v>7031977</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11924,7 +11899,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11934,7 +11909,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11945,26 +11920,41 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120407749</v>
+        <v>120398201</v>
       </c>
       <c r="B99" t="n">
-        <v>77479</v>
+        <v>105017</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11973,38 +11963,38 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>228579</v>
+        <v>221725</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447916</v>
+        <v>448113</v>
       </c>
       <c r="R99" t="n">
-        <v>7032098</v>
+        <v>7032192</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12036,7 +12026,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12046,7 +12036,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12057,26 +12047,31 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>På marken</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120398194</v>
+        <v>120410103</v>
       </c>
       <c r="B100" t="n">
-        <v>77479</v>
+        <v>74654</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12089,34 +12084,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>448084</v>
+        <v>447924</v>
       </c>
       <c r="R100" t="n">
-        <v>7032156</v>
+        <v>7032085</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12146,21 +12141,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AD100" t="b">
         <v>0</v>
       </c>
@@ -12169,41 +12154,26 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120398188</v>
+        <v>120410101</v>
       </c>
       <c r="B101" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12212,38 +12182,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>448087</v>
+        <v>447936</v>
       </c>
       <c r="R101" t="n">
-        <v>7032124</v>
+        <v>7032054</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12273,21 +12243,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -12296,41 +12256,26 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120410103</v>
+        <v>120407741</v>
       </c>
       <c r="B102" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12343,21 +12288,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12367,10 +12312,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>447924</v>
+        <v>447935</v>
       </c>
       <c r="R102" t="n">
-        <v>7032085</v>
+        <v>7032200</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12400,9 +12345,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12417,22 +12372,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120398171</v>
+        <v>120410102</v>
       </c>
       <c r="B103" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12445,34 +12400,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447838</v>
+        <v>447931</v>
       </c>
       <c r="R103" t="n">
-        <v>7031933</v>
+        <v>7031818</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12502,21 +12457,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -12525,41 +12470,26 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>på granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120407779</v>
+        <v>120407748</v>
       </c>
       <c r="B104" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12572,21 +12502,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12596,10 +12526,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>448080</v>
+        <v>447916</v>
       </c>
       <c r="R104" t="n">
-        <v>7032230</v>
+        <v>7032098</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12631,7 +12561,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12641,7 +12571,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12661,17 +12591,17 @@
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120410105</v>
+        <v>120398194</v>
       </c>
       <c r="B105" t="n">
-        <v>90580</v>
+        <v>77479</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -12684,34 +12614,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447912</v>
+        <v>448084</v>
       </c>
       <c r="R105" t="n">
-        <v>7031942</v>
+        <v>7032156</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12741,11 +12671,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AD105" t="b">
         <v>0</v>
       </c>
@@ -12754,26 +12694,41 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120410089</v>
+        <v>120398198</v>
       </c>
       <c r="B106" t="n">
-        <v>90580</v>
+        <v>78626</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12786,34 +12741,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1202</v>
+        <v>283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>448084</v>
+        <v>448094</v>
       </c>
       <c r="R106" t="n">
-        <v>7032224</v>
+        <v>7032145</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12843,11 +12798,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
       <c r="AD106" t="b">
         <v>0</v>
       </c>
@@ -12856,26 +12821,41 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120410098</v>
+        <v>120398200</v>
       </c>
       <c r="B107" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12888,34 +12868,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447938</v>
+        <v>448113</v>
       </c>
       <c r="R107" t="n">
-        <v>7031999</v>
+        <v>7032192</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12945,11 +12925,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12958,26 +12948,41 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120407778</v>
+        <v>120407780</v>
       </c>
       <c r="B108" t="n">
-        <v>74638</v>
+        <v>101469</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12986,25 +12991,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6439</v>
+        <v>22</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Buser) C. G. Westerl.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13014,10 +13019,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>448118</v>
+        <v>448079</v>
       </c>
       <c r="R108" t="n">
-        <v>7032220</v>
+        <v>7032239</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13049,7 +13054,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13059,7 +13064,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13086,10 +13091,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120398203</v>
+        <v>120407783</v>
       </c>
       <c r="B109" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13102,34 +13107,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>448121</v>
+        <v>448072</v>
       </c>
       <c r="R109" t="n">
-        <v>7032229</v>
+        <v>7032251</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13161,7 +13166,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -13171,7 +13176,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13182,41 +13187,26 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120407741</v>
+        <v>120407756</v>
       </c>
       <c r="B110" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13229,21 +13219,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -13253,10 +13243,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447935</v>
+        <v>447945</v>
       </c>
       <c r="R110" t="n">
-        <v>7032200</v>
+        <v>7031891</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13288,7 +13278,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13298,7 +13288,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13325,10 +13315,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120398176</v>
+        <v>120407744</v>
       </c>
       <c r="B111" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13341,34 +13331,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447950</v>
+        <v>447906</v>
       </c>
       <c r="R111" t="n">
-        <v>7031971</v>
+        <v>7032176</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13400,7 +13390,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13410,7 +13400,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13421,41 +13411,26 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120407759</v>
+        <v>120410088</v>
       </c>
       <c r="B112" t="n">
-        <v>91512</v>
+        <v>90580</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13464,25 +13439,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4769</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13492,10 +13467,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447940</v>
+        <v>448098</v>
       </c>
       <c r="R112" t="n">
-        <v>7031893</v>
+        <v>7032176</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13525,19 +13500,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13552,22 +13517,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120407755</v>
+        <v>120398199</v>
       </c>
       <c r="B113" t="n">
-        <v>78542</v>
+        <v>78626</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13580,34 +13545,43 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447922</v>
+        <v>448099</v>
       </c>
       <c r="R113" t="n">
-        <v>7031922</v>
+        <v>7032188</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13639,7 +13613,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13649,7 +13623,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13660,26 +13634,41 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120407746</v>
+        <v>120398171</v>
       </c>
       <c r="B114" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13692,34 +13681,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447902</v>
+        <v>447838</v>
       </c>
       <c r="R114" t="n">
-        <v>7032164</v>
+        <v>7031933</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13751,7 +13740,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13761,7 +13750,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13772,26 +13761,41 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>på granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120398201</v>
+        <v>120398189</v>
       </c>
       <c r="B115" t="n">
-        <v>105017</v>
+        <v>78626</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13800,38 +13804,47 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>221725</v>
+        <v>283</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>448113</v>
+        <v>448087</v>
       </c>
       <c r="R115" t="n">
-        <v>7032192</v>
+        <v>7032124</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13863,7 +13876,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13873,7 +13886,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13885,9 +13898,19 @@
       <c r="AG115" t="b">
         <v>0</v>
       </c>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>På marken</t>
+          <t>På grenar på gammal undertryckt gran # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -13898,17 +13921,17 @@
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120398181</v>
+        <v>120407778</v>
       </c>
       <c r="B116" t="n">
-        <v>77479</v>
+        <v>74638</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13917,38 +13940,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228579</v>
+        <v>6439</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447981</v>
+        <v>448118</v>
       </c>
       <c r="R116" t="n">
-        <v>7031976</v>
+        <v>7032220</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13980,7 +14003,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13990,7 +14013,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14001,41 +14024,26 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Johan Råghall, Jana Novak, Fredrik Jonsson, Ulrika Nordin, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120407753</v>
+        <v>120407773</v>
       </c>
       <c r="B117" t="n">
-        <v>74640</v>
+        <v>77479</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14044,25 +14052,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>306</v>
+        <v>228579</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -14072,10 +14080,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447913</v>
+        <v>448090</v>
       </c>
       <c r="R117" t="n">
-        <v>7031958</v>
+        <v>7032160</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14107,7 +14115,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14117,7 +14125,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14137,17 +14145,17 @@
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120410099</v>
+        <v>120398188</v>
       </c>
       <c r="B118" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14160,34 +14168,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447940</v>
+        <v>448087</v>
       </c>
       <c r="R118" t="n">
-        <v>7032074</v>
+        <v>7032124</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14217,11 +14225,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -14230,26 +14248,41 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120398172</v>
+        <v>120398193</v>
       </c>
       <c r="B119" t="n">
-        <v>74652</v>
+        <v>78542</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14258,38 +14291,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>447921</v>
+        <v>448084</v>
       </c>
       <c r="R119" t="n">
-        <v>7031952</v>
+        <v>7032156</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14321,7 +14354,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14331,7 +14364,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14355,7 +14388,7 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>Djup hålighet vid granbas # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -14373,10 +14406,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120407748</v>
+        <v>120398203</v>
       </c>
       <c r="B120" t="n">
-        <v>82321</v>
+        <v>74654</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14389,34 +14422,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447916</v>
+        <v>448121</v>
       </c>
       <c r="R120" t="n">
-        <v>7032098</v>
+        <v>7032229</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14448,7 +14481,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14458,7 +14491,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14469,23 +14502,38 @@
       </c>
       <c r="AG120" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO120" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120407766</v>
+        <v>120407755</v>
       </c>
       <c r="B121" t="n">
         <v>78542</v>
@@ -14525,10 +14573,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>448082</v>
+        <v>447922</v>
       </c>
       <c r="R121" t="n">
-        <v>7032097</v>
+        <v>7031922</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14560,7 +14608,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14570,7 +14618,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14590,14 +14638,14 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120398191</v>
+        <v>120398175</v>
       </c>
       <c r="B122" t="n">
         <v>78626</v>
@@ -14630,26 +14678,17 @@
           <t>(Degel.) Krog</t>
         </is>
       </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J122" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>448091</v>
+        <v>447933</v>
       </c>
       <c r="R122" t="n">
-        <v>7032130</v>
+        <v>7031977</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14681,7 +14720,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14691,7 +14730,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14715,7 +14754,7 @@
       </c>
       <c r="AO122" t="inlineStr">
         <is>
-          <t>På klen undertryckt gran # Picea abies</t>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14726,17 +14765,17 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120407780</v>
+        <v>120410104</v>
       </c>
       <c r="B123" t="n">
-        <v>101469</v>
+        <v>74654</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14745,25 +14784,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>22</v>
+        <v>6440</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14773,10 +14812,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>448079</v>
+        <v>447915</v>
       </c>
       <c r="R123" t="n">
-        <v>7032239</v>
+        <v>7032086</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14806,19 +14845,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>10:34</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>10:34</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14833,22 +14862,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120407762</v>
+        <v>120407777</v>
       </c>
       <c r="B124" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14861,21 +14890,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14885,10 +14914,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>447905</v>
+        <v>448119</v>
       </c>
       <c r="R124" t="n">
-        <v>7031937</v>
+        <v>7032212</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14920,7 +14949,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14930,7 +14959,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14957,10 +14986,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120398199</v>
+        <v>120407754</v>
       </c>
       <c r="B125" t="n">
-        <v>78626</v>
+        <v>57320</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14973,43 +15002,43 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J125" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>448099</v>
+        <v>447910</v>
       </c>
       <c r="R125" t="n">
-        <v>7032188</v>
+        <v>7031953</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15041,7 +15070,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15051,7 +15080,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15062,41 +15091,26 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ125" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK125" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120398189</v>
+        <v>120398190</v>
       </c>
       <c r="B126" t="n">
-        <v>78626</v>
+        <v>78542</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15109,43 +15123,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
           <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>448087</v>
+        <v>448091</v>
       </c>
       <c r="R126" t="n">
-        <v>7032124</v>
+        <v>7032130</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15177,7 +15182,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15187,7 +15192,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15211,7 +15216,7 @@
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>På grenar på gammal undertryckt gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -15229,10 +15234,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120398179</v>
+        <v>120407758</v>
       </c>
       <c r="B127" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15245,34 +15250,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>447981</v>
+        <v>447946</v>
       </c>
       <c r="R127" t="n">
-        <v>7031976</v>
+        <v>7031890</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15304,7 +15309,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15314,7 +15319,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15325,41 +15330,26 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ127" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK127" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120407743</v>
+        <v>120410089</v>
       </c>
       <c r="B128" t="n">
-        <v>77479</v>
+        <v>90580</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15372,21 +15362,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15396,10 +15386,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>447906</v>
+        <v>448084</v>
       </c>
       <c r="R128" t="n">
-        <v>7032176</v>
+        <v>7032224</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15429,19 +15419,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z128" t="inlineStr">
-        <is>
-          <t>14:26</t>
-        </is>
-      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB128" t="inlineStr">
-        <is>
-          <t>14:26</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15456,22 +15436,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120410104</v>
+        <v>120398204</v>
       </c>
       <c r="B129" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15484,34 +15464,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>447915</v>
+        <v>448111</v>
       </c>
       <c r="R129" t="n">
-        <v>7032086</v>
+        <v>7032232</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15541,11 +15521,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AA129" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
       <c r="AD129" t="b">
         <v>0</v>
       </c>
@@ -15554,26 +15544,41 @@
       </c>
       <c r="AG129" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO129" t="inlineStr">
+        <is>
+          <t>På död rönn # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120407777</v>
+        <v>120407759</v>
       </c>
       <c r="B130" t="n">
-        <v>78542</v>
+        <v>91512</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15582,25 +15587,25 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15610,10 +15615,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>448119</v>
+        <v>447940</v>
       </c>
       <c r="R130" t="n">
-        <v>7032212</v>
+        <v>7031893</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15645,7 +15650,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15655,7 +15660,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15675,17 +15680,17 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120407757</v>
+        <v>120398192</v>
       </c>
       <c r="B131" t="n">
-        <v>77479</v>
+        <v>74654</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15698,34 +15703,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>228579</v>
+        <v>6440</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>447945</v>
+        <v>448084</v>
       </c>
       <c r="R131" t="n">
-        <v>7031891</v>
+        <v>7032156</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15757,7 +15762,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15767,7 +15772,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15778,26 +15783,41 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO131" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120407773</v>
+        <v>120398205</v>
       </c>
       <c r="B132" t="n">
-        <v>77479</v>
+        <v>79623</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15810,34 +15830,34 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>448090</v>
+        <v>448111</v>
       </c>
       <c r="R132" t="n">
-        <v>7032160</v>
+        <v>7032232</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15869,7 +15889,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15879,7 +15899,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15890,23 +15910,38 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO132" t="inlineStr">
+        <is>
+          <t>På död rönn # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120407745</v>
+        <v>120410100</v>
       </c>
       <c r="B133" t="n">
         <v>90598</v>
@@ -15946,10 +15981,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>447909</v>
+        <v>447936</v>
       </c>
       <c r="R133" t="n">
-        <v>7032166</v>
+        <v>7032074</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15979,19 +16014,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16006,22 +16031,22 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120407776</v>
+        <v>120407779</v>
       </c>
       <c r="B134" t="n">
-        <v>91512</v>
+        <v>78542</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16030,25 +16055,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -16058,10 +16083,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>448121</v>
+        <v>448080</v>
       </c>
       <c r="R134" t="n">
-        <v>7032208</v>
+        <v>7032230</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16093,7 +16118,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16103,7 +16128,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16130,10 +16155,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120398190</v>
+        <v>120410090</v>
       </c>
       <c r="B135" t="n">
-        <v>78542</v>
+        <v>105017</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16142,38 +16167,38 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6425</v>
+        <v>221725</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>448091</v>
+        <v>448077</v>
       </c>
       <c r="R135" t="n">
-        <v>7032130</v>
+        <v>7032240</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16203,21 +16228,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
@@ -16226,31 +16241,16 @@
       </c>
       <c r="AG135" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ135" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK135" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Britta Sterner, Jana Novak, Johan Råghall, Ulrika Nordin, Fredrik Jonsson</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>

--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -8247,10 +8247,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120407772</v>
+        <v>120407763</v>
       </c>
       <c r="B67" t="n">
-        <v>78626</v>
+        <v>78542</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8263,21 +8263,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>448093</v>
+        <v>447956</v>
       </c>
       <c r="R67" t="n">
-        <v>7032124</v>
+        <v>7031963</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8359,10 +8359,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120398176</v>
+        <v>120407772</v>
       </c>
       <c r="B68" t="n">
-        <v>78542</v>
+        <v>78626</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8375,34 +8375,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447950</v>
+        <v>448093</v>
       </c>
       <c r="R68" t="n">
-        <v>7031971</v>
+        <v>7032124</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8455,38 +8455,23 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120407763</v>
+        <v>120398176</v>
       </c>
       <c r="B69" t="n">
         <v>78542</v>
@@ -8522,14 +8507,14 @@
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447956</v>
+        <v>447950</v>
       </c>
       <c r="R69" t="n">
-        <v>7031963</v>
+        <v>7031971</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8561,7 +8546,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8571,7 +8556,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8582,16 +8567,31 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -10181,10 +10181,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120407747</v>
+        <v>120407775</v>
       </c>
       <c r="B84" t="n">
-        <v>78542</v>
+        <v>91512</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10193,25 +10193,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10221,10 +10221,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447884</v>
+        <v>448101</v>
       </c>
       <c r="R84" t="n">
-        <v>7032094</v>
+        <v>7032166</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10286,17 +10286,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120407775</v>
+        <v>120407747</v>
       </c>
       <c r="B85" t="n">
-        <v>91512</v>
+        <v>78542</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10305,25 +10305,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10333,10 +10333,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>448101</v>
+        <v>447884</v>
       </c>
       <c r="R85" t="n">
-        <v>7032166</v>
+        <v>7032094</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10398,7 +10398,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -10868,10 +10868,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120407749</v>
+        <v>120398172</v>
       </c>
       <c r="B90" t="n">
-        <v>77479</v>
+        <v>74652</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10880,38 +10880,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228579</v>
+        <v>6486</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447916</v>
+        <v>447921</v>
       </c>
       <c r="R90" t="n">
-        <v>7032098</v>
+        <v>7031952</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10943,7 +10943,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10964,26 +10964,41 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Djup hålighet vid granbas # Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120398172</v>
+        <v>120398179</v>
       </c>
       <c r="B91" t="n">
-        <v>74652</v>
+        <v>74654</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10992,25 +11007,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6486</v>
+        <v>6440</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11020,10 +11035,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447921</v>
+        <v>447981</v>
       </c>
       <c r="R91" t="n">
-        <v>7031952</v>
+        <v>7031976</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11055,7 +11070,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11065,7 +11080,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11089,7 +11104,7 @@
       </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>Djup hålighet vid granbas # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -11107,10 +11122,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120398179</v>
+        <v>120407749</v>
       </c>
       <c r="B92" t="n">
-        <v>74654</v>
+        <v>77479</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11123,34 +11138,34 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447981</v>
+        <v>447916</v>
       </c>
       <c r="R92" t="n">
-        <v>7031976</v>
+        <v>7032098</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11182,7 +11197,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11192,7 +11207,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11203,31 +11218,16 @@
       </c>
       <c r="AG92" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -11951,10 +11951,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120398201</v>
+        <v>120410101</v>
       </c>
       <c r="B99" t="n">
-        <v>105017</v>
+        <v>94334</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11967,34 +11967,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>221725</v>
+        <v>2809</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>448113</v>
+        <v>447936</v>
       </c>
       <c r="R99" t="n">
-        <v>7032192</v>
+        <v>7032054</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12024,21 +12024,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AD99" t="b">
         <v>0</v>
       </c>
@@ -12047,31 +12037,26 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>På marken</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120410103</v>
+        <v>120407741</v>
       </c>
       <c r="B100" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12084,21 +12069,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12108,10 +12093,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447924</v>
+        <v>447935</v>
       </c>
       <c r="R100" t="n">
-        <v>7032085</v>
+        <v>7032200</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12141,9 +12126,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12158,22 +12153,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120410101</v>
+        <v>120410102</v>
       </c>
       <c r="B101" t="n">
-        <v>94334</v>
+        <v>90598</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12182,25 +12177,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2809</v>
+        <v>5432</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12210,10 +12205,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447936</v>
+        <v>447931</v>
       </c>
       <c r="R101" t="n">
-        <v>7032054</v>
+        <v>7031818</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12272,10 +12267,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120407741</v>
+        <v>120398201</v>
       </c>
       <c r="B102" t="n">
-        <v>90598</v>
+        <v>105017</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12284,38 +12279,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5432</v>
+        <v>221725</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>447935</v>
+        <v>448113</v>
       </c>
       <c r="R102" t="n">
-        <v>7032200</v>
+        <v>7032192</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12347,7 +12342,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12357,7 +12352,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12368,26 +12363,31 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>På marken</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120410102</v>
+        <v>120407748</v>
       </c>
       <c r="B103" t="n">
-        <v>90598</v>
+        <v>82321</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12400,21 +12400,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12424,10 +12424,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447931</v>
+        <v>447916</v>
       </c>
       <c r="R103" t="n">
-        <v>7031818</v>
+        <v>7032098</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12457,9 +12457,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12474,22 +12484,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120407748</v>
+        <v>120410103</v>
       </c>
       <c r="B104" t="n">
-        <v>82321</v>
+        <v>74654</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12502,21 +12512,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -12526,10 +12536,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>447916</v>
+        <v>447924</v>
       </c>
       <c r="R104" t="n">
-        <v>7032098</v>
+        <v>7032085</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12559,19 +12569,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>14:10</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>14:10</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12586,12 +12586,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -13315,10 +13315,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120407744</v>
+        <v>120398199</v>
       </c>
       <c r="B111" t="n">
-        <v>74654</v>
+        <v>78626</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13331,34 +13331,43 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447906</v>
+        <v>448099</v>
       </c>
       <c r="R111" t="n">
-        <v>7032176</v>
+        <v>7032188</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13390,7 +13399,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13400,7 +13409,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13411,26 +13420,41 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120410088</v>
+        <v>120407744</v>
       </c>
       <c r="B112" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13443,21 +13467,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -13467,7 +13491,7 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>448098</v>
+        <v>447906</v>
       </c>
       <c r="R112" t="n">
         <v>7032176</v>
@@ -13500,9 +13524,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13517,22 +13551,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120398199</v>
+        <v>120410088</v>
       </c>
       <c r="B113" t="n">
-        <v>78626</v>
+        <v>90580</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13545,43 +13579,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>448099</v>
+        <v>448098</v>
       </c>
       <c r="R113" t="n">
-        <v>7032188</v>
+        <v>7032176</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13611,21 +13636,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>11:02</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -13634,31 +13649,16 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
@@ -15234,10 +15234,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120407758</v>
+        <v>120410089</v>
       </c>
       <c r="B127" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15250,21 +15250,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15274,10 +15274,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>447946</v>
+        <v>448084</v>
       </c>
       <c r="R127" t="n">
-        <v>7031890</v>
+        <v>7032224</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15307,19 +15307,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15334,22 +15324,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120410089</v>
+        <v>120407758</v>
       </c>
       <c r="B128" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15362,21 +15352,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15386,10 +15376,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>448084</v>
+        <v>447946</v>
       </c>
       <c r="R128" t="n">
-        <v>7032224</v>
+        <v>7031890</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15419,9 +15409,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA128" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15436,22 +15436,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120398204</v>
+        <v>120398192</v>
       </c>
       <c r="B129" t="n">
-        <v>79624</v>
+        <v>74654</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15464,21 +15464,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15488,10 +15488,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>448111</v>
+        <v>448084</v>
       </c>
       <c r="R129" t="n">
-        <v>7032232</v>
+        <v>7032156</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15523,7 +15523,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15533,7 +15533,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15547,17 +15547,17 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>På död rönn # Sorbus aucuparia</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -15575,10 +15575,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120407759</v>
+        <v>120398205</v>
       </c>
       <c r="B130" t="n">
-        <v>91512</v>
+        <v>79623</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15587,38 +15587,38 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>4769</v>
+        <v>6458</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>447940</v>
+        <v>448111</v>
       </c>
       <c r="R130" t="n">
-        <v>7031893</v>
+        <v>7032232</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15650,7 +15650,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15671,26 +15671,41 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO130" t="inlineStr">
+        <is>
+          <t>På död rönn # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120398192</v>
+        <v>120398204</v>
       </c>
       <c r="B131" t="n">
-        <v>74654</v>
+        <v>79624</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15703,21 +15718,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6440</v>
+        <v>2081</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15727,10 +15742,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>448084</v>
+        <v>448111</v>
       </c>
       <c r="R131" t="n">
-        <v>7032156</v>
+        <v>7032232</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15762,7 +15777,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -15772,7 +15787,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15786,17 +15801,17 @@
       </c>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO131" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På död rönn # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
@@ -15814,10 +15829,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120398205</v>
+        <v>120407759</v>
       </c>
       <c r="B132" t="n">
-        <v>79623</v>
+        <v>91512</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15826,38 +15841,38 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>4769</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>448111</v>
+        <v>447940</v>
       </c>
       <c r="R132" t="n">
-        <v>7032232</v>
+        <v>7031893</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15889,7 +15904,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15899,7 +15914,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15910,31 +15925,16 @@
       </c>
       <c r="AG132" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ132" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK132" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>På död rönn # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>

--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -7760,10 +7760,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120398195</v>
+        <v>120410089</v>
       </c>
       <c r="B63" t="n">
-        <v>90598</v>
+        <v>90580</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7776,34 +7776,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>448076</v>
+        <v>448084</v>
       </c>
       <c r="R63" t="n">
-        <v>7032148</v>
+        <v>7032224</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7833,21 +7833,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>11:12</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7856,41 +7846,26 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>På död gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120398191</v>
+        <v>120410104</v>
       </c>
       <c r="B64" t="n">
-        <v>78626</v>
+        <v>74654</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7903,43 +7878,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>448091</v>
+        <v>447915</v>
       </c>
       <c r="R64" t="n">
-        <v>7032130</v>
+        <v>7032086</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7969,21 +7935,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7992,41 +7948,26 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>På klen undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120407746</v>
+        <v>120407768</v>
       </c>
       <c r="B65" t="n">
-        <v>78542</v>
+        <v>78626</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8039,21 +7980,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8063,10 +8004,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>447902</v>
+        <v>448083</v>
       </c>
       <c r="R65" t="n">
-        <v>7032164</v>
+        <v>7032095</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8098,7 +8039,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8108,7 +8049,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8128,17 +8069,17 @@
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120407776</v>
+        <v>120410101</v>
       </c>
       <c r="B66" t="n">
-        <v>91512</v>
+        <v>94334</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8151,21 +8092,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4769</v>
+        <v>2809</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -8175,10 +8116,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>448121</v>
+        <v>447936</v>
       </c>
       <c r="R66" t="n">
-        <v>7032208</v>
+        <v>7032054</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8208,19 +8149,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>10:49</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>10:49</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8235,19 +8166,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120407763</v>
+        <v>120407740</v>
       </c>
       <c r="B67" t="n">
         <v>78542</v>
@@ -8287,10 +8218,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447956</v>
+        <v>448010</v>
       </c>
       <c r="R67" t="n">
-        <v>7031963</v>
+        <v>7032227</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8322,7 +8253,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8332,7 +8263,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8352,17 +8283,17 @@
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120407772</v>
+        <v>120407744</v>
       </c>
       <c r="B68" t="n">
-        <v>78626</v>
+        <v>74654</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8375,21 +8306,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8399,10 +8330,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>448093</v>
+        <v>447906</v>
       </c>
       <c r="R68" t="n">
-        <v>7032124</v>
+        <v>7032176</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8434,7 +8365,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8444,7 +8375,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8464,17 +8395,17 @@
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120398176</v>
+        <v>120407780</v>
       </c>
       <c r="B69" t="n">
-        <v>78542</v>
+        <v>101469</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8483,38 +8414,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>22</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Buser) C. G. Westerl.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447950</v>
+        <v>448079</v>
       </c>
       <c r="R69" t="n">
-        <v>7031971</v>
+        <v>7032239</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8546,7 +8477,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8556,7 +8487,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8567,41 +8498,26 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120407768</v>
+        <v>120398171</v>
       </c>
       <c r="B70" t="n">
-        <v>78626</v>
+        <v>90580</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8614,34 +8530,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>448083</v>
+        <v>447838</v>
       </c>
       <c r="R70" t="n">
-        <v>7032095</v>
+        <v>7031933</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8673,7 +8589,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8683,7 +8599,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8694,26 +8610,41 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>på granlåga # Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120407762</v>
+        <v>120407775</v>
       </c>
       <c r="B71" t="n">
-        <v>90580</v>
+        <v>91512</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8722,25 +8653,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>4769</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8750,10 +8681,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447905</v>
+        <v>448101</v>
       </c>
       <c r="R71" t="n">
-        <v>7031937</v>
+        <v>7032166</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8785,7 +8716,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8795,7 +8726,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8822,10 +8753,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120410098</v>
+        <v>120398196</v>
       </c>
       <c r="B72" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8838,34 +8769,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447938</v>
+        <v>448076</v>
       </c>
       <c r="R72" t="n">
-        <v>7031999</v>
+        <v>7032148</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8895,11 +8826,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8908,26 +8849,41 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>På död gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120407757</v>
+        <v>120398174</v>
       </c>
       <c r="B73" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8940,34 +8896,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447945</v>
+        <v>447933</v>
       </c>
       <c r="R73" t="n">
-        <v>7031891</v>
+        <v>7031977</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8999,7 +8955,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9009,7 +8965,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9020,26 +8976,41 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120398202</v>
+        <v>120407749</v>
       </c>
       <c r="B74" t="n">
-        <v>78542</v>
+        <v>77479</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9052,34 +9023,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>448121</v>
+        <v>447916</v>
       </c>
       <c r="R74" t="n">
-        <v>7032229</v>
+        <v>7032098</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9111,7 +9082,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9121,7 +9092,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9132,41 +9103,26 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120398177</v>
+        <v>120407783</v>
       </c>
       <c r="B75" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9179,34 +9135,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447950</v>
+        <v>448072</v>
       </c>
       <c r="R75" t="n">
-        <v>7031971</v>
+        <v>7032251</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9238,7 +9194,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9248,7 +9204,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9259,31 +9215,16 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -9514,10 +9455,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120410105</v>
+        <v>120407747</v>
       </c>
       <c r="B78" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9530,21 +9471,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9554,10 +9495,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447912</v>
+        <v>447884</v>
       </c>
       <c r="R78" t="n">
-        <v>7031942</v>
+        <v>7032094</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9587,9 +9528,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:18</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9604,22 +9555,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120407781</v>
+        <v>120407753</v>
       </c>
       <c r="B79" t="n">
-        <v>77479</v>
+        <v>74640</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9628,25 +9579,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228579</v>
+        <v>306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9656,10 +9607,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>448064</v>
+        <v>447913</v>
       </c>
       <c r="R79" t="n">
-        <v>7032247</v>
+        <v>7031958</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9691,7 +9642,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9701,7 +9652,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>10:33</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9721,7 +9672,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -9840,10 +9791,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120410099</v>
+        <v>120398189</v>
       </c>
       <c r="B81" t="n">
-        <v>90598</v>
+        <v>78626</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9856,34 +9807,43 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447940</v>
+        <v>448087</v>
       </c>
       <c r="R81" t="n">
-        <v>7032074</v>
+        <v>7032124</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9913,11 +9873,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9926,26 +9896,41 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>På grenar på gammal undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120407752</v>
+        <v>120398202</v>
       </c>
       <c r="B82" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9958,34 +9943,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>447908</v>
+        <v>448121</v>
       </c>
       <c r="R82" t="n">
-        <v>7032002</v>
+        <v>7032229</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10017,7 +10002,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10027,7 +10012,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10038,26 +10023,41 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120398196</v>
+        <v>120398204</v>
       </c>
       <c r="B83" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10070,21 +10070,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10094,10 +10094,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>448076</v>
+        <v>448111</v>
       </c>
       <c r="R83" t="n">
-        <v>7032148</v>
+        <v>7032232</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10129,7 +10129,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10153,17 +10153,17 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>På död gammal gran # Picea abies</t>
+          <t>På död rönn # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10181,10 +10181,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120407775</v>
+        <v>120398201</v>
       </c>
       <c r="B84" t="n">
-        <v>91512</v>
+        <v>105017</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10197,34 +10197,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4769</v>
+        <v>221725</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>448101</v>
+        <v>448113</v>
       </c>
       <c r="R84" t="n">
-        <v>7032166</v>
+        <v>7032192</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10256,7 +10256,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10266,7 +10266,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10277,26 +10277,31 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>På marken</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120407747</v>
+        <v>120407762</v>
       </c>
       <c r="B85" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10309,21 +10314,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10333,10 +10338,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447884</v>
+        <v>447905</v>
       </c>
       <c r="R85" t="n">
-        <v>7032094</v>
+        <v>7031937</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10368,7 +10373,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10378,7 +10383,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>14:18</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10398,17 +10403,17 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120407745</v>
+        <v>120407763</v>
       </c>
       <c r="B86" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10421,21 +10426,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10445,10 +10450,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447909</v>
+        <v>447956</v>
       </c>
       <c r="R86" t="n">
-        <v>7032166</v>
+        <v>7031963</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10480,7 +10485,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -10490,7 +10495,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10510,17 +10515,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120398180</v>
+        <v>120398191</v>
       </c>
       <c r="B87" t="n">
-        <v>78542</v>
+        <v>78626</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10533,34 +10538,43 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>447981</v>
+        <v>448091</v>
       </c>
       <c r="R87" t="n">
-        <v>7031976</v>
+        <v>7032130</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10592,7 +10606,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10602,7 +10616,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10626,7 +10640,7 @@
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>På klen undertryckt gran # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10644,10 +10658,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120407750</v>
+        <v>120398199</v>
       </c>
       <c r="B88" t="n">
-        <v>74654</v>
+        <v>78626</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10660,34 +10674,43 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447916</v>
+        <v>448099</v>
       </c>
       <c r="R88" t="n">
-        <v>7032098</v>
+        <v>7032188</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10719,7 +10742,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10729,7 +10752,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10740,23 +10763,38 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120407740</v>
+        <v>120398188</v>
       </c>
       <c r="B89" t="n">
         <v>78542</v>
@@ -10792,14 +10830,14 @@
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>448010</v>
+        <v>448087</v>
       </c>
       <c r="R89" t="n">
-        <v>7032227</v>
+        <v>7032124</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10831,7 +10869,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10841,7 +10879,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10852,26 +10890,41 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120398172</v>
+        <v>120398180</v>
       </c>
       <c r="B90" t="n">
-        <v>74652</v>
+        <v>78542</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10880,25 +10933,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6486</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10908,10 +10961,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447921</v>
+        <v>447981</v>
       </c>
       <c r="R90" t="n">
-        <v>7031952</v>
+        <v>7031976</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10943,7 +10996,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10953,7 +11006,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10977,7 +11030,7 @@
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>Djup hålighet vid granbas # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10995,10 +11048,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120398179</v>
+        <v>120407781</v>
       </c>
       <c r="B91" t="n">
-        <v>74654</v>
+        <v>77479</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11011,34 +11064,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447981</v>
+        <v>448064</v>
       </c>
       <c r="R91" t="n">
-        <v>7031976</v>
+        <v>7032247</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11070,7 +11123,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -11080,7 +11133,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11091,41 +11144,26 @@
       </c>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120407749</v>
+        <v>120407764</v>
       </c>
       <c r="B92" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11138,21 +11176,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11162,10 +11200,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447916</v>
+        <v>447980</v>
       </c>
       <c r="R92" t="n">
-        <v>7032098</v>
+        <v>7031975</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11197,7 +11235,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -11207,7 +11245,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11227,17 +11265,17 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120398181</v>
+        <v>120410090</v>
       </c>
       <c r="B93" t="n">
-        <v>77479</v>
+        <v>105017</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11246,38 +11284,38 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228579</v>
+        <v>221725</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447981</v>
+        <v>448077</v>
       </c>
       <c r="R93" t="n">
-        <v>7031976</v>
+        <v>7032240</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11307,21 +11345,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AD93" t="b">
         <v>0</v>
       </c>
@@ -11330,41 +11358,26 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120398178</v>
+        <v>120407755</v>
       </c>
       <c r="B94" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11377,34 +11390,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447950</v>
+        <v>447922</v>
       </c>
       <c r="R94" t="n">
-        <v>7031971</v>
+        <v>7031922</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11436,7 +11449,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11446,7 +11459,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11457,38 +11470,23 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ94" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK94" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120407766</v>
+        <v>120407746</v>
       </c>
       <c r="B95" t="n">
         <v>78542</v>
@@ -11528,10 +11526,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>448082</v>
+        <v>447902</v>
       </c>
       <c r="R95" t="n">
-        <v>7032097</v>
+        <v>7032164</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11563,7 +11561,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11573,7 +11571,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11593,14 +11591,14 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120407764</v>
+        <v>120398190</v>
       </c>
       <c r="B96" t="n">
         <v>78542</v>
@@ -11636,14 +11634,14 @@
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447980</v>
+        <v>448091</v>
       </c>
       <c r="R96" t="n">
-        <v>7031975</v>
+        <v>7032130</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11675,7 +11673,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -11685,7 +11683,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11696,26 +11694,41 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120407753</v>
+        <v>120398200</v>
       </c>
       <c r="B97" t="n">
-        <v>74640</v>
+        <v>78542</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11724,38 +11737,38 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447913</v>
+        <v>448113</v>
       </c>
       <c r="R97" t="n">
-        <v>7031958</v>
+        <v>7032192</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11787,7 +11800,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11797,7 +11810,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11808,26 +11821,41 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120398174</v>
+        <v>120410088</v>
       </c>
       <c r="B98" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11840,34 +11868,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447933</v>
+        <v>448098</v>
       </c>
       <c r="R98" t="n">
-        <v>7031977</v>
+        <v>7032176</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11897,21 +11925,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -11920,41 +11938,26 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120410101</v>
+        <v>120407772</v>
       </c>
       <c r="B99" t="n">
-        <v>94334</v>
+        <v>78626</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11963,25 +11966,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2809</v>
+        <v>283</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11991,10 +11994,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447936</v>
+        <v>448093</v>
       </c>
       <c r="R99" t="n">
-        <v>7032054</v>
+        <v>7032124</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12024,9 +12027,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12041,22 +12054,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120407741</v>
+        <v>120407748</v>
       </c>
       <c r="B100" t="n">
-        <v>90598</v>
+        <v>82321</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12069,21 +12082,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12093,10 +12106,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447935</v>
+        <v>447916</v>
       </c>
       <c r="R100" t="n">
-        <v>7032200</v>
+        <v>7032098</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12128,7 +12141,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12138,7 +12151,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12165,10 +12178,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120410102</v>
+        <v>120407750</v>
       </c>
       <c r="B101" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12181,21 +12194,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12205,10 +12218,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447931</v>
+        <v>447916</v>
       </c>
       <c r="R101" t="n">
-        <v>7031818</v>
+        <v>7032098</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12238,9 +12251,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12255,22 +12278,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120398201</v>
+        <v>120407756</v>
       </c>
       <c r="B102" t="n">
-        <v>105017</v>
+        <v>74654</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12279,38 +12302,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>221725</v>
+        <v>6440</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>448113</v>
+        <v>447945</v>
       </c>
       <c r="R102" t="n">
-        <v>7032192</v>
+        <v>7031891</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12342,7 +12365,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12352,7 +12375,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12363,31 +12386,26 @@
       </c>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>På marken</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120407748</v>
+        <v>120407757</v>
       </c>
       <c r="B103" t="n">
-        <v>82321</v>
+        <v>77479</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12400,21 +12418,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1312</v>
+        <v>228579</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -12424,10 +12442,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447916</v>
+        <v>447945</v>
       </c>
       <c r="R103" t="n">
-        <v>7032098</v>
+        <v>7031891</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12459,7 +12477,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12469,7 +12487,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12496,10 +12514,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120410103</v>
+        <v>120398176</v>
       </c>
       <c r="B104" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12512,34 +12530,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>447924</v>
+        <v>447950</v>
       </c>
       <c r="R104" t="n">
-        <v>7032085</v>
+        <v>7031971</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12569,11 +12587,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AD104" t="b">
         <v>0</v>
       </c>
@@ -12582,23 +12610,38 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120398194</v>
+        <v>120398178</v>
       </c>
       <c r="B105" t="n">
         <v>77479</v>
@@ -12634,14 +12677,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>448084</v>
+        <v>447950</v>
       </c>
       <c r="R105" t="n">
-        <v>7032156</v>
+        <v>7031971</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12673,7 +12716,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12683,7 +12726,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12707,7 +12750,7 @@
       </c>
       <c r="AO105" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12725,10 +12768,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120398198</v>
+        <v>120407745</v>
       </c>
       <c r="B106" t="n">
-        <v>78626</v>
+        <v>90598</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12741,34 +12784,34 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>283</v>
+        <v>5432</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>448094</v>
+        <v>447909</v>
       </c>
       <c r="R106" t="n">
-        <v>7032145</v>
+        <v>7032166</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12800,7 +12843,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12810,7 +12853,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12821,41 +12864,26 @@
       </c>
       <c r="AG106" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ106" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK106" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120398200</v>
+        <v>120410102</v>
       </c>
       <c r="B107" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12868,34 +12896,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>448113</v>
+        <v>447931</v>
       </c>
       <c r="R107" t="n">
-        <v>7032192</v>
+        <v>7031818</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12925,21 +12953,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12948,41 +12966,26 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ107" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK107" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120407780</v>
+        <v>120407778</v>
       </c>
       <c r="B108" t="n">
-        <v>101469</v>
+        <v>74638</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12991,25 +12994,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>22</v>
+        <v>6439</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -13019,10 +13022,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>448079</v>
+        <v>448118</v>
       </c>
       <c r="R108" t="n">
-        <v>7032239</v>
+        <v>7032220</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13054,7 +13057,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13064,7 +13067,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13091,10 +13094,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120407783</v>
+        <v>120410103</v>
       </c>
       <c r="B109" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13107,21 +13110,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -13131,10 +13134,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>448072</v>
+        <v>447924</v>
       </c>
       <c r="R109" t="n">
-        <v>7032251</v>
+        <v>7032085</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13164,19 +13167,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>10:29</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>10:29</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -13191,19 +13184,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120407756</v>
+        <v>120398203</v>
       </c>
       <c r="B110" t="n">
         <v>74654</v>
@@ -13239,14 +13232,14 @@
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447945</v>
+        <v>448121</v>
       </c>
       <c r="R110" t="n">
-        <v>7031891</v>
+        <v>7032229</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13278,7 +13271,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -13288,7 +13281,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -13299,26 +13292,41 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120398199</v>
+        <v>120407754</v>
       </c>
       <c r="B111" t="n">
-        <v>78626</v>
+        <v>57320</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13331,43 +13339,43 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>283</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>bålar</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>448099</v>
+        <v>447910</v>
       </c>
       <c r="R111" t="n">
-        <v>7032188</v>
+        <v>7031953</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13399,7 +13407,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -13409,7 +13417,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13420,41 +13428,26 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120407744</v>
+        <v>120398194</v>
       </c>
       <c r="B112" t="n">
-        <v>74654</v>
+        <v>77479</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13467,34 +13460,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6440</v>
+        <v>228579</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447906</v>
+        <v>448084</v>
       </c>
       <c r="R112" t="n">
-        <v>7032176</v>
+        <v>7032156</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13526,7 +13519,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13536,7 +13529,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13547,26 +13540,41 @@
       </c>
       <c r="AG112" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO112" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120410088</v>
+        <v>120407766</v>
       </c>
       <c r="B113" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13579,21 +13587,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -13603,10 +13611,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>448098</v>
+        <v>448082</v>
       </c>
       <c r="R113" t="n">
-        <v>7032176</v>
+        <v>7032097</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13636,9 +13644,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>11:27</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13653,22 +13671,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120398171</v>
+        <v>120407777</v>
       </c>
       <c r="B114" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13681,34 +13699,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447838</v>
+        <v>448119</v>
       </c>
       <c r="R114" t="n">
-        <v>7031933</v>
+        <v>7032212</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13740,7 +13758,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13750,7 +13768,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13761,41 +13779,26 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>på granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120398189</v>
+        <v>120398192</v>
       </c>
       <c r="B115" t="n">
-        <v>78626</v>
+        <v>74654</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13808,43 +13811,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>448087</v>
+        <v>448084</v>
       </c>
       <c r="R115" t="n">
-        <v>7032124</v>
+        <v>7032156</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13876,7 +13870,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -13886,7 +13880,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13910,7 +13904,7 @@
       </c>
       <c r="AO115" t="inlineStr">
         <is>
-          <t>På grenar på gammal undertryckt gran # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT115" t="inlineStr"/>
@@ -13928,10 +13922,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120407778</v>
+        <v>120398205</v>
       </c>
       <c r="B116" t="n">
-        <v>74638</v>
+        <v>79623</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13940,38 +13934,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6439</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>448118</v>
+        <v>448111</v>
       </c>
       <c r="R116" t="n">
-        <v>7032220</v>
+        <v>7032232</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -14003,7 +13997,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14013,7 +14007,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14024,26 +14018,41 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>På död rönn # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120407773</v>
+        <v>120398193</v>
       </c>
       <c r="B117" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14056,34 +14065,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>448090</v>
+        <v>448084</v>
       </c>
       <c r="R117" t="n">
-        <v>7032160</v>
+        <v>7032156</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14115,7 +14124,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14125,7 +14134,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14136,26 +14145,41 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120398188</v>
+        <v>120410098</v>
       </c>
       <c r="B118" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14168,34 +14192,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>448087</v>
+        <v>447938</v>
       </c>
       <c r="R118" t="n">
-        <v>7032124</v>
+        <v>7031999</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14225,21 +14249,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>11:19</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -14248,41 +14262,26 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ118" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK118" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120398193</v>
+        <v>120398177</v>
       </c>
       <c r="B119" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14295,34 +14294,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>448084</v>
+        <v>447950</v>
       </c>
       <c r="R119" t="n">
-        <v>7032156</v>
+        <v>7031971</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14354,7 +14353,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14364,7 +14363,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14388,7 +14387,7 @@
       </c>
       <c r="AO119" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT119" t="inlineStr"/>
@@ -14406,7 +14405,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120398203</v>
+        <v>120398179</v>
       </c>
       <c r="B120" t="n">
         <v>74654</v>
@@ -14442,14 +14441,14 @@
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>448121</v>
+        <v>447981</v>
       </c>
       <c r="R120" t="n">
-        <v>7032229</v>
+        <v>7031976</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14481,7 +14480,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14491,7 +14490,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14533,10 +14532,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120407755</v>
+        <v>120398175</v>
       </c>
       <c r="B121" t="n">
-        <v>78542</v>
+        <v>78626</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14549,34 +14548,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447922</v>
+        <v>447933</v>
       </c>
       <c r="R121" t="n">
-        <v>7031922</v>
+        <v>7031977</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14608,7 +14607,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14618,7 +14617,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:59</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14629,26 +14628,41 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120398175</v>
+        <v>120410105</v>
       </c>
       <c r="B122" t="n">
-        <v>78626</v>
+        <v>90580</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14661,34 +14675,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>283</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447933</v>
+        <v>447912</v>
       </c>
       <c r="R122" t="n">
-        <v>7031977</v>
+        <v>7031942</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14718,21 +14732,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>11:59</t>
-        </is>
-      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -14741,41 +14745,26 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120410104</v>
+        <v>120407752</v>
       </c>
       <c r="B123" t="n">
-        <v>74654</v>
+        <v>90598</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14788,21 +14777,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14812,10 +14801,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447915</v>
+        <v>447908</v>
       </c>
       <c r="R123" t="n">
-        <v>7032086</v>
+        <v>7032002</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14845,9 +14834,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14862,22 +14861,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120407777</v>
+        <v>120407759</v>
       </c>
       <c r="B124" t="n">
-        <v>78542</v>
+        <v>91512</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14886,25 +14885,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -14914,10 +14913,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>448119</v>
+        <v>447940</v>
       </c>
       <c r="R124" t="n">
-        <v>7032212</v>
+        <v>7031893</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14949,7 +14948,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14959,7 +14958,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14979,17 +14978,17 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120407754</v>
+        <v>120407776</v>
       </c>
       <c r="B125" t="n">
-        <v>57320</v>
+        <v>91512</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14998,47 +14997,38 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>100109</v>
+        <v>4769</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M125" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Scop.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
           <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>447910</v>
+        <v>448121</v>
       </c>
       <c r="R125" t="n">
-        <v>7031953</v>
+        <v>7032208</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15070,7 +15060,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15080,7 +15070,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15100,17 +15090,17 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120398190</v>
+        <v>120407773</v>
       </c>
       <c r="B126" t="n">
-        <v>78542</v>
+        <v>77479</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15123,34 +15113,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>448091</v>
+        <v>448090</v>
       </c>
       <c r="R126" t="n">
-        <v>7032130</v>
+        <v>7032160</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15182,7 +15172,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15192,7 +15182,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15203,41 +15193,26 @@
       </c>
       <c r="AG126" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ126" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK126" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120410089</v>
+        <v>120398195</v>
       </c>
       <c r="B127" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15250,34 +15225,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>448084</v>
+        <v>448076</v>
       </c>
       <c r="R127" t="n">
-        <v>7032224</v>
+        <v>7032148</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15307,11 +15282,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AA127" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>11:12</t>
+        </is>
+      </c>
       <c r="AD127" t="b">
         <v>0</v>
       </c>
@@ -15320,26 +15305,41 @@
       </c>
       <c r="AG127" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO127" t="inlineStr">
+        <is>
+          <t>På död gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120407758</v>
+        <v>120398198</v>
       </c>
       <c r="B128" t="n">
-        <v>78542</v>
+        <v>78626</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15352,34 +15352,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>447946</v>
+        <v>448094</v>
       </c>
       <c r="R128" t="n">
-        <v>7031890</v>
+        <v>7032145</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15421,7 +15421,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15432,26 +15432,41 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO128" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120398192</v>
+        <v>120398172</v>
       </c>
       <c r="B129" t="n">
-        <v>74654</v>
+        <v>74652</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15460,38 +15475,38 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6440</v>
+        <v>6486</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>448084</v>
+        <v>447921</v>
       </c>
       <c r="R129" t="n">
-        <v>7032156</v>
+        <v>7031952</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15523,7 +15538,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15533,7 +15548,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15557,7 +15572,7 @@
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>Djup hålighet vid granbas # Picea abies</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -15575,10 +15590,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120398205</v>
+        <v>120407758</v>
       </c>
       <c r="B130" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15591,34 +15606,34 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>448111</v>
+        <v>447946</v>
       </c>
       <c r="R130" t="n">
-        <v>7032232</v>
+        <v>7031890</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15650,7 +15665,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15660,7 +15675,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15671,41 +15686,26 @@
       </c>
       <c r="AG130" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ130" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK130" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>På död rönn # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120398204</v>
+        <v>120410100</v>
       </c>
       <c r="B131" t="n">
-        <v>79624</v>
+        <v>90598</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15718,34 +15718,34 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>448111</v>
+        <v>447936</v>
       </c>
       <c r="R131" t="n">
-        <v>7032232</v>
+        <v>7032074</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15775,21 +15775,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z131" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB131" t="inlineStr">
-        <is>
-          <t>10:40</t>
-        </is>
-      </c>
       <c r="AD131" t="b">
         <v>0</v>
       </c>
@@ -15798,41 +15788,26 @@
       </c>
       <c r="AG131" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ131" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK131" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>På död rönn # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120407759</v>
+        <v>120407779</v>
       </c>
       <c r="B132" t="n">
-        <v>91512</v>
+        <v>78542</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -15841,25 +15816,25 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4769</v>
+        <v>6425</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -15869,10 +15844,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>447940</v>
+        <v>448080</v>
       </c>
       <c r="R132" t="n">
-        <v>7031893</v>
+        <v>7032230</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15904,7 +15879,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15914,7 +15889,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15934,17 +15909,17 @@
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120410100</v>
+        <v>120398181</v>
       </c>
       <c r="B133" t="n">
-        <v>90598</v>
+        <v>77479</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15957,34 +15932,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>447936</v>
+        <v>447981</v>
       </c>
       <c r="R133" t="n">
-        <v>7032074</v>
+        <v>7031976</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -16014,11 +15989,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA133" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AD133" t="b">
         <v>0</v>
       </c>
@@ -16027,26 +16012,41 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO133" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120407779</v>
+        <v>120410099</v>
       </c>
       <c r="B134" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16059,21 +16059,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -16083,10 +16083,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>448080</v>
+        <v>447940</v>
       </c>
       <c r="R134" t="n">
-        <v>7032230</v>
+        <v>7032074</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16116,19 +16116,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>10:38</t>
-        </is>
-      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>10:38</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16143,22 +16133,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120410090</v>
+        <v>120407741</v>
       </c>
       <c r="B135" t="n">
-        <v>105017</v>
+        <v>90598</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16167,25 +16157,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>221725</v>
+        <v>5432</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -16195,10 +16185,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>448077</v>
+        <v>447935</v>
       </c>
       <c r="R135" t="n">
-        <v>7032240</v>
+        <v>7032200</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16228,9 +16218,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA135" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -16245,12 +16245,12 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>

--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -7760,10 +7760,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120410089</v>
+        <v>120398176</v>
       </c>
       <c r="B63" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7776,34 +7776,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>448084</v>
+        <v>447950</v>
       </c>
       <c r="R63" t="n">
-        <v>7032224</v>
+        <v>7031971</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7833,11 +7833,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7846,26 +7856,41 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120410104</v>
+        <v>120407777</v>
       </c>
       <c r="B64" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7878,21 +7903,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7902,10 +7927,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447915</v>
+        <v>448119</v>
       </c>
       <c r="R64" t="n">
-        <v>7032086</v>
+        <v>7032212</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7935,9 +7960,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>10:48</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7952,22 +7987,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120407768</v>
+        <v>120410103</v>
       </c>
       <c r="B65" t="n">
-        <v>78626</v>
+        <v>74654</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7980,21 +8015,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8004,10 +8039,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>448083</v>
+        <v>447924</v>
       </c>
       <c r="R65" t="n">
-        <v>7032095</v>
+        <v>7032085</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8037,19 +8072,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>11:26</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>11:26</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8064,22 +8089,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120410101</v>
+        <v>120398177</v>
       </c>
       <c r="B66" t="n">
-        <v>94334</v>
+        <v>74654</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8088,38 +8113,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>2809</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447936</v>
+        <v>447950</v>
       </c>
       <c r="R66" t="n">
-        <v>7032054</v>
+        <v>7031971</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8149,11 +8174,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8162,26 +8197,41 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>på bark på stam av gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120407740</v>
+        <v>120407752</v>
       </c>
       <c r="B67" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8194,21 +8244,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8218,10 +8268,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>448010</v>
+        <v>447908</v>
       </c>
       <c r="R67" t="n">
-        <v>7032227</v>
+        <v>7032002</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8253,7 +8303,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8263,7 +8313,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8290,7 +8340,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120407744</v>
+        <v>120398179</v>
       </c>
       <c r="B68" t="n">
         <v>74654</v>
@@ -8326,14 +8376,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447906</v>
+        <v>447981</v>
       </c>
       <c r="R68" t="n">
-        <v>7032176</v>
+        <v>7031976</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8365,7 +8415,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8375,7 +8425,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8386,26 +8436,41 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120407780</v>
+        <v>120407773</v>
       </c>
       <c r="B69" t="n">
-        <v>101469</v>
+        <v>77479</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8414,25 +8479,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>22</v>
+        <v>228579</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skarptandad daggkåpa</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alchemilla oxyodonta</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Buser) C. G. Westerl.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8442,10 +8507,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>448079</v>
+        <v>448090</v>
       </c>
       <c r="R69" t="n">
-        <v>7032239</v>
+        <v>7032160</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8477,7 +8542,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8487,7 +8552,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>10:34</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8514,10 +8579,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120398171</v>
+        <v>120407745</v>
       </c>
       <c r="B70" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8530,34 +8595,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447838</v>
+        <v>447909</v>
       </c>
       <c r="R70" t="n">
-        <v>7031933</v>
+        <v>7032166</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8589,7 +8654,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8599,7 +8664,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8610,41 +8675,26 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>på granlåga # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120407775</v>
+        <v>120398173</v>
       </c>
       <c r="B71" t="n">
-        <v>91512</v>
+        <v>78626</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8653,38 +8703,38 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>4769</v>
+        <v>283</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>448101</v>
+        <v>447933</v>
       </c>
       <c r="R71" t="n">
-        <v>7032166</v>
+        <v>7031977</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8716,7 +8766,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8726,7 +8776,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8737,23 +8787,38 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120398196</v>
+        <v>120407747</v>
       </c>
       <c r="B72" t="n">
         <v>78542</v>
@@ -8789,14 +8854,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>448076</v>
+        <v>447884</v>
       </c>
       <c r="R72" t="n">
-        <v>7032148</v>
+        <v>7032094</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8828,7 +8893,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8838,7 +8903,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:18</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8849,41 +8914,26 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>På död gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120398174</v>
+        <v>120398195</v>
       </c>
       <c r="B73" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8896,34 +8946,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>447933</v>
+        <v>448076</v>
       </c>
       <c r="R73" t="n">
-        <v>7031977</v>
+        <v>7032148</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8955,7 +9005,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8965,7 +9015,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8989,7 +9039,7 @@
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>På död gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9007,10 +9057,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120407749</v>
+        <v>120398196</v>
       </c>
       <c r="B74" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9023,34 +9073,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>447916</v>
+        <v>448076</v>
       </c>
       <c r="R74" t="n">
-        <v>7032098</v>
+        <v>7032148</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9082,7 +9132,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9092,7 +9142,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9103,23 +9153,38 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>På död gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120407783</v>
+        <v>120407766</v>
       </c>
       <c r="B75" t="n">
         <v>78542</v>
@@ -9159,10 +9224,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>448072</v>
+        <v>448082</v>
       </c>
       <c r="R75" t="n">
-        <v>7032251</v>
+        <v>7032097</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9194,7 +9259,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9204,7 +9269,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9231,10 +9296,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120407751</v>
+        <v>120407778</v>
       </c>
       <c r="B76" t="n">
-        <v>78542</v>
+        <v>74638</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9243,25 +9308,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6439</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Tibell</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9271,10 +9336,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447900</v>
+        <v>448118</v>
       </c>
       <c r="R76" t="n">
-        <v>7032092</v>
+        <v>7032220</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9306,7 +9371,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9316,7 +9381,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9336,17 +9401,17 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120407774</v>
+        <v>120398172</v>
       </c>
       <c r="B77" t="n">
-        <v>90580</v>
+        <v>74652</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9355,38 +9420,38 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>6486</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>448102</v>
+        <v>447921</v>
       </c>
       <c r="R77" t="n">
-        <v>7032163</v>
+        <v>7031952</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9418,7 +9483,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -9428,7 +9493,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9439,26 +9504,41 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Djup hålighet vid granbas # Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120407747</v>
+        <v>120410104</v>
       </c>
       <c r="B78" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9471,21 +9551,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9495,10 +9575,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447884</v>
+        <v>447915</v>
       </c>
       <c r="R78" t="n">
-        <v>7032094</v>
+        <v>7032086</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9528,19 +9608,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>14:18</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>14:18</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9555,22 +9625,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120407753</v>
+        <v>120398188</v>
       </c>
       <c r="B79" t="n">
-        <v>74640</v>
+        <v>78542</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9579,38 +9649,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447913</v>
+        <v>448087</v>
       </c>
       <c r="R79" t="n">
-        <v>7031958</v>
+        <v>7032124</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9642,7 +9712,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9652,7 +9722,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9663,26 +9733,41 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120407743</v>
+        <v>120407780</v>
       </c>
       <c r="B80" t="n">
-        <v>77479</v>
+        <v>101469</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9691,25 +9776,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228579</v>
+        <v>22</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skarptandad daggkåpa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alchemilla oxyodonta</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Buser) C. G. Westerl.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9719,10 +9804,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447906</v>
+        <v>448079</v>
       </c>
       <c r="R80" t="n">
-        <v>7032176</v>
+        <v>7032239</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9754,7 +9839,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9764,7 +9849,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>10:34</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9784,14 +9869,14 @@
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120398189</v>
+        <v>120407772</v>
       </c>
       <c r="B81" t="n">
         <v>78626</v>
@@ -9824,23 +9909,14 @@
           <t>(Degel.) Krog</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>448087</v>
+        <v>448093</v>
       </c>
       <c r="R81" t="n">
         <v>7032124</v>
@@ -9875,7 +9951,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9885,7 +9961,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9896,41 +9972,26 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>På grenar på gammal undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120398202</v>
+        <v>120407748</v>
       </c>
       <c r="B82" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9943,34 +10004,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>448121</v>
+        <v>447916</v>
       </c>
       <c r="R82" t="n">
-        <v>7032229</v>
+        <v>7032098</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10002,7 +10063,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10012,7 +10073,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10023,41 +10084,26 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120398204</v>
+        <v>120398201</v>
       </c>
       <c r="B83" t="n">
-        <v>79624</v>
+        <v>105017</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10066,25 +10112,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>221725</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -10094,10 +10140,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>448111</v>
+        <v>448113</v>
       </c>
       <c r="R83" t="n">
-        <v>7032232</v>
+        <v>7032192</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10129,7 +10175,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10139,7 +10185,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10151,19 +10197,9 @@
       <c r="AG83" t="b">
         <v>0</v>
       </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>På död rönn # Sorbus aucuparia</t>
+          <t>På marken</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10181,10 +10217,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>120398201</v>
+        <v>120407774</v>
       </c>
       <c r="B84" t="n">
-        <v>105017</v>
+        <v>90580</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10193,38 +10229,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221725</v>
+        <v>1202</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>448113</v>
+        <v>448102</v>
       </c>
       <c r="R84" t="n">
-        <v>7032192</v>
+        <v>7032163</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10256,7 +10292,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10266,7 +10302,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10277,31 +10313,26 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>På marken</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>120407762</v>
+        <v>120410099</v>
       </c>
       <c r="B85" t="n">
-        <v>90580</v>
+        <v>90598</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10314,21 +10345,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -10338,10 +10369,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447905</v>
+        <v>447940</v>
       </c>
       <c r="R85" t="n">
-        <v>7031937</v>
+        <v>7032074</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10371,19 +10402,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>12:19</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>12:19</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10398,22 +10419,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>120407763</v>
+        <v>120410102</v>
       </c>
       <c r="B86" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10426,21 +10447,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -10450,10 +10471,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447956</v>
+        <v>447931</v>
       </c>
       <c r="R86" t="n">
-        <v>7031963</v>
+        <v>7031818</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10483,19 +10504,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>11:52</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>11:52</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10510,22 +10521,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>120398191</v>
+        <v>120407751</v>
       </c>
       <c r="B87" t="n">
-        <v>78626</v>
+        <v>78542</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10538,43 +10549,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>448091</v>
+        <v>447900</v>
       </c>
       <c r="R87" t="n">
-        <v>7032130</v>
+        <v>7032092</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10606,7 +10608,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10616,7 +10618,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10627,38 +10629,23 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>På klen undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>120398199</v>
+        <v>120398191</v>
       </c>
       <c r="B88" t="n">
         <v>78626</v>
@@ -10693,7 +10680,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -10707,10 +10694,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>448099</v>
+        <v>448091</v>
       </c>
       <c r="R88" t="n">
-        <v>7032188</v>
+        <v>7032130</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10742,7 +10729,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10752,7 +10739,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10776,7 +10763,7 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+          <t>På klen undertryckt gran # Picea abies</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10794,10 +10781,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>120398188</v>
+        <v>120407775</v>
       </c>
       <c r="B89" t="n">
-        <v>78542</v>
+        <v>91512</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10806,38 +10793,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>448087</v>
+        <v>448101</v>
       </c>
       <c r="R89" t="n">
-        <v>7032124</v>
+        <v>7032166</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10869,7 +10856,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10879,7 +10866,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10890,41 +10877,26 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>120398180</v>
+        <v>120407776</v>
       </c>
       <c r="B90" t="n">
-        <v>78542</v>
+        <v>91512</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10933,38 +10905,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>4769</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447981</v>
+        <v>448121</v>
       </c>
       <c r="R90" t="n">
-        <v>7031976</v>
+        <v>7032208</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10996,7 +10968,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -11006,7 +10978,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>10:49</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -11017,41 +10989,26 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>120407781</v>
+        <v>120410098</v>
       </c>
       <c r="B91" t="n">
-        <v>77479</v>
+        <v>90580</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -11064,21 +11021,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -11088,10 +11045,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>448064</v>
+        <v>447938</v>
       </c>
       <c r="R91" t="n">
-        <v>7032247</v>
+        <v>7031999</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -11121,19 +11078,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>10:33</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>10:33</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -11148,22 +11095,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>120407764</v>
+        <v>120410100</v>
       </c>
       <c r="B92" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -11176,21 +11123,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -11200,10 +11147,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447980</v>
+        <v>447936</v>
       </c>
       <c r="R92" t="n">
-        <v>7031975</v>
+        <v>7032074</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -11233,19 +11180,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>11:45</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>11:45</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -11260,22 +11197,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>120410090</v>
+        <v>120407740</v>
       </c>
       <c r="B93" t="n">
-        <v>105017</v>
+        <v>78542</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -11284,25 +11221,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>221725</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -11312,10 +11249,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>448077</v>
+        <v>448010</v>
       </c>
       <c r="R93" t="n">
-        <v>7032240</v>
+        <v>7032227</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11345,9 +11282,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -11362,22 +11309,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>120407755</v>
+        <v>120398199</v>
       </c>
       <c r="B94" t="n">
-        <v>78542</v>
+        <v>78626</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -11390,34 +11337,43 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>283</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447922</v>
+        <v>448099</v>
       </c>
       <c r="R94" t="n">
-        <v>7031922</v>
+        <v>7032188</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11449,7 +11405,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -11459,7 +11415,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -11470,26 +11426,41 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>120407746</v>
+        <v>120398205</v>
       </c>
       <c r="B95" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -11502,34 +11473,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447902</v>
+        <v>448111</v>
       </c>
       <c r="R95" t="n">
-        <v>7032164</v>
+        <v>7032232</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11561,7 +11532,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -11571,7 +11542,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11582,26 +11553,41 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>På död rönn # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>120398190</v>
+        <v>120410101</v>
       </c>
       <c r="B96" t="n">
-        <v>78542</v>
+        <v>94334</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -11610,38 +11596,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>2809</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>448091</v>
+        <v>447936</v>
       </c>
       <c r="R96" t="n">
-        <v>7032130</v>
+        <v>7032054</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11671,21 +11657,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AD96" t="b">
         <v>0</v>
       </c>
@@ -11694,41 +11670,26 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>120398200</v>
+        <v>120410089</v>
       </c>
       <c r="B97" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -11741,34 +11702,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>448113</v>
+        <v>448084</v>
       </c>
       <c r="R97" t="n">
-        <v>7032192</v>
+        <v>7032224</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11798,21 +11759,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>10:54</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -11821,41 +11772,26 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>120410088</v>
+        <v>120407756</v>
       </c>
       <c r="B98" t="n">
-        <v>90580</v>
+        <v>74654</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -11868,21 +11804,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>6440</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11892,10 +11828,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>448098</v>
+        <v>447945</v>
       </c>
       <c r="R98" t="n">
-        <v>7032176</v>
+        <v>7031891</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11925,9 +11861,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11942,22 +11888,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>120407772</v>
+        <v>120398202</v>
       </c>
       <c r="B99" t="n">
-        <v>78626</v>
+        <v>78542</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11970,34 +11916,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>448093</v>
+        <v>448121</v>
       </c>
       <c r="R99" t="n">
-        <v>7032124</v>
+        <v>7032229</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -12029,7 +11975,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -12039,7 +11985,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -12050,26 +11996,41 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>120407748</v>
+        <v>120407743</v>
       </c>
       <c r="B100" t="n">
-        <v>82321</v>
+        <v>77479</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -12082,21 +12043,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>228579</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -12106,10 +12067,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447916</v>
+        <v>447906</v>
       </c>
       <c r="R100" t="n">
-        <v>7032098</v>
+        <v>7032176</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -12141,7 +12102,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -12151,7 +12112,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12178,10 +12139,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>120407750</v>
+        <v>120407783</v>
       </c>
       <c r="B101" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -12194,21 +12155,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -12218,10 +12179,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447916</v>
+        <v>448072</v>
       </c>
       <c r="R101" t="n">
-        <v>7032098</v>
+        <v>7032251</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -12253,7 +12214,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -12263,7 +12224,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -12283,17 +12244,17 @@
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>120407756</v>
+        <v>120407762</v>
       </c>
       <c r="B102" t="n">
-        <v>74654</v>
+        <v>90580</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -12306,21 +12267,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -12330,10 +12291,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>447945</v>
+        <v>447905</v>
       </c>
       <c r="R102" t="n">
-        <v>7031891</v>
+        <v>7031937</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12365,7 +12326,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -12375,7 +12336,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12395,17 +12356,17 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>120407757</v>
+        <v>120398180</v>
       </c>
       <c r="B103" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -12418,34 +12379,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447945</v>
+        <v>447981</v>
       </c>
       <c r="R103" t="n">
-        <v>7031891</v>
+        <v>7031976</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12477,7 +12438,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -12487,7 +12448,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12498,26 +12459,41 @@
       </c>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>120398176</v>
+        <v>120407741</v>
       </c>
       <c r="B104" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -12530,34 +12506,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>447950</v>
+        <v>447935</v>
       </c>
       <c r="R104" t="n">
-        <v>7031971</v>
+        <v>7032200</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12589,7 +12565,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -12599,7 +12575,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12610,38 +12586,23 @@
       </c>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>120398178</v>
+        <v>120407757</v>
       </c>
       <c r="B105" t="n">
         <v>77479</v>
@@ -12677,14 +12638,14 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447950</v>
+        <v>447945</v>
       </c>
       <c r="R105" t="n">
-        <v>7031971</v>
+        <v>7031891</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12716,7 +12677,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -12726,7 +12687,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12737,41 +12698,26 @@
       </c>
       <c r="AG105" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ105" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK105" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>120407745</v>
+        <v>120407768</v>
       </c>
       <c r="B106" t="n">
-        <v>90598</v>
+        <v>78626</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -12784,21 +12730,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12808,10 +12754,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>447909</v>
+        <v>448083</v>
       </c>
       <c r="R106" t="n">
-        <v>7032166</v>
+        <v>7032095</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12843,7 +12789,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12853,7 +12799,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>14:24</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12873,17 +12819,17 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>120410102</v>
+        <v>120398189</v>
       </c>
       <c r="B107" t="n">
-        <v>90598</v>
+        <v>78626</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -12896,34 +12842,43 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5432</v>
+        <v>283</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Degel.) Krog</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447931</v>
+        <v>448087</v>
       </c>
       <c r="R107" t="n">
-        <v>7031818</v>
+        <v>7032124</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12953,11 +12908,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12966,26 +12931,41 @@
       </c>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ107" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO107" t="inlineStr">
+        <is>
+          <t>På grenar på gammal undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>120407778</v>
+        <v>120398200</v>
       </c>
       <c r="B108" t="n">
-        <v>74638</v>
+        <v>78542</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12994,38 +12974,38 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6439</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>448118</v>
+        <v>448113</v>
       </c>
       <c r="R108" t="n">
-        <v>7032220</v>
+        <v>7032192</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13057,7 +13037,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -13067,7 +13047,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -13078,26 +13058,41 @@
       </c>
       <c r="AG108" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ108" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO108" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>120410103</v>
+        <v>120398174</v>
       </c>
       <c r="B109" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -13110,34 +13105,34 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>447924</v>
+        <v>447933</v>
       </c>
       <c r="R109" t="n">
-        <v>7032085</v>
+        <v>7031977</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -13167,11 +13162,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>11:59</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -13180,26 +13185,41 @@
       </c>
       <c r="AG109" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ109" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO109" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120398203</v>
+        <v>120410088</v>
       </c>
       <c r="B110" t="n">
-        <v>74654</v>
+        <v>90580</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13212,34 +13232,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6440</v>
+        <v>1202</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>448121</v>
+        <v>448098</v>
       </c>
       <c r="R110" t="n">
-        <v>7032229</v>
+        <v>7032176</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13269,21 +13289,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>10:48</t>
-        </is>
-      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -13292,41 +13302,26 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120407754</v>
+        <v>120410105</v>
       </c>
       <c r="B111" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13339,43 +13334,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447910</v>
+        <v>447912</v>
       </c>
       <c r="R111" t="n">
-        <v>7031953</v>
+        <v>7031942</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13405,19 +13391,9 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>13:52</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-10-12</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>13:52</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -13432,22 +13408,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>120398194</v>
+        <v>120398171</v>
       </c>
       <c r="B112" t="n">
-        <v>77479</v>
+        <v>90580</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -13460,34 +13436,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>448084</v>
+        <v>447838</v>
       </c>
       <c r="R112" t="n">
-        <v>7032156</v>
+        <v>7031933</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13519,7 +13495,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -13529,7 +13505,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -13553,7 +13529,7 @@
       </c>
       <c r="AO112" t="inlineStr">
         <is>
-          <t>på gammal gran # Picea abies</t>
+          <t>på granlåga # Picea abies</t>
         </is>
       </c>
       <c r="AT112" t="inlineStr"/>
@@ -13571,7 +13547,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120407766</v>
+        <v>120398190</v>
       </c>
       <c r="B113" t="n">
         <v>78542</v>
@@ -13607,14 +13583,14 @@
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>448082</v>
+        <v>448091</v>
       </c>
       <c r="R113" t="n">
-        <v>7032097</v>
+        <v>7032130</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13646,7 +13622,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -13656,7 +13632,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>11:27</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13667,26 +13643,41 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120407777</v>
+        <v>120398194</v>
       </c>
       <c r="B114" t="n">
-        <v>78542</v>
+        <v>77479</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13699,34 +13690,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>448119</v>
+        <v>448084</v>
       </c>
       <c r="R114" t="n">
-        <v>7032212</v>
+        <v>7032156</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13758,7 +13749,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13768,7 +13759,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13779,26 +13770,41 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>120398192</v>
+        <v>120410090</v>
       </c>
       <c r="B115" t="n">
-        <v>74654</v>
+        <v>105017</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -13807,38 +13813,38 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6440</v>
+        <v>221725</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>448084</v>
+        <v>448077</v>
       </c>
       <c r="R115" t="n">
-        <v>7032156</v>
+        <v>7032240</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13868,21 +13874,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
@@ -13891,41 +13887,26 @@
       </c>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>120398205</v>
+        <v>120407758</v>
       </c>
       <c r="B116" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -13938,34 +13919,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>448111</v>
+        <v>447946</v>
       </c>
       <c r="R116" t="n">
-        <v>7032232</v>
+        <v>7031890</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13997,7 +13978,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -14007,7 +13988,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -14018,41 +13999,26 @@
       </c>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>rönn</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Sorbus aucuparia</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>På död rönn # Sorbus aucuparia</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120398193</v>
+        <v>120407750</v>
       </c>
       <c r="B117" t="n">
-        <v>78542</v>
+        <v>74654</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -14065,34 +14031,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>448084</v>
+        <v>447916</v>
       </c>
       <c r="R117" t="n">
-        <v>7032156</v>
+        <v>7032098</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -14124,7 +14090,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -14134,7 +14100,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -14145,41 +14111,26 @@
       </c>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ117" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK117" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>120410098</v>
+        <v>120407779</v>
       </c>
       <c r="B118" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -14192,21 +14143,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -14216,10 +14167,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447938</v>
+        <v>448080</v>
       </c>
       <c r="R118" t="n">
-        <v>7031999</v>
+        <v>7032230</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -14249,9 +14200,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>10:38</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -14266,22 +14227,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>120398177</v>
+        <v>120407759</v>
       </c>
       <c r="B119" t="n">
-        <v>74654</v>
+        <v>91512</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -14290,38 +14251,38 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6440</v>
+        <v>4769</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>447950</v>
+        <v>447940</v>
       </c>
       <c r="R119" t="n">
-        <v>7031971</v>
+        <v>7031893</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14353,7 +14314,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -14363,7 +14324,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -14374,41 +14335,26 @@
       </c>
       <c r="AG119" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ119" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK119" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>120398179</v>
+        <v>120398193</v>
       </c>
       <c r="B120" t="n">
-        <v>74654</v>
+        <v>78542</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -14421,34 +14367,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447981</v>
+        <v>448084</v>
       </c>
       <c r="R120" t="n">
-        <v>7031976</v>
+        <v>7032156</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14480,7 +14426,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -14490,7 +14436,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14514,7 +14460,7 @@
       </c>
       <c r="AO120" t="inlineStr">
         <is>
-          <t>På gammal gran # Picea abies</t>
+          <t>på gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
@@ -14532,10 +14478,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120398175</v>
+        <v>120407755</v>
       </c>
       <c r="B121" t="n">
-        <v>78626</v>
+        <v>78542</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14548,34 +14494,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>283</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447933</v>
+        <v>447922</v>
       </c>
       <c r="R121" t="n">
-        <v>7031977</v>
+        <v>7031922</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14607,7 +14553,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14617,7 +14563,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>11:59</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14628,41 +14574,26 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ121" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK121" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120410105</v>
+        <v>120398181</v>
       </c>
       <c r="B122" t="n">
-        <v>90580</v>
+        <v>77479</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14675,34 +14606,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447912</v>
+        <v>447981</v>
       </c>
       <c r="R122" t="n">
-        <v>7031942</v>
+        <v>7031976</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14732,11 +14663,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
       <c r="AD122" t="b">
         <v>0</v>
       </c>
@@ -14745,26 +14686,41 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO122" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120407752</v>
+        <v>120407753</v>
       </c>
       <c r="B123" t="n">
-        <v>90598</v>
+        <v>74640</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14773,25 +14729,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>5432</v>
+        <v>306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14801,10 +14757,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447908</v>
+        <v>447913</v>
       </c>
       <c r="R123" t="n">
-        <v>7032002</v>
+        <v>7031958</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14836,7 +14792,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14846,7 +14802,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14873,10 +14829,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120407759</v>
+        <v>120398198</v>
       </c>
       <c r="B124" t="n">
-        <v>91512</v>
+        <v>78626</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14885,38 +14841,38 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4769</v>
+        <v>283</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>447940</v>
+        <v>448094</v>
       </c>
       <c r="R124" t="n">
-        <v>7031893</v>
+        <v>7032145</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14948,7 +14904,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14958,7 +14914,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14969,26 +14925,41 @@
       </c>
       <c r="AG124" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO124" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120407776</v>
+        <v>120407744</v>
       </c>
       <c r="B125" t="n">
-        <v>91512</v>
+        <v>74654</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14997,25 +14968,25 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4769</v>
+        <v>6440</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -15025,10 +14996,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>448121</v>
+        <v>447906</v>
       </c>
       <c r="R125" t="n">
-        <v>7032208</v>
+        <v>7032176</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15060,7 +15031,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15070,7 +15041,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>10:49</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15090,17 +15061,17 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120407773</v>
+        <v>120398204</v>
       </c>
       <c r="B126" t="n">
-        <v>77479</v>
+        <v>79624</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15113,34 +15084,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>448090</v>
+        <v>448111</v>
       </c>
       <c r="R126" t="n">
-        <v>7032160</v>
+        <v>7032232</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15172,7 +15143,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15182,7 +15153,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15193,26 +15164,41 @@
       </c>
       <c r="AG126" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>På död rönn # Sorbus aucuparia</t>
+        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120398195</v>
+        <v>120398192</v>
       </c>
       <c r="B127" t="n">
-        <v>90598</v>
+        <v>74654</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -15225,21 +15211,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -15249,10 +15235,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>448076</v>
+        <v>448084</v>
       </c>
       <c r="R127" t="n">
-        <v>7032148</v>
+        <v>7032156</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15284,7 +15270,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15294,7 +15280,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15318,7 +15304,7 @@
       </c>
       <c r="AO127" t="inlineStr">
         <is>
-          <t>På död gammal gran # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -15336,10 +15322,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120398198</v>
+        <v>120398203</v>
       </c>
       <c r="B128" t="n">
-        <v>78626</v>
+        <v>74654</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -15352,21 +15338,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>283</v>
+        <v>6440</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -15376,10 +15362,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>448094</v>
+        <v>448121</v>
       </c>
       <c r="R128" t="n">
-        <v>7032145</v>
+        <v>7032229</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15411,7 +15397,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15421,7 +15407,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15445,7 +15431,7 @@
       </c>
       <c r="AO128" t="inlineStr">
         <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -15463,10 +15449,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120398172</v>
+        <v>120398178</v>
       </c>
       <c r="B129" t="n">
-        <v>74652</v>
+        <v>77479</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15475,25 +15461,25 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6486</v>
+        <v>228579</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -15503,10 +15489,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>447921</v>
+        <v>447950</v>
       </c>
       <c r="R129" t="n">
-        <v>7031952</v>
+        <v>7031971</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15538,7 +15524,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15548,7 +15534,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15572,7 +15558,7 @@
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>Djup hålighet vid granbas # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -15590,10 +15576,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>120407758</v>
+        <v>120407781</v>
       </c>
       <c r="B130" t="n">
-        <v>78542</v>
+        <v>77479</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
@@ -15606,21 +15592,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -15630,10 +15616,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>447946</v>
+        <v>448064</v>
       </c>
       <c r="R130" t="n">
-        <v>7031890</v>
+        <v>7032247</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15665,7 +15651,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -15675,7 +15661,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -15695,17 +15681,17 @@
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>120410100</v>
+        <v>120407763</v>
       </c>
       <c r="B131" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -15718,21 +15704,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15742,10 +15728,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>447936</v>
+        <v>447956</v>
       </c>
       <c r="R131" t="n">
-        <v>7032074</v>
+        <v>7031963</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15775,9 +15761,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
       <c r="AA131" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15792,19 +15788,19 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Fredrik Jonsson, Ulrika Nordin, Britta Sterner, Jana Novak</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>120407779</v>
+        <v>120407764</v>
       </c>
       <c r="B132" t="n">
         <v>78542</v>
@@ -15844,10 +15840,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>448080</v>
+        <v>447980</v>
       </c>
       <c r="R132" t="n">
-        <v>7032230</v>
+        <v>7031975</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15879,7 +15875,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -15889,7 +15885,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15916,10 +15912,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>120398181</v>
+        <v>120407746</v>
       </c>
       <c r="B133" t="n">
-        <v>77479</v>
+        <v>78542</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -15932,34 +15928,34 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>447981</v>
+        <v>447902</v>
       </c>
       <c r="R133" t="n">
-        <v>7031976</v>
+        <v>7032164</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15991,7 +15987,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -16001,7 +15997,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16012,41 +16008,26 @@
       </c>
       <c r="AG133" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ133" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK133" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120410099</v>
+        <v>120407749</v>
       </c>
       <c r="B134" t="n">
-        <v>90598</v>
+        <v>77479</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16059,21 +16040,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>5432</v>
+        <v>228579</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -16083,10 +16064,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>447940</v>
+        <v>447916</v>
       </c>
       <c r="R134" t="n">
-        <v>7032074</v>
+        <v>7032098</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16116,9 +16097,19 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>14:10</t>
+        </is>
+      </c>
       <c r="AA134" t="inlineStr">
         <is>
           <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16133,22 +16124,22 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120407741</v>
+        <v>120407754</v>
       </c>
       <c r="B135" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16161,34 +16152,43 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P135" t="inlineStr">
         <is>
           <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>447935</v>
+        <v>447910</v>
       </c>
       <c r="R135" t="n">
-        <v>7032200</v>
+        <v>7031953</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD135" t="b">

--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -13216,10 +13216,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>120410088</v>
+        <v>120398190</v>
       </c>
       <c r="B110" t="n">
-        <v>90580</v>
+        <v>78542</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -13232,34 +13232,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>448098</v>
+        <v>448091</v>
       </c>
       <c r="R110" t="n">
-        <v>7032176</v>
+        <v>7032130</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13289,11 +13289,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>11:16</t>
+        </is>
+      </c>
       <c r="AD110" t="b">
         <v>0</v>
       </c>
@@ -13302,26 +13312,41 @@
       </c>
       <c r="AG110" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ110" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO110" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>120410105</v>
+        <v>120398194</v>
       </c>
       <c r="B111" t="n">
-        <v>90580</v>
+        <v>77479</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -13334,34 +13359,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447912</v>
+        <v>448084</v>
       </c>
       <c r="R111" t="n">
-        <v>7031942</v>
+        <v>7032156</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13391,11 +13416,21 @@
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AD111" t="b">
         <v>0</v>
       </c>
@@ -13404,16 +13439,31 @@
       </c>
       <c r="AG111" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ111" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO111" t="inlineStr">
+        <is>
+          <t>på gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Britta Sterner</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Britta Sterner, Johan Råghall</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -13547,10 +13597,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>120398190</v>
+        <v>120410088</v>
       </c>
       <c r="B113" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -13563,34 +13613,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>448091</v>
+        <v>448098</v>
       </c>
       <c r="R113" t="n">
-        <v>7032130</v>
+        <v>7032176</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13620,21 +13670,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>11:16</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -13643,41 +13683,26 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>120398194</v>
+        <v>120410105</v>
       </c>
       <c r="B114" t="n">
-        <v>77479</v>
+        <v>90580</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -13690,34 +13715,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>448084</v>
+        <v>447912</v>
       </c>
       <c r="R114" t="n">
-        <v>7032156</v>
+        <v>7031942</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13747,21 +13772,11 @@
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-10-12</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -13770,31 +13785,16 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>på gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Britta Sterner</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Britta Sterner, Johan Råghall</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
@@ -14478,10 +14478,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120407755</v>
+        <v>120398181</v>
       </c>
       <c r="B121" t="n">
-        <v>78542</v>
+        <v>77479</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -14494,34 +14494,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447922</v>
+        <v>447981</v>
       </c>
       <c r="R121" t="n">
-        <v>7031922</v>
+        <v>7031976</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14553,7 +14553,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14574,26 +14574,41 @@
       </c>
       <c r="AG121" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO121" t="inlineStr">
+        <is>
+          <t>På gammal gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>120398181</v>
+        <v>120407753</v>
       </c>
       <c r="B122" t="n">
-        <v>77479</v>
+        <v>74640</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -14602,38 +14617,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228579</v>
+        <v>306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Kornig nållav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Chaenotheca chlorella</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447981</v>
+        <v>447913</v>
       </c>
       <c r="R122" t="n">
-        <v>7031976</v>
+        <v>7031958</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14665,7 +14680,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -14675,7 +14690,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14686,41 +14701,26 @@
       </c>
       <c r="AG122" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ122" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK122" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>120407753</v>
+        <v>120407755</v>
       </c>
       <c r="B123" t="n">
-        <v>74640</v>
+        <v>78542</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -14729,25 +14729,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>306</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kornig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Chaenotheca chlorella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14757,10 +14757,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447913</v>
+        <v>447922</v>
       </c>
       <c r="R123" t="n">
-        <v>7031958</v>
+        <v>7031922</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14792,7 +14792,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -14802,7 +14802,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14829,10 +14829,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>120398198</v>
+        <v>120398178</v>
       </c>
       <c r="B124" t="n">
-        <v>78626</v>
+        <v>77479</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -14845,34 +14845,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>283</v>
+        <v>228579</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kavernularia</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hypogymnia hultenii</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Degel.) Krog</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>448094</v>
+        <v>447950</v>
       </c>
       <c r="R124" t="n">
-        <v>7032145</v>
+        <v>7031971</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14938,7 +14938,7 @@
       </c>
       <c r="AO124" t="inlineStr">
         <is>
-          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+          <t>på bark på stam av gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
@@ -14956,10 +14956,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>120407744</v>
+        <v>120398198</v>
       </c>
       <c r="B125" t="n">
-        <v>74654</v>
+        <v>78626</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -14972,34 +14972,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6440</v>
+        <v>283</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Kavernularia</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hypogymnia hultenii</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Degel.) Krog</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Stångmyren, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>447906</v>
+        <v>448094</v>
       </c>
       <c r="R125" t="n">
-        <v>7032176</v>
+        <v>7032145</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -15031,7 +15031,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -15041,7 +15041,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -15052,26 +15052,41 @@
       </c>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>på tunna grangrenar på undertryckt gran # Picea abies</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Johan Råghall</t>
+          <t>Fredrik Jonsson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Johan Råghall, Britta Sterner</t>
+          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>120398204</v>
+        <v>120398192</v>
       </c>
       <c r="B126" t="n">
-        <v>79624</v>
+        <v>74654</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -15084,21 +15099,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>2081</v>
+        <v>6440</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -15108,10 +15123,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>448111</v>
+        <v>448084</v>
       </c>
       <c r="R126" t="n">
-        <v>7032232</v>
+        <v>7032156</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -15143,7 +15158,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -15153,7 +15168,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -15167,17 +15182,17 @@
       </c>
       <c r="AJ126" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK126" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO126" t="inlineStr">
         <is>
-          <t>På död rönn # Sorbus aucuparia</t>
+          <t>På gammal gran # Picea abies</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -15195,7 +15210,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>120398192</v>
+        <v>120398203</v>
       </c>
       <c r="B127" t="n">
         <v>74654</v>
@@ -15235,10 +15250,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>448084</v>
+        <v>448121</v>
       </c>
       <c r="R127" t="n">
-        <v>7032156</v>
+        <v>7032229</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -15270,7 +15285,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -15280,7 +15295,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15322,7 +15337,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>120398203</v>
+        <v>120407744</v>
       </c>
       <c r="B128" t="n">
         <v>74654</v>
@@ -15358,14 +15373,14 @@
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
+          <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>448121</v>
+        <v>447906</v>
       </c>
       <c r="R128" t="n">
-        <v>7032229</v>
+        <v>7032176</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15397,7 +15412,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -15407,7 +15422,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -15418,41 +15433,26 @@
       </c>
       <c r="AG128" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ128" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK128" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>På gammal gran # Picea abies</t>
-        </is>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson</t>
+          <t>Johan Råghall</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Fredrik Jonsson, Ulrika Nordin, Johan Råghall, Jana Novak, Britta Sterner</t>
+          <t>Johan Råghall, Britta Sterner</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>120398178</v>
+        <v>120398204</v>
       </c>
       <c r="B129" t="n">
-        <v>77479</v>
+        <v>79624</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
@@ -15465,34 +15465,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>228579</v>
+        <v>2081</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>S. om Stångmyren, Ö. om Tvärån, Alsen, Jmt</t>
+          <t>M. Nybodarna och Stångmyren, Ö. Tvärån, Alsen, Jmt</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>447950</v>
+        <v>448111</v>
       </c>
       <c r="R129" t="n">
-        <v>7031971</v>
+        <v>7032232</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15524,7 +15524,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -15534,7 +15534,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -15548,17 +15548,17 @@
       </c>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO129" t="inlineStr">
         <is>
-          <t>på bark på stam av gammal gran # Picea abies</t>
+          <t>På död rönn # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -16024,10 +16024,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>120407749</v>
+        <v>120407754</v>
       </c>
       <c r="B134" t="n">
-        <v>77479</v>
+        <v>57320</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -16040,34 +16040,43 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Tibell</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P134" t="inlineStr">
         <is>
           <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>447916</v>
+        <v>447910</v>
       </c>
       <c r="R134" t="n">
-        <v>7032098</v>
+        <v>7031953</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -16099,7 +16108,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -16109,7 +16118,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -16136,10 +16145,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>120407754</v>
+        <v>120407749</v>
       </c>
       <c r="B135" t="n">
-        <v>57320</v>
+        <v>77479</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -16152,43 +16161,34 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M135" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
           <t>Stångmyren, Jmt</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>447910</v>
+        <v>447916</v>
       </c>
       <c r="R135" t="n">
-        <v>7031953</v>
+        <v>7032098</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -16220,7 +16220,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD135" t="b">

--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -16260,7 +16260,7 @@
         <v>120970546</v>
       </c>
       <c r="B136" t="n">
-        <v>98069</v>
+        <v>98079</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>

--- a/artfynd/A 21847-2024 artfynd.xlsx
+++ b/artfynd/A 21847-2024 artfynd.xlsx
@@ -16260,7 +16260,7 @@
         <v>120970546</v>
       </c>
       <c r="B136" t="n">
-        <v>98079</v>
+        <v>98092</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
